--- a/output/2025-10-01.xlsx
+++ b/output/2025-10-01.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1.78</v>
+        <v>2.86</v>
       </c>
       <c r="F14" t="n">
-        <v>5.68</v>
+        <v>5.15</v>
       </c>
       <c r="G14" t="n">
-        <v>47.5</v>
+        <v>53.3</v>
       </c>
       <c r="H14" t="n">
-        <v>1.6</v>
+        <v>3.3</v>
       </c>
       <c r="I14" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J14" t="n">
-        <v>28.58</v>
+        <v>37.42</v>
       </c>
       <c r="K14" t="n">
-        <v>75.29000000000001</v>
+        <v>30</v>
       </c>
       <c r="L14" t="n">
-        <v>80.53</v>
+        <v>47.96</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07:19:11</t>
+          <t>07:19:05</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="F15" t="n">
-        <v>5.86</v>
+        <v>6.06</v>
       </c>
       <c r="G15" t="n">
-        <v>43.5</v>
+        <v>47.2</v>
       </c>
       <c r="H15" t="n">
-        <v>1.1</v>
+        <v>0.1</v>
       </c>
       <c r="I15" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>54.11</v>
+        <v>-76.66</v>
       </c>
       <c r="K15" t="n">
-        <v>12.07</v>
+        <v>-84.40000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>55.44</v>
+        <v>114.02</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07:20:24</t>
+          <t>07:20:02</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.14</v>
+        <v>2.05</v>
       </c>
       <c r="F16" t="n">
-        <v>5.77</v>
+        <v>5.92</v>
       </c>
       <c r="G16" t="n">
-        <v>47.3</v>
+        <v>59.7</v>
       </c>
       <c r="H16" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J16" t="n">
-        <v>-7.65</v>
+        <v>-14.13</v>
       </c>
       <c r="K16" t="n">
-        <v>-44.32</v>
+        <v>86.14</v>
       </c>
       <c r="L16" t="n">
-        <v>44.97</v>
+        <v>87.29000000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07:24:26</t>
+          <t>07:23:20</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,28 +751,28 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="F17" t="n">
-        <v>5.69</v>
+        <v>6.39</v>
       </c>
       <c r="G17" t="n">
-        <v>62.4</v>
+        <v>39.8</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="I17" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J17" t="n">
-        <v>124.19</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>-117.52</v>
+        <v>-22.64</v>
       </c>
       <c r="L17" t="n">
-        <v>170.98</v>
+        <v>24.5</v>
       </c>
     </row>
     <row r="18">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.12</v>
+        <v>1.76</v>
       </c>
       <c r="F18" t="n">
-        <v>5.88</v>
+        <v>6.13</v>
       </c>
       <c r="G18" t="n">
-        <v>49.5</v>
+        <v>41.7</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="I18" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J18" t="n">
-        <v>-58.56</v>
+        <v>-128.75</v>
       </c>
       <c r="K18" t="n">
-        <v>54.78</v>
+        <v>-229.87</v>
       </c>
       <c r="L18" t="n">
-        <v>80.19</v>
+        <v>263.47</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07:26:44</t>
+          <t>07:27:44</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.36</v>
+        <v>2.08</v>
       </c>
       <c r="F19" t="n">
-        <v>5.99</v>
+        <v>5.93</v>
       </c>
       <c r="G19" t="n">
-        <v>46.4</v>
+        <v>51.6</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J19" t="n">
-        <v>106.75</v>
+        <v>4.68</v>
       </c>
       <c r="K19" t="n">
-        <v>97.45999999999999</v>
+        <v>-121.35</v>
       </c>
       <c r="L19" t="n">
-        <v>144.55</v>
+        <v>121.44</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07:32:34</t>
+          <t>07:33:12</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.24</v>
+        <v>1.84</v>
       </c>
       <c r="F20" t="n">
-        <v>5.38</v>
+        <v>5.84</v>
       </c>
       <c r="G20" t="n">
-        <v>38.9</v>
+        <v>47.4</v>
       </c>
       <c r="H20" t="n">
         <v>0</v>
@@ -892,19 +892,19 @@
         <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>143.63</v>
+        <v>-205.73</v>
       </c>
       <c r="K20" t="n">
-        <v>-65.97</v>
+        <v>-29.51</v>
       </c>
       <c r="L20" t="n">
-        <v>158.06</v>
+        <v>207.84</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07:33:51</t>
+          <t>07:34:50</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.16</v>
+        <v>2.02</v>
       </c>
       <c r="F21" t="n">
-        <v>6.85</v>
+        <v>6.01</v>
       </c>
       <c r="G21" t="n">
-        <v>45.7</v>
+        <v>41.2</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="I21" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J21" t="n">
-        <v>40.55</v>
+        <v>173.95</v>
       </c>
       <c r="K21" t="n">
-        <v>-28.31</v>
+        <v>19.08</v>
       </c>
       <c r="L21" t="n">
-        <v>49.45</v>
+        <v>174.99</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07:36:00</t>
+          <t>07:36:02</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.05</v>
+        <v>2.13</v>
       </c>
       <c r="F22" t="n">
-        <v>5.88</v>
+        <v>5.97</v>
       </c>
       <c r="G22" t="n">
-        <v>58.8</v>
+        <v>51.2</v>
       </c>
       <c r="H22" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J22" t="n">
-        <v>-40.16</v>
+        <v>-209.23</v>
       </c>
       <c r="K22" t="n">
-        <v>-187.18</v>
+        <v>-95.43000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>191.44</v>
+        <v>229.97</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07:40:35</t>
+          <t>07:41:27</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="F23" t="n">
-        <v>6.57</v>
+        <v>6.13</v>
       </c>
       <c r="G23" t="n">
-        <v>44.8</v>
+        <v>33.9</v>
       </c>
       <c r="H23" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
         <v>25</v>
       </c>
       <c r="J23" t="n">
-        <v>-10.18</v>
+        <v>83.45999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>130.07</v>
+        <v>132.62</v>
       </c>
       <c r="L23" t="n">
-        <v>130.47</v>
+        <v>156.69</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07:42:14</t>
+          <t>07:42:58</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.03</v>
+        <v>1.94</v>
       </c>
       <c r="F24" t="n">
-        <v>6.08</v>
+        <v>6.2</v>
       </c>
       <c r="G24" t="n">
-        <v>79.2</v>
+        <v>49.6</v>
       </c>
       <c r="H24" t="n">
         <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>121.95</v>
+        <v>168.48</v>
       </c>
       <c r="K24" t="n">
-        <v>80.64</v>
+        <v>-22.57</v>
       </c>
       <c r="L24" t="n">
-        <v>146.2</v>
+        <v>169.99</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07:44:24</t>
+          <t>07:44:27</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>1.8</v>
+        <v>2.19</v>
       </c>
       <c r="F25" t="n">
-        <v>5.64</v>
+        <v>6.35</v>
       </c>
       <c r="G25" t="n">
-        <v>51.6</v>
+        <v>45.3</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J25" t="n">
-        <v>-172.17</v>
+        <v>3.78</v>
       </c>
       <c r="K25" t="n">
-        <v>-85.7</v>
+        <v>-264.62</v>
       </c>
       <c r="L25" t="n">
-        <v>192.32</v>
+        <v>264.65</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07:49:49</t>
+          <t>07:49:51</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1.96</v>
+        <v>2.44</v>
       </c>
       <c r="F26" t="n">
-        <v>5.99</v>
+        <v>6.35</v>
       </c>
       <c r="G26" t="n">
-        <v>50.2</v>
+        <v>32.8</v>
       </c>
       <c r="H26" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
       <c r="I26" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J26" t="n">
-        <v>-363.56</v>
+        <v>-628.67</v>
       </c>
       <c r="K26" t="n">
-        <v>174.87</v>
+        <v>25.83</v>
       </c>
       <c r="L26" t="n">
-        <v>403.43</v>
+        <v>629.2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07:52:25</t>
+          <t>07:51:27</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>1.91</v>
+        <v>2.31</v>
       </c>
       <c r="F27" t="n">
-        <v>5.76</v>
+        <v>5.85</v>
       </c>
       <c r="G27" t="n">
-        <v>58.9</v>
+        <v>44.9</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="I27" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J27" t="n">
-        <v>-40.05</v>
+        <v>-297.08</v>
       </c>
       <c r="K27" t="n">
-        <v>-143.32</v>
+        <v>-268.94</v>
       </c>
       <c r="L27" t="n">
-        <v>148.81</v>
+        <v>400.73</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07:54:23</t>
+          <t>07:53:35</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.91</v>
+        <v>2.26</v>
       </c>
       <c r="F28" t="n">
-        <v>6.13</v>
+        <v>6.17</v>
       </c>
       <c r="G28" t="n">
-        <v>44.9</v>
+        <v>60</v>
       </c>
       <c r="H28" t="n">
-        <v>6.9</v>
+        <v>1.6</v>
       </c>
       <c r="I28" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J28" t="n">
-        <v>119.35</v>
+        <v>56.74</v>
       </c>
       <c r="K28" t="n">
-        <v>127.78</v>
+        <v>107.9</v>
       </c>
       <c r="L28" t="n">
-        <v>174.85</v>
+        <v>121.91</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08:05:07</t>
+          <t>08:03:44</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,13 +1255,13 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.31</v>
+        <v>2.27</v>
       </c>
       <c r="F29" t="n">
-        <v>7.38</v>
+        <v>6.83</v>
       </c>
       <c r="G29" t="n">
-        <v>45</v>
+        <v>44.7</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
@@ -1270,19 +1270,19 @@
         <v>28</v>
       </c>
       <c r="J29" t="n">
-        <v>-3.63</v>
+        <v>-27.86</v>
       </c>
       <c r="K29" t="n">
-        <v>-44</v>
+        <v>-36.02</v>
       </c>
       <c r="L29" t="n">
-        <v>44.15</v>
+        <v>45.54</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08:06:39</t>
+          <t>08:05:19</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.25</v>
+        <v>1.79</v>
       </c>
       <c r="F30" t="n">
-        <v>5.9</v>
+        <v>5.77</v>
       </c>
       <c r="G30" t="n">
-        <v>50.4</v>
+        <v>45.6</v>
       </c>
       <c r="H30" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J30" t="n">
-        <v>9.970000000000001</v>
+        <v>44.74</v>
       </c>
       <c r="K30" t="n">
-        <v>17.82</v>
+        <v>-40.99</v>
       </c>
       <c r="L30" t="n">
-        <v>20.42</v>
+        <v>60.68</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08:07:30</t>
+          <t>08:07:15</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.22</v>
+        <v>2.48</v>
       </c>
       <c r="F31" t="n">
-        <v>7.13</v>
+        <v>6.18</v>
       </c>
       <c r="G31" t="n">
-        <v>50.6</v>
+        <v>53.5</v>
       </c>
       <c r="H31" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J31" t="n">
-        <v>12.18</v>
+        <v>53.84</v>
       </c>
       <c r="K31" t="n">
-        <v>33.65</v>
+        <v>69.75</v>
       </c>
       <c r="L31" t="n">
-        <v>35.79</v>
+        <v>88.11</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08:11:10</t>
+          <t>08:11:14</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="F32" t="n">
-        <v>5.92</v>
+        <v>6.11</v>
       </c>
       <c r="G32" t="n">
-        <v>44.2</v>
+        <v>44.5</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
       </c>
       <c r="I32" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>-62.48</v>
+        <v>-87.88</v>
       </c>
       <c r="K32" t="n">
-        <v>-32.91</v>
+        <v>-87.8</v>
       </c>
       <c r="L32" t="n">
-        <v>70.62</v>
+        <v>124.22</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08:12:32</t>
+          <t>08:13:18</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.37</v>
+        <v>2.3</v>
       </c>
       <c r="F33" t="n">
-        <v>6.45</v>
+        <v>5.8</v>
       </c>
       <c r="G33" t="n">
-        <v>42.6</v>
+        <v>51.3</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="I33" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J33" t="n">
-        <v>-76.77</v>
+        <v>-91.76000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>28.39</v>
+        <v>-4.83</v>
       </c>
       <c r="L33" t="n">
-        <v>81.84999999999999</v>
+        <v>91.89</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08:13:57</t>
+          <t>08:14:23</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.38</v>
+        <v>2.7</v>
       </c>
       <c r="F34" t="n">
-        <v>6.47</v>
+        <v>5.84</v>
       </c>
       <c r="G34" t="n">
-        <v>40.8</v>
+        <v>47.8</v>
       </c>
       <c r="H34" t="n">
-        <v>0.8</v>
+        <v>1.2</v>
       </c>
       <c r="I34" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J34" t="n">
-        <v>72.89</v>
+        <v>-138.25</v>
       </c>
       <c r="K34" t="n">
-        <v>68.86</v>
+        <v>-15.96</v>
       </c>
       <c r="L34" t="n">
-        <v>100.27</v>
+        <v>139.17</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08:18:32</t>
+          <t>08:19:26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.46</v>
+        <v>1.98</v>
       </c>
       <c r="F35" t="n">
-        <v>5.88</v>
+        <v>6.2</v>
       </c>
       <c r="G35" t="n">
-        <v>46.3</v>
+        <v>34.3</v>
       </c>
       <c r="H35" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J35" t="n">
-        <v>6.67</v>
+        <v>283.15</v>
       </c>
       <c r="K35" t="n">
-        <v>-248.69</v>
+        <v>179.77</v>
       </c>
       <c r="L35" t="n">
-        <v>248.78</v>
+        <v>335.4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08:20:00</t>
+          <t>08:21:03</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.31</v>
+        <v>2.37</v>
       </c>
       <c r="F36" t="n">
-        <v>6.34</v>
+        <v>6.14</v>
       </c>
       <c r="G36" t="n">
-        <v>58.3</v>
+        <v>51.5</v>
       </c>
       <c r="H36" t="n">
         <v>0</v>
       </c>
       <c r="I36" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J36" t="n">
-        <v>-22.82</v>
+        <v>-191.9</v>
       </c>
       <c r="K36" t="n">
-        <v>81.29000000000001</v>
+        <v>285.95</v>
       </c>
       <c r="L36" t="n">
-        <v>84.43000000000001</v>
+        <v>344.38</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08:22:15</t>
+          <t>08:21:55</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.88</v>
+        <v>2.26</v>
       </c>
       <c r="F37" t="n">
-        <v>7.02</v>
+        <v>6.02</v>
       </c>
       <c r="G37" t="n">
-        <v>61.4</v>
+        <v>57.4</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="I37" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J37" t="n">
-        <v>101.41</v>
+        <v>59.59</v>
       </c>
       <c r="K37" t="n">
-        <v>11.09</v>
+        <v>23.01</v>
       </c>
       <c r="L37" t="n">
-        <v>102.02</v>
+        <v>63.88</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08:27:36</t>
+          <t>08:26:13</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,13 +1633,13 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>1.99</v>
+        <v>2.87</v>
       </c>
       <c r="F38" t="n">
         <v>6.3</v>
       </c>
       <c r="G38" t="n">
-        <v>58.8</v>
+        <v>48.9</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -1648,19 +1648,19 @@
         <v>25</v>
       </c>
       <c r="J38" t="n">
-        <v>190.48</v>
+        <v>304.61</v>
       </c>
       <c r="K38" t="n">
-        <v>-65.81</v>
+        <v>325.53</v>
       </c>
       <c r="L38" t="n">
-        <v>201.53</v>
+        <v>445.82</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08:30:02</t>
+          <t>08:28:03</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.08</v>
+        <v>2.9</v>
       </c>
       <c r="F39" t="n">
-        <v>5.37</v>
+        <v>6.42</v>
       </c>
       <c r="G39" t="n">
-        <v>60.6</v>
+        <v>59.7</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="I39" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J39" t="n">
-        <v>-136.5</v>
+        <v>-39.64</v>
       </c>
       <c r="K39" t="n">
-        <v>177.53</v>
+        <v>-80.76000000000001</v>
       </c>
       <c r="L39" t="n">
-        <v>223.94</v>
+        <v>89.97</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08:31:52</t>
+          <t>08:29:13</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.31</v>
+        <v>2.24</v>
       </c>
       <c r="F40" t="n">
-        <v>6.56</v>
+        <v>5.78</v>
       </c>
       <c r="G40" t="n">
-        <v>53.5</v>
+        <v>26.7</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="I40" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J40" t="n">
-        <v>-264.67</v>
+        <v>411.41</v>
       </c>
       <c r="K40" t="n">
-        <v>91.76000000000001</v>
+        <v>12.69</v>
       </c>
       <c r="L40" t="n">
-        <v>280.13</v>
+        <v>411.61</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08:36:26</t>
+          <t>08:33:28</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,13 +1759,13 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.03</v>
+        <v>2.29</v>
       </c>
       <c r="F41" t="n">
-        <v>6.53</v>
+        <v>5.7</v>
       </c>
       <c r="G41" t="n">
-        <v>41.6</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
@@ -1774,19 +1774,19 @@
         <v>26</v>
       </c>
       <c r="J41" t="n">
-        <v>-201.88</v>
+        <v>14.92</v>
       </c>
       <c r="K41" t="n">
-        <v>238.02</v>
+        <v>-167.86</v>
       </c>
       <c r="L41" t="n">
-        <v>312.1</v>
+        <v>168.53</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08:37:46</t>
+          <t>08:35:24</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>2.32</v>
+        <v>2.48</v>
       </c>
       <c r="F42" t="n">
-        <v>6</v>
+        <v>5.83</v>
       </c>
       <c r="G42" t="n">
-        <v>50.9</v>
+        <v>48.9</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J42" t="n">
-        <v>134.92</v>
+        <v>-264.7</v>
       </c>
       <c r="K42" t="n">
-        <v>-11.57</v>
+        <v>-689.86</v>
       </c>
       <c r="L42" t="n">
-        <v>135.42</v>
+        <v>738.9</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08:39:15</t>
+          <t>08:38:00</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.66</v>
+        <v>1.93</v>
       </c>
       <c r="F43" t="n">
-        <v>5.46</v>
+        <v>5.72</v>
       </c>
       <c r="G43" t="n">
-        <v>53.7</v>
+        <v>45</v>
       </c>
       <c r="H43" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J43" t="n">
-        <v>-12.05</v>
+        <v>240.98</v>
       </c>
       <c r="K43" t="n">
-        <v>-300.59</v>
+        <v>70.45999999999999</v>
       </c>
       <c r="L43" t="n">
-        <v>300.83</v>
+        <v>251.07</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08:50:18</t>
+          <t>08:49:42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.39</v>
+        <v>2.62</v>
       </c>
       <c r="F44" t="n">
-        <v>6.25</v>
+        <v>6.05</v>
       </c>
       <c r="G44" t="n">
-        <v>59.7</v>
+        <v>40.7</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J44" t="n">
-        <v>-1.66</v>
+        <v>-46.27</v>
       </c>
       <c r="K44" t="n">
-        <v>24.54</v>
+        <v>-63.04</v>
       </c>
       <c r="L44" t="n">
-        <v>24.6</v>
+        <v>78.2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:51:41</t>
+          <t>08:51:49</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.14</v>
+        <v>2.21</v>
       </c>
       <c r="F45" t="n">
-        <v>5.73</v>
+        <v>5.56</v>
       </c>
       <c r="G45" t="n">
-        <v>53.7</v>
+        <v>48.7</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J45" t="n">
-        <v>78.93000000000001</v>
+        <v>23.29</v>
       </c>
       <c r="K45" t="n">
-        <v>31.52</v>
+        <v>-9.27</v>
       </c>
       <c r="L45" t="n">
-        <v>84.98999999999999</v>
+        <v>25.07</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08:53:57</t>
+          <t>08:52:39</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="F46" t="n">
-        <v>6.26</v>
+        <v>5.75</v>
       </c>
       <c r="G46" t="n">
-        <v>50.9</v>
+        <v>45.5</v>
       </c>
       <c r="H46" t="n">
-        <v>6.7</v>
+        <v>5.3</v>
       </c>
       <c r="I46" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J46" t="n">
-        <v>59.44</v>
+        <v>-72.45</v>
       </c>
       <c r="K46" t="n">
-        <v>-35.27</v>
+        <v>-79.08</v>
       </c>
       <c r="L46" t="n">
-        <v>69.12</v>
+        <v>107.25</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08:58:27</t>
+          <t>08:56:55</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.55</v>
+        <v>2.22</v>
       </c>
       <c r="F47" t="n">
-        <v>5.97</v>
+        <v>6.25</v>
       </c>
       <c r="G47" t="n">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="H47" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
         <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>-72.76000000000001</v>
+        <v>-88.86</v>
       </c>
       <c r="K47" t="n">
-        <v>118.09</v>
+        <v>46.37</v>
       </c>
       <c r="L47" t="n">
-        <v>138.71</v>
+        <v>100.23</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09:00:31</t>
+          <t>08:58:34</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.57</v>
+        <v>2.31</v>
       </c>
       <c r="F48" t="n">
-        <v>5.71</v>
+        <v>5.67</v>
       </c>
       <c r="G48" t="n">
-        <v>45.7</v>
+        <v>46.7</v>
       </c>
       <c r="H48" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J48" t="n">
-        <v>15.32</v>
+        <v>95.01000000000001</v>
       </c>
       <c r="K48" t="n">
-        <v>-40</v>
+        <v>-140.77</v>
       </c>
       <c r="L48" t="n">
-        <v>42.83</v>
+        <v>169.83</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09:01:42</t>
+          <t>09:00:02</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.23</v>
+        <v>2.35</v>
       </c>
       <c r="F49" t="n">
-        <v>5.65</v>
+        <v>6.26</v>
       </c>
       <c r="G49" t="n">
-        <v>53.8</v>
+        <v>46.1</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="I49" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="J49" t="n">
-        <v>57.74</v>
+        <v>-11.26</v>
       </c>
       <c r="K49" t="n">
-        <v>-32.63</v>
+        <v>-172.46</v>
       </c>
       <c r="L49" t="n">
-        <v>66.31999999999999</v>
+        <v>172.82</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09:07:28</t>
+          <t>09:06:02</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="F50" t="n">
-        <v>5.75</v>
+        <v>6.13</v>
       </c>
       <c r="G50" t="n">
-        <v>42.3</v>
+        <v>33.1</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="I50" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>121.55</v>
+        <v>127.4</v>
       </c>
       <c r="K50" t="n">
-        <v>-101.54</v>
+        <v>-71.81</v>
       </c>
       <c r="L50" t="n">
-        <v>158.38</v>
+        <v>146.24</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09:09:44</t>
+          <t>09:07:33</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.2</v>
+        <v>2.53</v>
       </c>
       <c r="F51" t="n">
-        <v>5.83</v>
+        <v>7.09</v>
       </c>
       <c r="G51" t="n">
-        <v>55.5</v>
+        <v>45.2</v>
       </c>
       <c r="H51" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J51" t="n">
-        <v>73.73999999999999</v>
+        <v>-43.69</v>
       </c>
       <c r="K51" t="n">
-        <v>-63.4</v>
+        <v>-146.31</v>
       </c>
       <c r="L51" t="n">
-        <v>97.25</v>
+        <v>152.69</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09:11:43</t>
+          <t>09:08:51</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.13</v>
+        <v>2.31</v>
       </c>
       <c r="F52" t="n">
-        <v>5.82</v>
+        <v>6.46</v>
       </c>
       <c r="G52" t="n">
-        <v>52.7</v>
+        <v>61.7</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J52" t="n">
-        <v>-98.53</v>
+        <v>117.37</v>
       </c>
       <c r="K52" t="n">
-        <v>-152.53</v>
+        <v>-61.36</v>
       </c>
       <c r="L52" t="n">
-        <v>181.58</v>
+        <v>132.44</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09:18:21</t>
+          <t>09:13:44</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>2.32</v>
+        <v>2.15</v>
       </c>
       <c r="F53" t="n">
-        <v>5.58</v>
+        <v>6.52</v>
       </c>
       <c r="G53" t="n">
-        <v>53.5</v>
+        <v>42.1</v>
       </c>
       <c r="H53" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="I53" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J53" t="n">
-        <v>-134.5</v>
+        <v>-68.62</v>
       </c>
       <c r="K53" t="n">
-        <v>-87.87</v>
+        <v>-86.81</v>
       </c>
       <c r="L53" t="n">
-        <v>160.66</v>
+        <v>110.66</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09:20:37</t>
+          <t>09:14:36</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.47</v>
+        <v>2.72</v>
       </c>
       <c r="F54" t="n">
-        <v>6.01</v>
+        <v>6.23</v>
       </c>
       <c r="G54" t="n">
-        <v>53.9</v>
+        <v>55.9</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>-59.17</v>
+        <v>17.66</v>
       </c>
       <c r="K54" t="n">
-        <v>-76.59</v>
+        <v>-350.07</v>
       </c>
       <c r="L54" t="n">
-        <v>96.78</v>
+        <v>350.52</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09:21:38</t>
+          <t>09:15:37</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="F55" t="n">
-        <v>5.61</v>
+        <v>6.1</v>
       </c>
       <c r="G55" t="n">
-        <v>51.4</v>
+        <v>43.2</v>
       </c>
       <c r="H55" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="I55" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J55" t="n">
-        <v>-113.5</v>
+        <v>31.76</v>
       </c>
       <c r="K55" t="n">
-        <v>164.95</v>
+        <v>-103.07</v>
       </c>
       <c r="L55" t="n">
-        <v>200.23</v>
+        <v>107.85</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09:26:18</t>
+          <t>09:19:22</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.67</v>
+        <v>3.46</v>
       </c>
       <c r="F56" t="n">
-        <v>6.03</v>
+        <v>5.63</v>
       </c>
       <c r="G56" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="I56" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J56" t="n">
-        <v>631.62</v>
+        <v>376.74</v>
       </c>
       <c r="K56" t="n">
-        <v>-341.88</v>
+        <v>609.8</v>
       </c>
       <c r="L56" t="n">
-        <v>718.21</v>
+        <v>716.79</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09:27:29</t>
+          <t>09:20:55</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>2.59</v>
+        <v>2.17</v>
       </c>
       <c r="F57" t="n">
-        <v>6.01</v>
+        <v>5.84</v>
       </c>
       <c r="G57" t="n">
-        <v>35.7</v>
+        <v>62.7</v>
       </c>
       <c r="H57" t="n">
-        <v>1.8</v>
+        <v>0.1</v>
       </c>
       <c r="I57" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J57" t="n">
-        <v>392.41</v>
+        <v>-147.02</v>
       </c>
       <c r="K57" t="n">
-        <v>185.68</v>
+        <v>23.31</v>
       </c>
       <c r="L57" t="n">
-        <v>434.13</v>
+        <v>148.86</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09:28:58</t>
+          <t>09:23:07</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.55</v>
+        <v>2.46</v>
       </c>
       <c r="F58" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="G58" t="n">
-        <v>52.1</v>
+        <v>43.1</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="I58" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>7.83</v>
+        <v>371.36</v>
       </c>
       <c r="K58" t="n">
-        <v>-210.36</v>
+        <v>-200.31</v>
       </c>
       <c r="L58" t="n">
-        <v>210.5</v>
+        <v>421.94</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09:38:58</t>
+          <t>09:31:01</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.08</v>
+        <v>2.53</v>
       </c>
       <c r="F59" t="n">
-        <v>5.81</v>
+        <v>5.95</v>
       </c>
       <c r="G59" t="n">
-        <v>36</v>
+        <v>65.8</v>
       </c>
       <c r="H59" t="n">
         <v>0</v>
@@ -2530,19 +2530,19 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>0.62</v>
+        <v>-34.39</v>
       </c>
       <c r="K59" t="n">
-        <v>10.02</v>
+        <v>181.29</v>
       </c>
       <c r="L59" t="n">
-        <v>10.04</v>
+        <v>184.52</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09:40:41</t>
+          <t>09:32:14</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.69</v>
+        <v>2.11</v>
       </c>
       <c r="F60" t="n">
-        <v>5.65</v>
+        <v>5.57</v>
       </c>
       <c r="G60" t="n">
-        <v>58.5</v>
+        <v>36.6</v>
       </c>
       <c r="H60" t="n">
         <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J60" t="n">
-        <v>82.95999999999999</v>
+        <v>-47.99</v>
       </c>
       <c r="K60" t="n">
-        <v>-67.45999999999999</v>
+        <v>-51.8</v>
       </c>
       <c r="L60" t="n">
-        <v>106.93</v>
+        <v>70.61</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09:42:17</t>
+          <t>09:33:55</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.01</v>
+        <v>2.25</v>
       </c>
       <c r="F61" t="n">
-        <v>5.46</v>
+        <v>4.93</v>
       </c>
       <c r="G61" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>0.9</v>
       </c>
       <c r="I61" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J61" t="n">
-        <v>10.62</v>
+        <v>60.55</v>
       </c>
       <c r="K61" t="n">
-        <v>-40.02</v>
+        <v>-21.23</v>
       </c>
       <c r="L61" t="n">
-        <v>41.41</v>
+        <v>64.16</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09:48:40</t>
+          <t>09:39:42</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.01</v>
+        <v>2.2</v>
       </c>
       <c r="F62" t="n">
-        <v>5.91</v>
+        <v>5.99</v>
       </c>
       <c r="G62" t="n">
-        <v>57.7</v>
+        <v>46.5</v>
       </c>
       <c r="H62" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J62" t="n">
-        <v>51.83</v>
+        <v>61</v>
       </c>
       <c r="K62" t="n">
-        <v>-7.64</v>
+        <v>26.25</v>
       </c>
       <c r="L62" t="n">
-        <v>52.39</v>
+        <v>66.41</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09:49:31</t>
+          <t>09:40:44</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,13 +2683,13 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.39</v>
+        <v>2.62</v>
       </c>
       <c r="F63" t="n">
-        <v>5.7</v>
+        <v>5.66</v>
       </c>
       <c r="G63" t="n">
-        <v>49.8</v>
+        <v>60.5</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
@@ -2698,19 +2698,19 @@
         <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>61.01</v>
+        <v>165.07</v>
       </c>
       <c r="K63" t="n">
-        <v>131.12</v>
+        <v>64.48999999999999</v>
       </c>
       <c r="L63" t="n">
-        <v>144.62</v>
+        <v>177.22</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09:50:03</t>
+          <t>09:42:51</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>2.35</v>
+        <v>2.52</v>
       </c>
       <c r="F64" t="n">
-        <v>6.5</v>
+        <v>6.11</v>
       </c>
       <c r="G64" t="n">
-        <v>48</v>
+        <v>38.5</v>
       </c>
       <c r="H64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I64" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J64" t="n">
-        <v>20.84</v>
+        <v>-27.64</v>
       </c>
       <c r="K64" t="n">
-        <v>-22.1</v>
+        <v>118.91</v>
       </c>
       <c r="L64" t="n">
-        <v>30.38</v>
+        <v>122.08</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09:54:38</t>
+          <t>09:47:21</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2.37</v>
+        <v>2.68</v>
       </c>
       <c r="F65" t="n">
-        <v>5.14</v>
+        <v>5.64</v>
       </c>
       <c r="G65" t="n">
-        <v>59.4</v>
+        <v>36.4</v>
       </c>
       <c r="H65" t="n">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="J65" t="n">
-        <v>-81.28</v>
+        <v>-104.76</v>
       </c>
       <c r="K65" t="n">
-        <v>2.98</v>
+        <v>86.06</v>
       </c>
       <c r="L65" t="n">
-        <v>81.33</v>
+        <v>135.58</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09:56:35</t>
+          <t>09:49:02</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>3.29</v>
+        <v>2.46</v>
       </c>
       <c r="F66" t="n">
-        <v>5.76</v>
+        <v>6.36</v>
       </c>
       <c r="G66" t="n">
-        <v>60.5</v>
+        <v>40.8</v>
       </c>
       <c r="H66" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="I66" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J66" t="n">
-        <v>249.42</v>
+        <v>75.67</v>
       </c>
       <c r="K66" t="n">
-        <v>-91.54000000000001</v>
+        <v>-74.90000000000001</v>
       </c>
       <c r="L66" t="n">
-        <v>265.68</v>
+        <v>106.47</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09:58:06</t>
+          <t>09:51:33</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>2.51</v>
+        <v>2.72</v>
       </c>
       <c r="F67" t="n">
-        <v>6.17</v>
+        <v>5.5</v>
       </c>
       <c r="G67" t="n">
-        <v>48.2</v>
+        <v>75.3</v>
       </c>
       <c r="H67" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="J67" t="n">
-        <v>16.61</v>
+        <v>-97.42</v>
       </c>
       <c r="K67" t="n">
-        <v>10.52</v>
+        <v>-183.51</v>
       </c>
       <c r="L67" t="n">
-        <v>19.66</v>
+        <v>207.77</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10:03:05</t>
+          <t>09:56:34</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="F68" t="n">
-        <v>6.04</v>
+        <v>5.8</v>
       </c>
       <c r="G68" t="n">
-        <v>47.9</v>
+        <v>36.4</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="I68" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>4.41</v>
+        <v>-212.8</v>
       </c>
       <c r="K68" t="n">
-        <v>230.63</v>
+        <v>201.89</v>
       </c>
       <c r="L68" t="n">
-        <v>230.67</v>
+        <v>293.33</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10:05:34</t>
+          <t>09:57:42</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>2.81</v>
+        <v>2.33</v>
       </c>
       <c r="F69" t="n">
-        <v>5.99</v>
+        <v>5.62</v>
       </c>
       <c r="G69" t="n">
-        <v>45.1</v>
+        <v>51</v>
       </c>
       <c r="H69" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="I69" t="n">
         <v>30</v>
       </c>
       <c r="J69" t="n">
-        <v>68.73999999999999</v>
+        <v>207.24</v>
       </c>
       <c r="K69" t="n">
-        <v>-29.06</v>
+        <v>-39.83</v>
       </c>
       <c r="L69" t="n">
-        <v>74.63</v>
+        <v>211.03</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>10:07:06</t>
+          <t>09:59:38</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="F70" t="n">
-        <v>6.01</v>
+        <v>6</v>
       </c>
       <c r="G70" t="n">
-        <v>61.7</v>
+        <v>48.9</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="I70" t="n">
         <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>2.48</v>
+        <v>153.71</v>
       </c>
       <c r="K70" t="n">
-        <v>202.78</v>
+        <v>89.52</v>
       </c>
       <c r="L70" t="n">
-        <v>202.79</v>
+        <v>177.88</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>10:09:52</t>
+          <t>10:04:54</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.61</v>
+        <v>2.14</v>
       </c>
       <c r="F71" t="n">
-        <v>5.95</v>
+        <v>6.31</v>
       </c>
       <c r="G71" t="n">
-        <v>40.1</v>
+        <v>58.4</v>
       </c>
       <c r="H71" t="n">
-        <v>16.7</v>
+        <v>3.9</v>
       </c>
       <c r="I71" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J71" t="n">
-        <v>525.52</v>
+        <v>394.01</v>
       </c>
       <c r="K71" t="n">
-        <v>-64.78</v>
+        <v>-169.12</v>
       </c>
       <c r="L71" t="n">
-        <v>529.5</v>
+        <v>428.77</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10:11:24</t>
+          <t>10:06:36</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>2.68</v>
+        <v>2.43</v>
       </c>
       <c r="F72" t="n">
-        <v>6.24</v>
+        <v>6.62</v>
       </c>
       <c r="G72" t="n">
-        <v>42.1</v>
+        <v>42.2</v>
       </c>
       <c r="H72" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="I72" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J72" t="n">
-        <v>-75.95999999999999</v>
+        <v>48.42</v>
       </c>
       <c r="K72" t="n">
-        <v>15.53</v>
+        <v>187.26</v>
       </c>
       <c r="L72" t="n">
-        <v>77.54000000000001</v>
+        <v>193.42</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10:13:17</t>
+          <t>10:07:58</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.58</v>
+        <v>2.38</v>
       </c>
       <c r="F73" t="n">
-        <v>6.51</v>
+        <v>5.84</v>
       </c>
       <c r="G73" t="n">
-        <v>43.7</v>
+        <v>52.6</v>
       </c>
       <c r="H73" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="I73" t="n">
         <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>-11.7</v>
+        <v>-111.62</v>
       </c>
       <c r="K73" t="n">
-        <v>39.93</v>
+        <v>-316.3</v>
       </c>
       <c r="L73" t="n">
-        <v>41.6</v>
+        <v>335.42</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10:24:01</t>
+          <t>10:15:37</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>2.25</v>
+        <v>2.65</v>
       </c>
       <c r="F74" t="n">
-        <v>6.87</v>
+        <v>5.77</v>
       </c>
       <c r="G74" t="n">
-        <v>42.4</v>
+        <v>33.1</v>
       </c>
       <c r="H74" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="I74" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J74" t="n">
-        <v>8.880000000000001</v>
+        <v>46.34</v>
       </c>
       <c r="K74" t="n">
-        <v>42.02</v>
+        <v>-18.8</v>
       </c>
       <c r="L74" t="n">
-        <v>42.95</v>
+        <v>50.01</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10:24:53</t>
+          <t>10:17:28</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="F75" t="n">
-        <v>5.36</v>
+        <v>6.2</v>
       </c>
       <c r="G75" t="n">
-        <v>45.4</v>
+        <v>50.9</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J75" t="n">
-        <v>-0.86</v>
+        <v>-51.11</v>
       </c>
       <c r="K75" t="n">
-        <v>-0.8</v>
+        <v>-125.82</v>
       </c>
       <c r="L75" t="n">
-        <v>1.17</v>
+        <v>135.81</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10:27:17</t>
+          <t>10:18:59</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>2.57</v>
+        <v>2.66</v>
       </c>
       <c r="F76" t="n">
-        <v>6.22</v>
+        <v>6.05</v>
       </c>
       <c r="G76" t="n">
-        <v>50.9</v>
+        <v>40.5</v>
       </c>
       <c r="H76" t="n">
-        <v>1.5</v>
+        <v>3.9</v>
       </c>
       <c r="I76" t="n">
         <v>28</v>
       </c>
       <c r="J76" t="n">
-        <v>-13.98</v>
+        <v>4.65</v>
       </c>
       <c r="K76" t="n">
-        <v>-2.3</v>
+        <v>229.67</v>
       </c>
       <c r="L76" t="n">
-        <v>14.17</v>
+        <v>229.72</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10:31:03</t>
+          <t>10:23:27</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="F77" t="n">
-        <v>6.14</v>
+        <v>5.39</v>
       </c>
       <c r="G77" t="n">
-        <v>55.9</v>
+        <v>50.1</v>
       </c>
       <c r="H77" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J77" t="n">
-        <v>34.19</v>
+        <v>-205.5</v>
       </c>
       <c r="K77" t="n">
-        <v>4.89</v>
+        <v>-162.21</v>
       </c>
       <c r="L77" t="n">
-        <v>34.53</v>
+        <v>261.8</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>10:31:59</t>
+          <t>10:24:41</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2.37</v>
+        <v>2.91</v>
       </c>
       <c r="F78" t="n">
-        <v>6.52</v>
+        <v>5.16</v>
       </c>
       <c r="G78" t="n">
-        <v>47.5</v>
+        <v>42.6</v>
       </c>
       <c r="H78" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="I78" t="n">
         <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>-1.35</v>
+        <v>285.82</v>
       </c>
       <c r="K78" t="n">
-        <v>-29.63</v>
+        <v>-145.88</v>
       </c>
       <c r="L78" t="n">
-        <v>29.66</v>
+        <v>320.89</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>10:33:28</t>
+          <t>10:26:43</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.28</v>
+        <v>2.87</v>
       </c>
       <c r="F79" t="n">
-        <v>6.36</v>
+        <v>6.23</v>
       </c>
       <c r="G79" t="n">
-        <v>43.9</v>
+        <v>41.9</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>87.20999999999999</v>
+        <v>27.09</v>
       </c>
       <c r="K79" t="n">
-        <v>-36.75</v>
+        <v>94.34</v>
       </c>
       <c r="L79" t="n">
-        <v>94.64</v>
+        <v>98.15000000000001</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>10:38:01</t>
+          <t>10:31:13</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="F80" t="n">
-        <v>5.9</v>
+        <v>5.61</v>
       </c>
       <c r="G80" t="n">
-        <v>38.6</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I80" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="J80" t="n">
-        <v>27.81</v>
+        <v>170.26</v>
       </c>
       <c r="K80" t="n">
-        <v>-9.449999999999999</v>
+        <v>25.26</v>
       </c>
       <c r="L80" t="n">
-        <v>29.37</v>
+        <v>172.13</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10:39:40</t>
+          <t>10:33:32</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2.32</v>
+        <v>2.64</v>
       </c>
       <c r="F81" t="n">
-        <v>5.72</v>
+        <v>5.92</v>
       </c>
       <c r="G81" t="n">
-        <v>46.9</v>
+        <v>48.4</v>
       </c>
       <c r="H81" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J81" t="n">
-        <v>34.15</v>
+        <v>98.98999999999999</v>
       </c>
       <c r="K81" t="n">
-        <v>-3.48</v>
+        <v>-148.58</v>
       </c>
       <c r="L81" t="n">
-        <v>34.32</v>
+        <v>178.54</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10:41:49</t>
+          <t>10:34:39</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.34</v>
+        <v>2.13</v>
       </c>
       <c r="F82" t="n">
-        <v>5.71</v>
+        <v>5.66</v>
       </c>
       <c r="G82" t="n">
-        <v>36.9</v>
+        <v>53.2</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="I82" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J82" t="n">
-        <v>87.17</v>
+        <v>-13.37</v>
       </c>
       <c r="K82" t="n">
-        <v>25.79</v>
+        <v>60.78</v>
       </c>
       <c r="L82" t="n">
-        <v>90.90000000000001</v>
+        <v>62.24</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10:45:13</t>
+          <t>10:38:35</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="F83" t="n">
-        <v>6.91</v>
+        <v>6.08</v>
       </c>
       <c r="G83" t="n">
-        <v>50.9</v>
+        <v>53.4</v>
       </c>
       <c r="H83" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="I83" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J83" t="n">
-        <v>369.16</v>
+        <v>-87.48999999999999</v>
       </c>
       <c r="K83" t="n">
-        <v>57.1</v>
+        <v>-213.67</v>
       </c>
       <c r="L83" t="n">
-        <v>373.55</v>
+        <v>230.89</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10:46:55</t>
+          <t>10:40:51</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2.78</v>
+        <v>2.68</v>
       </c>
       <c r="F84" t="n">
-        <v>6.35</v>
+        <v>5.65</v>
       </c>
       <c r="G84" t="n">
-        <v>55.8</v>
+        <v>53.6</v>
       </c>
       <c r="H84" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="I84" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>-268.1</v>
+        <v>-248.94</v>
       </c>
       <c r="K84" t="n">
-        <v>31.03</v>
+        <v>-39.51</v>
       </c>
       <c r="L84" t="n">
-        <v>269.89</v>
+        <v>252.06</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10:49:01</t>
+          <t>10:42:37</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>2.6</v>
+        <v>2.74</v>
       </c>
       <c r="F85" t="n">
-        <v>5.98</v>
+        <v>5.34</v>
       </c>
       <c r="G85" t="n">
-        <v>47.5</v>
+        <v>58.8</v>
       </c>
       <c r="H85" t="n">
-        <v>0.4</v>
+        <v>2.8</v>
       </c>
       <c r="I85" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J85" t="n">
-        <v>24.73</v>
+        <v>-136.16</v>
       </c>
       <c r="K85" t="n">
-        <v>-20.69</v>
+        <v>-172.2</v>
       </c>
       <c r="L85" t="n">
-        <v>32.24</v>
+        <v>219.53</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10:53:26</t>
+          <t>10:47:39</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>2.8</v>
+        <v>2.48</v>
       </c>
       <c r="F86" t="n">
-        <v>6.02</v>
+        <v>5.58</v>
       </c>
       <c r="G86" t="n">
-        <v>53</v>
+        <v>49.4</v>
       </c>
       <c r="H86" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J86" t="n">
-        <v>-39.11</v>
+        <v>44.83</v>
       </c>
       <c r="K86" t="n">
-        <v>784.29</v>
+        <v>79.56999999999999</v>
       </c>
       <c r="L86" t="n">
-        <v>785.26</v>
+        <v>91.33</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10:54:52</t>
+          <t>10:48:56</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2.49</v>
+        <v>2.25</v>
       </c>
       <c r="F87" t="n">
-        <v>5.63</v>
+        <v>6.18</v>
       </c>
       <c r="G87" t="n">
-        <v>41.7</v>
+        <v>62.5</v>
       </c>
       <c r="H87" t="n">
         <v>0</v>
       </c>
       <c r="I87" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J87" t="n">
-        <v>11.19</v>
+        <v>209.1</v>
       </c>
       <c r="K87" t="n">
-        <v>51.92</v>
+        <v>-262.77</v>
       </c>
       <c r="L87" t="n">
-        <v>53.11</v>
+        <v>335.81</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10:56:54</t>
+          <t>10:49:47</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>2.56</v>
+        <v>2.49</v>
       </c>
       <c r="F88" t="n">
-        <v>5.43</v>
+        <v>6.24</v>
       </c>
       <c r="G88" t="n">
-        <v>47.7</v>
+        <v>46.3</v>
       </c>
       <c r="H88" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J88" t="n">
-        <v>87.08</v>
+        <v>45.69</v>
       </c>
       <c r="K88" t="n">
-        <v>58.69</v>
+        <v>61.42</v>
       </c>
       <c r="L88" t="n">
-        <v>105.01</v>
+        <v>76.55</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-10-01.xlsx
+++ b/output/2025-10-01.xlsx
@@ -640,13 +640,13 @@
         <v>29</v>
       </c>
       <c r="J14" t="n">
-        <v>37.42</v>
+        <v>45.24</v>
       </c>
       <c r="K14" t="n">
-        <v>30</v>
+        <v>36.26</v>
       </c>
       <c r="L14" t="n">
-        <v>47.96</v>
+        <v>57.98</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>-76.66</v>
+        <v>-53.66</v>
       </c>
       <c r="K15" t="n">
-        <v>-84.40000000000001</v>
+        <v>-59.08</v>
       </c>
       <c r="L15" t="n">
-        <v>114.02</v>
+        <v>79.81</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>31</v>
       </c>
       <c r="J16" t="n">
-        <v>-14.13</v>
+        <v>-8.24</v>
       </c>
       <c r="K16" t="n">
-        <v>86.14</v>
+        <v>50.19</v>
       </c>
       <c r="L16" t="n">
-        <v>87.29000000000001</v>
+        <v>50.86</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>31</v>
       </c>
       <c r="J17" t="n">
-        <v>9.359999999999999</v>
+        <v>15.42</v>
       </c>
       <c r="K17" t="n">
-        <v>-22.64</v>
+        <v>-37.29</v>
       </c>
       <c r="L17" t="n">
-        <v>24.5</v>
+        <v>40.35</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>30</v>
       </c>
       <c r="J18" t="n">
-        <v>-128.75</v>
+        <v>-72.59999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>-229.87</v>
+        <v>-129.62</v>
       </c>
       <c r="L18" t="n">
-        <v>263.47</v>
+        <v>148.57</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>28</v>
       </c>
       <c r="J19" t="n">
-        <v>4.68</v>
+        <v>3.46</v>
       </c>
       <c r="K19" t="n">
-        <v>-121.35</v>
+        <v>-89.76000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>121.44</v>
+        <v>89.83</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>-205.73</v>
+        <v>-177.74</v>
       </c>
       <c r="K20" t="n">
-        <v>-29.51</v>
+        <v>-25.5</v>
       </c>
       <c r="L20" t="n">
-        <v>207.84</v>
+        <v>179.56</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>29</v>
       </c>
       <c r="J21" t="n">
-        <v>173.95</v>
+        <v>133.35</v>
       </c>
       <c r="K21" t="n">
-        <v>19.08</v>
+        <v>14.63</v>
       </c>
       <c r="L21" t="n">
-        <v>174.99</v>
+        <v>134.15</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>31</v>
       </c>
       <c r="J22" t="n">
-        <v>-209.23</v>
+        <v>-132.83</v>
       </c>
       <c r="K22" t="n">
-        <v>-95.43000000000001</v>
+        <v>-60.58</v>
       </c>
       <c r="L22" t="n">
-        <v>229.97</v>
+        <v>145.99</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>25</v>
       </c>
       <c r="J23" t="n">
-        <v>83.45999999999999</v>
+        <v>95.98999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>132.62</v>
+        <v>152.54</v>
       </c>
       <c r="L23" t="n">
-        <v>156.69</v>
+        <v>180.23</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>168.48</v>
+        <v>190.42</v>
       </c>
       <c r="K24" t="n">
-        <v>-22.57</v>
+        <v>-25.51</v>
       </c>
       <c r="L24" t="n">
-        <v>169.99</v>
+        <v>192.12</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>28</v>
       </c>
       <c r="J25" t="n">
-        <v>3.78</v>
+        <v>3.21</v>
       </c>
       <c r="K25" t="n">
-        <v>-264.62</v>
+        <v>-224.27</v>
       </c>
       <c r="L25" t="n">
-        <v>264.65</v>
+        <v>224.29</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>28</v>
       </c>
       <c r="J26" t="n">
-        <v>-628.67</v>
+        <v>-543.59</v>
       </c>
       <c r="K26" t="n">
-        <v>25.83</v>
+        <v>22.33</v>
       </c>
       <c r="L26" t="n">
-        <v>629.2</v>
+        <v>544.05</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>28</v>
       </c>
       <c r="J27" t="n">
-        <v>-297.08</v>
+        <v>-283.3</v>
       </c>
       <c r="K27" t="n">
-        <v>-268.94</v>
+        <v>-256.47</v>
       </c>
       <c r="L27" t="n">
-        <v>400.73</v>
+        <v>382.14</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>29</v>
       </c>
       <c r="J28" t="n">
-        <v>56.74</v>
+        <v>87.63</v>
       </c>
       <c r="K28" t="n">
-        <v>107.9</v>
+        <v>166.64</v>
       </c>
       <c r="L28" t="n">
-        <v>121.91</v>
+        <v>188.28</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>28</v>
       </c>
       <c r="J29" t="n">
-        <v>-27.86</v>
+        <v>-27</v>
       </c>
       <c r="K29" t="n">
-        <v>-36.02</v>
+        <v>-34.9</v>
       </c>
       <c r="L29" t="n">
-        <v>45.54</v>
+        <v>44.12</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>31</v>
       </c>
       <c r="J30" t="n">
-        <v>44.74</v>
+        <v>31.04</v>
       </c>
       <c r="K30" t="n">
-        <v>-40.99</v>
+        <v>-28.44</v>
       </c>
       <c r="L30" t="n">
-        <v>60.68</v>
+        <v>42.1</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>29</v>
       </c>
       <c r="J31" t="n">
-        <v>53.84</v>
+        <v>41.01</v>
       </c>
       <c r="K31" t="n">
-        <v>69.75</v>
+        <v>53.13</v>
       </c>
       <c r="L31" t="n">
-        <v>88.11</v>
+        <v>67.12</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>-87.88</v>
+        <v>-72.17</v>
       </c>
       <c r="K32" t="n">
-        <v>-87.8</v>
+        <v>-72.09999999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>124.22</v>
+        <v>102.01</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>26</v>
       </c>
       <c r="J33" t="n">
-        <v>-91.76000000000001</v>
+        <v>-86.81999999999999</v>
       </c>
       <c r="K33" t="n">
-        <v>-4.83</v>
+        <v>-4.57</v>
       </c>
       <c r="L33" t="n">
-        <v>91.89</v>
+        <v>86.94</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>26</v>
       </c>
       <c r="J34" t="n">
-        <v>-138.25</v>
+        <v>-125.4</v>
       </c>
       <c r="K34" t="n">
-        <v>-15.96</v>
+        <v>-14.48</v>
       </c>
       <c r="L34" t="n">
-        <v>139.17</v>
+        <v>126.24</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>26</v>
       </c>
       <c r="J35" t="n">
-        <v>283.15</v>
+        <v>205.52</v>
       </c>
       <c r="K35" t="n">
-        <v>179.77</v>
+        <v>130.49</v>
       </c>
       <c r="L35" t="n">
-        <v>335.4</v>
+        <v>243.45</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>25</v>
       </c>
       <c r="J36" t="n">
-        <v>-191.9</v>
+        <v>-153.47</v>
       </c>
       <c r="K36" t="n">
-        <v>285.95</v>
+        <v>228.68</v>
       </c>
       <c r="L36" t="n">
-        <v>344.38</v>
+        <v>275.4</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>28</v>
       </c>
       <c r="J37" t="n">
-        <v>59.59</v>
+        <v>80.09</v>
       </c>
       <c r="K37" t="n">
-        <v>23.01</v>
+        <v>30.93</v>
       </c>
       <c r="L37" t="n">
-        <v>63.88</v>
+        <v>85.86</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>25</v>
       </c>
       <c r="J38" t="n">
-        <v>304.61</v>
+        <v>298.59</v>
       </c>
       <c r="K38" t="n">
-        <v>325.53</v>
+        <v>319.1</v>
       </c>
       <c r="L38" t="n">
-        <v>445.82</v>
+        <v>437.02</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>30</v>
       </c>
       <c r="J39" t="n">
-        <v>-39.64</v>
+        <v>-61.72</v>
       </c>
       <c r="K39" t="n">
-        <v>-80.76000000000001</v>
+        <v>-125.74</v>
       </c>
       <c r="L39" t="n">
-        <v>89.97</v>
+        <v>140.07</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>29</v>
       </c>
       <c r="J40" t="n">
-        <v>411.41</v>
+        <v>300.06</v>
       </c>
       <c r="K40" t="n">
-        <v>12.69</v>
+        <v>9.26</v>
       </c>
       <c r="L40" t="n">
-        <v>411.61</v>
+        <v>300.2</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>26</v>
       </c>
       <c r="J41" t="n">
-        <v>14.92</v>
+        <v>22.03</v>
       </c>
       <c r="K41" t="n">
-        <v>-167.86</v>
+        <v>-247.89</v>
       </c>
       <c r="L41" t="n">
-        <v>168.53</v>
+        <v>248.87</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>27</v>
       </c>
       <c r="J42" t="n">
-        <v>-264.7</v>
+        <v>-231.25</v>
       </c>
       <c r="K42" t="n">
-        <v>-689.86</v>
+        <v>-602.6799999999999</v>
       </c>
       <c r="L42" t="n">
-        <v>738.9</v>
+        <v>645.52</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>30</v>
       </c>
       <c r="J43" t="n">
-        <v>240.98</v>
+        <v>236.15</v>
       </c>
       <c r="K43" t="n">
-        <v>70.45999999999999</v>
+        <v>69.05</v>
       </c>
       <c r="L43" t="n">
-        <v>251.07</v>
+        <v>246.04</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>30</v>
       </c>
       <c r="J44" t="n">
-        <v>-46.27</v>
+        <v>-36.98</v>
       </c>
       <c r="K44" t="n">
-        <v>-63.04</v>
+        <v>-50.38</v>
       </c>
       <c r="L44" t="n">
-        <v>78.2</v>
+        <v>62.5</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>31</v>
       </c>
       <c r="J45" t="n">
-        <v>23.29</v>
+        <v>25.58</v>
       </c>
       <c r="K45" t="n">
-        <v>-9.27</v>
+        <v>-10.18</v>
       </c>
       <c r="L45" t="n">
-        <v>25.07</v>
+        <v>27.53</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>31</v>
       </c>
       <c r="J46" t="n">
-        <v>-72.45</v>
+        <v>-40.44</v>
       </c>
       <c r="K46" t="n">
-        <v>-79.08</v>
+        <v>-44.14</v>
       </c>
       <c r="L46" t="n">
-        <v>107.25</v>
+        <v>59.86</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>-88.86</v>
+        <v>-81.39</v>
       </c>
       <c r="K47" t="n">
-        <v>46.37</v>
+        <v>42.47</v>
       </c>
       <c r="L47" t="n">
-        <v>100.23</v>
+        <v>91.8</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>29</v>
       </c>
       <c r="J48" t="n">
-        <v>95.01000000000001</v>
+        <v>64.02</v>
       </c>
       <c r="K48" t="n">
-        <v>-140.77</v>
+        <v>-94.84999999999999</v>
       </c>
       <c r="L48" t="n">
-        <v>169.83</v>
+        <v>114.44</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>29</v>
       </c>
       <c r="J49" t="n">
-        <v>-11.26</v>
+        <v>-7.64</v>
       </c>
       <c r="K49" t="n">
-        <v>-172.46</v>
+        <v>-117.04</v>
       </c>
       <c r="L49" t="n">
-        <v>172.82</v>
+        <v>117.29</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>127.4</v>
+        <v>131.71</v>
       </c>
       <c r="K50" t="n">
-        <v>-71.81</v>
+        <v>-74.23999999999999</v>
       </c>
       <c r="L50" t="n">
-        <v>146.24</v>
+        <v>151.2</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>31</v>
       </c>
       <c r="J51" t="n">
-        <v>-43.69</v>
+        <v>-35.87</v>
       </c>
       <c r="K51" t="n">
-        <v>-146.31</v>
+        <v>-120.12</v>
       </c>
       <c r="L51" t="n">
-        <v>152.69</v>
+        <v>125.36</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>29</v>
       </c>
       <c r="J52" t="n">
-        <v>117.37</v>
+        <v>105.2</v>
       </c>
       <c r="K52" t="n">
-        <v>-61.36</v>
+        <v>-55</v>
       </c>
       <c r="L52" t="n">
-        <v>132.44</v>
+        <v>118.71</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>27</v>
       </c>
       <c r="J53" t="n">
-        <v>-68.62</v>
+        <v>-84.47</v>
       </c>
       <c r="K53" t="n">
-        <v>-86.81</v>
+        <v>-106.85</v>
       </c>
       <c r="L53" t="n">
-        <v>110.66</v>
+        <v>136.2</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>17.66</v>
+        <v>17.2</v>
       </c>
       <c r="K54" t="n">
-        <v>-350.07</v>
+        <v>-340.95</v>
       </c>
       <c r="L54" t="n">
-        <v>350.52</v>
+        <v>341.39</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>28</v>
       </c>
       <c r="J55" t="n">
-        <v>31.76</v>
+        <v>41.29</v>
       </c>
       <c r="K55" t="n">
-        <v>-103.07</v>
+        <v>-134.02</v>
       </c>
       <c r="L55" t="n">
-        <v>107.85</v>
+        <v>140.24</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>28</v>
       </c>
       <c r="J56" t="n">
-        <v>376.74</v>
+        <v>369.24</v>
       </c>
       <c r="K56" t="n">
-        <v>609.8</v>
+        <v>597.67</v>
       </c>
       <c r="L56" t="n">
-        <v>716.79</v>
+        <v>702.53</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>30</v>
       </c>
       <c r="J57" t="n">
-        <v>-147.02</v>
+        <v>-181.55</v>
       </c>
       <c r="K57" t="n">
-        <v>23.31</v>
+        <v>28.79</v>
       </c>
       <c r="L57" t="n">
-        <v>148.86</v>
+        <v>183.82</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>371.36</v>
+        <v>400.81</v>
       </c>
       <c r="K58" t="n">
-        <v>-200.31</v>
+        <v>-216.2</v>
       </c>
       <c r="L58" t="n">
-        <v>421.94</v>
+        <v>455.4</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>-34.39</v>
+        <v>-24.62</v>
       </c>
       <c r="K59" t="n">
-        <v>181.29</v>
+        <v>129.81</v>
       </c>
       <c r="L59" t="n">
-        <v>184.52</v>
+        <v>132.13</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>31</v>
       </c>
       <c r="J60" t="n">
-        <v>-47.99</v>
+        <v>-29.8</v>
       </c>
       <c r="K60" t="n">
-        <v>-51.8</v>
+        <v>-32.17</v>
       </c>
       <c r="L60" t="n">
-        <v>70.61</v>
+        <v>43.85</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>29</v>
       </c>
       <c r="J61" t="n">
-        <v>60.55</v>
+        <v>47.05</v>
       </c>
       <c r="K61" t="n">
-        <v>-21.23</v>
+        <v>-16.5</v>
       </c>
       <c r="L61" t="n">
-        <v>64.16</v>
+        <v>49.86</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>29</v>
       </c>
       <c r="J62" t="n">
-        <v>61</v>
+        <v>56.62</v>
       </c>
       <c r="K62" t="n">
-        <v>26.25</v>
+        <v>24.37</v>
       </c>
       <c r="L62" t="n">
-        <v>66.41</v>
+        <v>61.64</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>165.07</v>
+        <v>141.02</v>
       </c>
       <c r="K63" t="n">
-        <v>64.48999999999999</v>
+        <v>55.09</v>
       </c>
       <c r="L63" t="n">
-        <v>177.22</v>
+        <v>151.4</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>31</v>
       </c>
       <c r="J64" t="n">
-        <v>-27.64</v>
+        <v>-19.88</v>
       </c>
       <c r="K64" t="n">
-        <v>118.91</v>
+        <v>85.5</v>
       </c>
       <c r="L64" t="n">
-        <v>122.08</v>
+        <v>87.78</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>28</v>
       </c>
       <c r="J65" t="n">
-        <v>-104.76</v>
+        <v>-111.95</v>
       </c>
       <c r="K65" t="n">
-        <v>86.06</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="L65" t="n">
-        <v>135.58</v>
+        <v>144.88</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>28</v>
       </c>
       <c r="J66" t="n">
-        <v>75.67</v>
+        <v>84.19</v>
       </c>
       <c r="K66" t="n">
-        <v>-74.90000000000001</v>
+        <v>-83.34</v>
       </c>
       <c r="L66" t="n">
-        <v>106.47</v>
+        <v>118.47</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>28</v>
       </c>
       <c r="J67" t="n">
-        <v>-97.42</v>
+        <v>-88.98</v>
       </c>
       <c r="K67" t="n">
-        <v>-183.51</v>
+        <v>-167.6</v>
       </c>
       <c r="L67" t="n">
-        <v>207.77</v>
+        <v>189.75</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>-212.8</v>
+        <v>-193.92</v>
       </c>
       <c r="K68" t="n">
-        <v>201.89</v>
+        <v>183.97</v>
       </c>
       <c r="L68" t="n">
-        <v>293.33</v>
+        <v>267.3</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>30</v>
       </c>
       <c r="J69" t="n">
-        <v>207.24</v>
+        <v>180.15</v>
       </c>
       <c r="K69" t="n">
-        <v>-39.83</v>
+        <v>-34.63</v>
       </c>
       <c r="L69" t="n">
-        <v>211.03</v>
+        <v>183.45</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>153.71</v>
+        <v>173.12</v>
       </c>
       <c r="K70" t="n">
-        <v>89.52</v>
+        <v>100.83</v>
       </c>
       <c r="L70" t="n">
-        <v>177.88</v>
+        <v>200.34</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>28</v>
       </c>
       <c r="J71" t="n">
-        <v>394.01</v>
+        <v>353.09</v>
       </c>
       <c r="K71" t="n">
-        <v>-169.12</v>
+        <v>-151.56</v>
       </c>
       <c r="L71" t="n">
-        <v>428.77</v>
+        <v>384.24</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>26</v>
       </c>
       <c r="J72" t="n">
-        <v>48.42</v>
+        <v>69.68000000000001</v>
       </c>
       <c r="K72" t="n">
-        <v>187.26</v>
+        <v>269.5</v>
       </c>
       <c r="L72" t="n">
-        <v>193.42</v>
+        <v>278.36</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>-111.62</v>
+        <v>-124.54</v>
       </c>
       <c r="K73" t="n">
-        <v>-316.3</v>
+        <v>-352.91</v>
       </c>
       <c r="L73" t="n">
-        <v>335.42</v>
+        <v>374.24</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>30</v>
       </c>
       <c r="J74" t="n">
-        <v>46.34</v>
+        <v>46.21</v>
       </c>
       <c r="K74" t="n">
-        <v>-18.8</v>
+        <v>-18.75</v>
       </c>
       <c r="L74" t="n">
-        <v>50.01</v>
+        <v>49.87</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>30</v>
       </c>
       <c r="J75" t="n">
-        <v>-51.11</v>
+        <v>-34.13</v>
       </c>
       <c r="K75" t="n">
-        <v>-125.82</v>
+        <v>-84.03</v>
       </c>
       <c r="L75" t="n">
-        <v>135.81</v>
+        <v>90.7</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>28</v>
       </c>
       <c r="J76" t="n">
-        <v>4.65</v>
+        <v>3.02</v>
       </c>
       <c r="K76" t="n">
-        <v>229.67</v>
+        <v>148.79</v>
       </c>
       <c r="L76" t="n">
-        <v>229.72</v>
+        <v>148.82</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>27</v>
       </c>
       <c r="J77" t="n">
-        <v>-205.5</v>
+        <v>-150.06</v>
       </c>
       <c r="K77" t="n">
-        <v>-162.21</v>
+        <v>-118.45</v>
       </c>
       <c r="L77" t="n">
-        <v>261.8</v>
+        <v>191.17</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>285.82</v>
+        <v>216.8</v>
       </c>
       <c r="K78" t="n">
-        <v>-145.88</v>
+        <v>-110.65</v>
       </c>
       <c r="L78" t="n">
-        <v>320.89</v>
+        <v>243.41</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>27.09</v>
+        <v>30.48</v>
       </c>
       <c r="K79" t="n">
-        <v>94.34</v>
+        <v>106.15</v>
       </c>
       <c r="L79" t="n">
-        <v>98.15000000000001</v>
+        <v>110.44</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>26</v>
       </c>
       <c r="J80" t="n">
-        <v>170.26</v>
+        <v>165.38</v>
       </c>
       <c r="K80" t="n">
-        <v>25.26</v>
+        <v>24.54</v>
       </c>
       <c r="L80" t="n">
-        <v>172.13</v>
+        <v>167.19</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>29</v>
       </c>
       <c r="J81" t="n">
-        <v>98.98999999999999</v>
+        <v>88.3</v>
       </c>
       <c r="K81" t="n">
-        <v>-148.58</v>
+        <v>-132.53</v>
       </c>
       <c r="L81" t="n">
-        <v>178.54</v>
+        <v>159.25</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>31</v>
       </c>
       <c r="J82" t="n">
-        <v>-13.37</v>
+        <v>-14.34</v>
       </c>
       <c r="K82" t="n">
-        <v>60.78</v>
+        <v>65.2</v>
       </c>
       <c r="L82" t="n">
-        <v>62.24</v>
+        <v>66.76000000000001</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>31</v>
       </c>
       <c r="J83" t="n">
-        <v>-87.48999999999999</v>
+        <v>-77.22</v>
       </c>
       <c r="K83" t="n">
-        <v>-213.67</v>
+        <v>-188.6</v>
       </c>
       <c r="L83" t="n">
-        <v>230.89</v>
+        <v>203.8</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>-248.94</v>
+        <v>-267.11</v>
       </c>
       <c r="K84" t="n">
-        <v>-39.51</v>
+        <v>-42.39</v>
       </c>
       <c r="L84" t="n">
-        <v>252.06</v>
+        <v>270.46</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>27</v>
       </c>
       <c r="J85" t="n">
-        <v>-136.16</v>
+        <v>-150.12</v>
       </c>
       <c r="K85" t="n">
-        <v>-172.2</v>
+        <v>-189.86</v>
       </c>
       <c r="L85" t="n">
-        <v>219.53</v>
+        <v>242.03</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>29</v>
       </c>
       <c r="J86" t="n">
-        <v>44.83</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="K86" t="n">
-        <v>79.56999999999999</v>
+        <v>152.04</v>
       </c>
       <c r="L86" t="n">
-        <v>91.33</v>
+        <v>174.5</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>26</v>
       </c>
       <c r="J87" t="n">
-        <v>209.1</v>
+        <v>224.21</v>
       </c>
       <c r="K87" t="n">
-        <v>-262.77</v>
+        <v>-281.76</v>
       </c>
       <c r="L87" t="n">
-        <v>335.81</v>
+        <v>360.08</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>31</v>
       </c>
       <c r="J88" t="n">
-        <v>45.69</v>
+        <v>87.11</v>
       </c>
       <c r="K88" t="n">
-        <v>61.42</v>
+        <v>117.09</v>
       </c>
       <c r="L88" t="n">
-        <v>76.55</v>
+        <v>145.94</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-10-01.xlsx
+++ b/output/2025-10-01.xlsx
@@ -640,13 +640,13 @@
         <v>29</v>
       </c>
       <c r="J14" t="n">
-        <v>45.24</v>
+        <v>46.44</v>
       </c>
       <c r="K14" t="n">
-        <v>36.26</v>
+        <v>37.23</v>
       </c>
       <c r="L14" t="n">
-        <v>57.98</v>
+        <v>59.52</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>-53.66</v>
+        <v>-50.69</v>
       </c>
       <c r="K15" t="n">
-        <v>-59.08</v>
+        <v>-55.8</v>
       </c>
       <c r="L15" t="n">
-        <v>79.81</v>
+        <v>75.39</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>31</v>
       </c>
       <c r="J16" t="n">
-        <v>-8.24</v>
+        <v>-10.44</v>
       </c>
       <c r="K16" t="n">
-        <v>50.19</v>
+        <v>63.63</v>
       </c>
       <c r="L16" t="n">
-        <v>50.86</v>
+        <v>64.48</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>31</v>
       </c>
       <c r="J17" t="n">
-        <v>15.42</v>
+        <v>17.49</v>
       </c>
       <c r="K17" t="n">
-        <v>-37.29</v>
+        <v>-42.3</v>
       </c>
       <c r="L17" t="n">
-        <v>40.35</v>
+        <v>45.77</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>30</v>
       </c>
       <c r="J18" t="n">
-        <v>-72.59999999999999</v>
+        <v>-76.17</v>
       </c>
       <c r="K18" t="n">
-        <v>-129.62</v>
+        <v>-136</v>
       </c>
       <c r="L18" t="n">
-        <v>148.57</v>
+        <v>155.88</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>28</v>
       </c>
       <c r="J19" t="n">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
       <c r="K19" t="n">
-        <v>-89.76000000000001</v>
+        <v>-89.48</v>
       </c>
       <c r="L19" t="n">
-        <v>89.83</v>
+        <v>89.54000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>-177.74</v>
+        <v>-127.01</v>
       </c>
       <c r="K20" t="n">
-        <v>-25.5</v>
+        <v>-18.22</v>
       </c>
       <c r="L20" t="n">
-        <v>179.56</v>
+        <v>128.31</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>29</v>
       </c>
       <c r="J21" t="n">
-        <v>133.35</v>
+        <v>119.42</v>
       </c>
       <c r="K21" t="n">
-        <v>14.63</v>
+        <v>13.1</v>
       </c>
       <c r="L21" t="n">
-        <v>134.15</v>
+        <v>120.14</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>31</v>
       </c>
       <c r="J22" t="n">
-        <v>-132.83</v>
+        <v>-136.47</v>
       </c>
       <c r="K22" t="n">
-        <v>-60.58</v>
+        <v>-62.24</v>
       </c>
       <c r="L22" t="n">
-        <v>145.99</v>
+        <v>149.99</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>25</v>
       </c>
       <c r="J23" t="n">
-        <v>95.98999999999999</v>
+        <v>64.19</v>
       </c>
       <c r="K23" t="n">
-        <v>152.54</v>
+        <v>102</v>
       </c>
       <c r="L23" t="n">
-        <v>180.23</v>
+        <v>120.52</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>190.42</v>
+        <v>120.65</v>
       </c>
       <c r="K24" t="n">
-        <v>-25.51</v>
+        <v>-16.16</v>
       </c>
       <c r="L24" t="n">
-        <v>192.12</v>
+        <v>121.73</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>28</v>
       </c>
       <c r="J25" t="n">
-        <v>3.21</v>
+        <v>2.44</v>
       </c>
       <c r="K25" t="n">
-        <v>-224.27</v>
+        <v>-170.78</v>
       </c>
       <c r="L25" t="n">
-        <v>224.29</v>
+        <v>170.8</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>28</v>
       </c>
       <c r="J26" t="n">
-        <v>-543.59</v>
+        <v>-358.93</v>
       </c>
       <c r="K26" t="n">
-        <v>22.33</v>
+        <v>14.75</v>
       </c>
       <c r="L26" t="n">
-        <v>544.05</v>
+        <v>359.23</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>28</v>
       </c>
       <c r="J27" t="n">
-        <v>-283.3</v>
+        <v>-189.1</v>
       </c>
       <c r="K27" t="n">
-        <v>-256.47</v>
+        <v>-171.19</v>
       </c>
       <c r="L27" t="n">
-        <v>382.14</v>
+        <v>255.08</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>29</v>
       </c>
       <c r="J28" t="n">
-        <v>87.63</v>
+        <v>61.67</v>
       </c>
       <c r="K28" t="n">
-        <v>166.64</v>
+        <v>117.27</v>
       </c>
       <c r="L28" t="n">
-        <v>188.28</v>
+        <v>132.5</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>28</v>
       </c>
       <c r="J29" t="n">
-        <v>-27</v>
+        <v>-29.14</v>
       </c>
       <c r="K29" t="n">
-        <v>-34.9</v>
+        <v>-37.67</v>
       </c>
       <c r="L29" t="n">
-        <v>44.12</v>
+        <v>47.63</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>31</v>
       </c>
       <c r="J30" t="n">
-        <v>31.04</v>
+        <v>35.18</v>
       </c>
       <c r="K30" t="n">
-        <v>-28.44</v>
+        <v>-32.23</v>
       </c>
       <c r="L30" t="n">
-        <v>42.1</v>
+        <v>47.71</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>29</v>
       </c>
       <c r="J31" t="n">
-        <v>41.01</v>
+        <v>44.52</v>
       </c>
       <c r="K31" t="n">
-        <v>53.13</v>
+        <v>57.67</v>
       </c>
       <c r="L31" t="n">
-        <v>67.12</v>
+        <v>72.86</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>-72.17</v>
+        <v>-64.03</v>
       </c>
       <c r="K32" t="n">
-        <v>-72.09999999999999</v>
+        <v>-63.97</v>
       </c>
       <c r="L32" t="n">
-        <v>102.01</v>
+        <v>90.51000000000001</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>26</v>
       </c>
       <c r="J33" t="n">
-        <v>-86.81999999999999</v>
+        <v>-78.06</v>
       </c>
       <c r="K33" t="n">
-        <v>-4.57</v>
+        <v>-4.11</v>
       </c>
       <c r="L33" t="n">
-        <v>86.94</v>
+        <v>78.17</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>26</v>
       </c>
       <c r="J34" t="n">
-        <v>-125.4</v>
+        <v>-107.8</v>
       </c>
       <c r="K34" t="n">
-        <v>-14.48</v>
+        <v>-12.44</v>
       </c>
       <c r="L34" t="n">
-        <v>126.24</v>
+        <v>108.52</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>26</v>
       </c>
       <c r="J35" t="n">
-        <v>205.52</v>
+        <v>158.95</v>
       </c>
       <c r="K35" t="n">
-        <v>130.49</v>
+        <v>100.92</v>
       </c>
       <c r="L35" t="n">
-        <v>243.45</v>
+        <v>188.28</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>25</v>
       </c>
       <c r="J36" t="n">
-        <v>-153.47</v>
+        <v>-114.43</v>
       </c>
       <c r="K36" t="n">
-        <v>228.68</v>
+        <v>170.5</v>
       </c>
       <c r="L36" t="n">
-        <v>275.4</v>
+        <v>205.34</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>28</v>
       </c>
       <c r="J37" t="n">
-        <v>80.09</v>
+        <v>68.75</v>
       </c>
       <c r="K37" t="n">
-        <v>30.93</v>
+        <v>26.55</v>
       </c>
       <c r="L37" t="n">
-        <v>85.86</v>
+        <v>73.7</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>25</v>
       </c>
       <c r="J38" t="n">
-        <v>298.59</v>
+        <v>186.2</v>
       </c>
       <c r="K38" t="n">
-        <v>319.1</v>
+        <v>198.99</v>
       </c>
       <c r="L38" t="n">
-        <v>437.02</v>
+        <v>272.52</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>30</v>
       </c>
       <c r="J39" t="n">
-        <v>-61.72</v>
+        <v>-48.13</v>
       </c>
       <c r="K39" t="n">
-        <v>-125.74</v>
+        <v>-98.06999999999999</v>
       </c>
       <c r="L39" t="n">
-        <v>140.07</v>
+        <v>109.24</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>29</v>
       </c>
       <c r="J40" t="n">
-        <v>300.06</v>
+        <v>238.15</v>
       </c>
       <c r="K40" t="n">
-        <v>9.26</v>
+        <v>7.35</v>
       </c>
       <c r="L40" t="n">
-        <v>300.2</v>
+        <v>238.27</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>26</v>
       </c>
       <c r="J41" t="n">
-        <v>22.03</v>
+        <v>13.51</v>
       </c>
       <c r="K41" t="n">
-        <v>-247.89</v>
+        <v>-152.04</v>
       </c>
       <c r="L41" t="n">
-        <v>248.87</v>
+        <v>152.64</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>27</v>
       </c>
       <c r="J42" t="n">
-        <v>-231.25</v>
+        <v>-145.54</v>
       </c>
       <c r="K42" t="n">
-        <v>-602.6799999999999</v>
+        <v>-379.31</v>
       </c>
       <c r="L42" t="n">
-        <v>645.52</v>
+        <v>406.27</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>30</v>
       </c>
       <c r="J43" t="n">
-        <v>236.15</v>
+        <v>170.05</v>
       </c>
       <c r="K43" t="n">
-        <v>69.05</v>
+        <v>49.72</v>
       </c>
       <c r="L43" t="n">
-        <v>246.04</v>
+        <v>177.17</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>30</v>
       </c>
       <c r="J44" t="n">
-        <v>-36.98</v>
+        <v>-41.34</v>
       </c>
       <c r="K44" t="n">
-        <v>-50.38</v>
+        <v>-56.32</v>
       </c>
       <c r="L44" t="n">
-        <v>62.5</v>
+        <v>69.87</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>31</v>
       </c>
       <c r="J45" t="n">
-        <v>25.58</v>
+        <v>32.83</v>
       </c>
       <c r="K45" t="n">
-        <v>-10.18</v>
+        <v>-13.06</v>
       </c>
       <c r="L45" t="n">
-        <v>27.53</v>
+        <v>35.34</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>31</v>
       </c>
       <c r="J46" t="n">
-        <v>-40.44</v>
+        <v>-52.04</v>
       </c>
       <c r="K46" t="n">
-        <v>-44.14</v>
+        <v>-56.8</v>
       </c>
       <c r="L46" t="n">
-        <v>59.86</v>
+        <v>77.04000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>-81.39</v>
+        <v>-71.17</v>
       </c>
       <c r="K47" t="n">
-        <v>42.47</v>
+        <v>37.14</v>
       </c>
       <c r="L47" t="n">
-        <v>91.8</v>
+        <v>80.28</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>29</v>
       </c>
       <c r="J48" t="n">
-        <v>64.02</v>
+        <v>65.78</v>
       </c>
       <c r="K48" t="n">
-        <v>-94.84999999999999</v>
+        <v>-97.47</v>
       </c>
       <c r="L48" t="n">
-        <v>114.44</v>
+        <v>117.59</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>29</v>
       </c>
       <c r="J49" t="n">
-        <v>-7.64</v>
+        <v>-7.81</v>
       </c>
       <c r="K49" t="n">
-        <v>-117.04</v>
+        <v>-119.65</v>
       </c>
       <c r="L49" t="n">
-        <v>117.29</v>
+        <v>119.9</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>131.71</v>
+        <v>98.62</v>
       </c>
       <c r="K50" t="n">
-        <v>-74.23999999999999</v>
+        <v>-55.59</v>
       </c>
       <c r="L50" t="n">
-        <v>151.2</v>
+        <v>113.2</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>31</v>
       </c>
       <c r="J51" t="n">
-        <v>-35.87</v>
+        <v>-34.8</v>
       </c>
       <c r="K51" t="n">
-        <v>-120.12</v>
+        <v>-116.54</v>
       </c>
       <c r="L51" t="n">
-        <v>125.36</v>
+        <v>121.62</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>29</v>
       </c>
       <c r="J52" t="n">
-        <v>105.2</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="K52" t="n">
-        <v>-55</v>
+        <v>-49.19</v>
       </c>
       <c r="L52" t="n">
-        <v>118.71</v>
+        <v>106.18</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>27</v>
       </c>
       <c r="J53" t="n">
-        <v>-84.47</v>
+        <v>-61.86</v>
       </c>
       <c r="K53" t="n">
-        <v>-106.85</v>
+        <v>-78.26000000000001</v>
       </c>
       <c r="L53" t="n">
-        <v>136.2</v>
+        <v>99.76000000000001</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>26</v>
       </c>
       <c r="J54" t="n">
-        <v>17.2</v>
+        <v>11.3</v>
       </c>
       <c r="K54" t="n">
-        <v>-340.95</v>
+        <v>-223.96</v>
       </c>
       <c r="L54" t="n">
-        <v>341.39</v>
+        <v>224.24</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>28</v>
       </c>
       <c r="J55" t="n">
-        <v>41.29</v>
+        <v>30.66</v>
       </c>
       <c r="K55" t="n">
-        <v>-134.02</v>
+        <v>-99.52</v>
       </c>
       <c r="L55" t="n">
-        <v>140.24</v>
+        <v>104.14</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>28</v>
       </c>
       <c r="J56" t="n">
-        <v>369.24</v>
+        <v>229.3</v>
       </c>
       <c r="K56" t="n">
-        <v>597.67</v>
+        <v>371.15</v>
       </c>
       <c r="L56" t="n">
-        <v>702.53</v>
+        <v>436.27</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>30</v>
       </c>
       <c r="J57" t="n">
-        <v>-181.55</v>
+        <v>-135.8</v>
       </c>
       <c r="K57" t="n">
-        <v>28.79</v>
+        <v>21.53</v>
       </c>
       <c r="L57" t="n">
-        <v>183.82</v>
+        <v>137.5</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>400.81</v>
+        <v>233.16</v>
       </c>
       <c r="K58" t="n">
-        <v>-216.2</v>
+        <v>-125.77</v>
       </c>
       <c r="L58" t="n">
-        <v>455.4</v>
+        <v>264.92</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>-24.62</v>
+        <v>-23.15</v>
       </c>
       <c r="K59" t="n">
-        <v>129.81</v>
+        <v>122.07</v>
       </c>
       <c r="L59" t="n">
-        <v>132.13</v>
+        <v>124.24</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>31</v>
       </c>
       <c r="J60" t="n">
-        <v>-29.8</v>
+        <v>-38.96</v>
       </c>
       <c r="K60" t="n">
-        <v>-32.17</v>
+        <v>-42.06</v>
       </c>
       <c r="L60" t="n">
-        <v>43.85</v>
+        <v>57.33</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>29</v>
       </c>
       <c r="J61" t="n">
-        <v>47.05</v>
+        <v>53.57</v>
       </c>
       <c r="K61" t="n">
-        <v>-16.5</v>
+        <v>-18.79</v>
       </c>
       <c r="L61" t="n">
-        <v>49.86</v>
+        <v>56.76</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>29</v>
       </c>
       <c r="J62" t="n">
-        <v>56.62</v>
+        <v>59.07</v>
       </c>
       <c r="K62" t="n">
-        <v>24.37</v>
+        <v>25.42</v>
       </c>
       <c r="L62" t="n">
-        <v>61.64</v>
+        <v>64.3</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>141.02</v>
+        <v>117.55</v>
       </c>
       <c r="K63" t="n">
-        <v>55.09</v>
+        <v>45.92</v>
       </c>
       <c r="L63" t="n">
-        <v>151.4</v>
+        <v>126.2</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>31</v>
       </c>
       <c r="J64" t="n">
-        <v>-19.88</v>
+        <v>-22.24</v>
       </c>
       <c r="K64" t="n">
-        <v>85.5</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="L64" t="n">
-        <v>87.78</v>
+        <v>98.2</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>28</v>
       </c>
       <c r="J65" t="n">
-        <v>-111.95</v>
+        <v>-91.14</v>
       </c>
       <c r="K65" t="n">
-        <v>91.95999999999999</v>
+        <v>74.87</v>
       </c>
       <c r="L65" t="n">
-        <v>144.88</v>
+        <v>117.95</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>28</v>
       </c>
       <c r="J66" t="n">
-        <v>84.19</v>
+        <v>70.3</v>
       </c>
       <c r="K66" t="n">
-        <v>-83.34</v>
+        <v>-69.59</v>
       </c>
       <c r="L66" t="n">
-        <v>118.47</v>
+        <v>98.92</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>28</v>
       </c>
       <c r="J67" t="n">
-        <v>-88.98</v>
+        <v>-72.14</v>
       </c>
       <c r="K67" t="n">
-        <v>-167.6</v>
+        <v>-135.88</v>
       </c>
       <c r="L67" t="n">
-        <v>189.75</v>
+        <v>153.85</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>-193.92</v>
+        <v>-133.96</v>
       </c>
       <c r="K68" t="n">
-        <v>183.97</v>
+        <v>127.08</v>
       </c>
       <c r="L68" t="n">
-        <v>267.3</v>
+        <v>184.65</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>30</v>
       </c>
       <c r="J69" t="n">
-        <v>180.15</v>
+        <v>148.93</v>
       </c>
       <c r="K69" t="n">
-        <v>-34.63</v>
+        <v>-28.63</v>
       </c>
       <c r="L69" t="n">
-        <v>183.45</v>
+        <v>151.66</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>173.12</v>
+        <v>118.35</v>
       </c>
       <c r="K70" t="n">
-        <v>100.83</v>
+        <v>68.93000000000001</v>
       </c>
       <c r="L70" t="n">
-        <v>200.34</v>
+        <v>136.97</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>28</v>
       </c>
       <c r="J71" t="n">
-        <v>353.09</v>
+        <v>239.4</v>
       </c>
       <c r="K71" t="n">
-        <v>-151.56</v>
+        <v>-102.76</v>
       </c>
       <c r="L71" t="n">
-        <v>384.24</v>
+        <v>260.52</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>26</v>
       </c>
       <c r="J72" t="n">
-        <v>69.68000000000001</v>
+        <v>42.23</v>
       </c>
       <c r="K72" t="n">
-        <v>269.5</v>
+        <v>163.36</v>
       </c>
       <c r="L72" t="n">
-        <v>278.36</v>
+        <v>168.73</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>-124.54</v>
+        <v>-75.8</v>
       </c>
       <c r="K73" t="n">
-        <v>-352.91</v>
+        <v>-214.8</v>
       </c>
       <c r="L73" t="n">
-        <v>374.24</v>
+        <v>227.78</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>30</v>
       </c>
       <c r="J74" t="n">
-        <v>46.21</v>
+        <v>51.42</v>
       </c>
       <c r="K74" t="n">
-        <v>-18.75</v>
+        <v>-20.87</v>
       </c>
       <c r="L74" t="n">
-        <v>49.87</v>
+        <v>55.49</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>30</v>
       </c>
       <c r="J75" t="n">
-        <v>-34.13</v>
+        <v>-38.46</v>
       </c>
       <c r="K75" t="n">
-        <v>-84.03</v>
+        <v>-94.68000000000001</v>
       </c>
       <c r="L75" t="n">
-        <v>90.7</v>
+        <v>102.19</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>28</v>
       </c>
       <c r="J76" t="n">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="K76" t="n">
-        <v>148.79</v>
+        <v>149.44</v>
       </c>
       <c r="L76" t="n">
-        <v>148.82</v>
+        <v>149.47</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>27</v>
       </c>
       <c r="J77" t="n">
-        <v>-150.06</v>
+        <v>-134.47</v>
       </c>
       <c r="K77" t="n">
-        <v>-118.45</v>
+        <v>-106.14</v>
       </c>
       <c r="L77" t="n">
-        <v>191.17</v>
+        <v>171.32</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>216.8</v>
+        <v>182.93</v>
       </c>
       <c r="K78" t="n">
-        <v>-110.65</v>
+        <v>-93.37</v>
       </c>
       <c r="L78" t="n">
-        <v>243.41</v>
+        <v>205.38</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>30.48</v>
+        <v>24.82</v>
       </c>
       <c r="K79" t="n">
-        <v>106.15</v>
+        <v>86.45999999999999</v>
       </c>
       <c r="L79" t="n">
-        <v>110.44</v>
+        <v>89.95</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>26</v>
       </c>
       <c r="J80" t="n">
-        <v>165.38</v>
+        <v>126.83</v>
       </c>
       <c r="K80" t="n">
-        <v>24.54</v>
+        <v>18.82</v>
       </c>
       <c r="L80" t="n">
-        <v>167.19</v>
+        <v>128.22</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>29</v>
       </c>
       <c r="J81" t="n">
-        <v>88.3</v>
+        <v>75.78</v>
       </c>
       <c r="K81" t="n">
-        <v>-132.53</v>
+        <v>-113.74</v>
       </c>
       <c r="L81" t="n">
-        <v>159.25</v>
+        <v>136.67</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>31</v>
       </c>
       <c r="J82" t="n">
-        <v>-14.34</v>
+        <v>-14.73</v>
       </c>
       <c r="K82" t="n">
-        <v>65.2</v>
+        <v>66.98999999999999</v>
       </c>
       <c r="L82" t="n">
-        <v>66.76000000000001</v>
+        <v>68.59</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>31</v>
       </c>
       <c r="J83" t="n">
-        <v>-77.22</v>
+        <v>-64.87</v>
       </c>
       <c r="K83" t="n">
-        <v>-188.6</v>
+        <v>-158.42</v>
       </c>
       <c r="L83" t="n">
-        <v>203.8</v>
+        <v>171.19</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>-267.11</v>
+        <v>-176.12</v>
       </c>
       <c r="K84" t="n">
-        <v>-42.39</v>
+        <v>-27.95</v>
       </c>
       <c r="L84" t="n">
-        <v>270.46</v>
+        <v>178.33</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>27</v>
       </c>
       <c r="J85" t="n">
-        <v>-150.12</v>
+        <v>-102.6</v>
       </c>
       <c r="K85" t="n">
-        <v>-189.86</v>
+        <v>-129.76</v>
       </c>
       <c r="L85" t="n">
-        <v>242.03</v>
+        <v>165.43</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>29</v>
       </c>
       <c r="J86" t="n">
-        <v>85.65000000000001</v>
+        <v>59.17</v>
       </c>
       <c r="K86" t="n">
-        <v>152.04</v>
+        <v>105.04</v>
       </c>
       <c r="L86" t="n">
-        <v>174.5</v>
+        <v>120.56</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>26</v>
       </c>
       <c r="J87" t="n">
-        <v>224.21</v>
+        <v>138.01</v>
       </c>
       <c r="K87" t="n">
-        <v>-281.76</v>
+        <v>-173.43</v>
       </c>
       <c r="L87" t="n">
-        <v>360.08</v>
+        <v>221.64</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>31</v>
       </c>
       <c r="J88" t="n">
-        <v>87.11</v>
+        <v>67.14</v>
       </c>
       <c r="K88" t="n">
-        <v>117.09</v>
+        <v>90.25</v>
       </c>
       <c r="L88" t="n">
-        <v>145.94</v>
+        <v>112.48</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-10-01.xlsx
+++ b/output/2025-10-01.xlsx
@@ -640,13 +640,13 @@
         <v>29</v>
       </c>
       <c r="J14" t="n">
-        <v>46.44</v>
+        <v>41.62</v>
       </c>
       <c r="K14" t="n">
-        <v>37.23</v>
+        <v>33.36</v>
       </c>
       <c r="L14" t="n">
-        <v>59.52</v>
+        <v>53.34</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>-50.69</v>
+        <v>-46.23</v>
       </c>
       <c r="K15" t="n">
-        <v>-55.8</v>
+        <v>-50.9</v>
       </c>
       <c r="L15" t="n">
-        <v>75.39</v>
+        <v>68.77</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>31</v>
       </c>
       <c r="J16" t="n">
-        <v>-10.44</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>63.63</v>
+        <v>56.04</v>
       </c>
       <c r="L16" t="n">
-        <v>64.48</v>
+        <v>56.79</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>31</v>
       </c>
       <c r="J17" t="n">
-        <v>17.49</v>
+        <v>16.11</v>
       </c>
       <c r="K17" t="n">
-        <v>-42.3</v>
+        <v>-38.97</v>
       </c>
       <c r="L17" t="n">
-        <v>45.77</v>
+        <v>42.17</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>30</v>
       </c>
       <c r="J18" t="n">
-        <v>-76.17</v>
+        <v>-68.84999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>-136</v>
+        <v>-122.92</v>
       </c>
       <c r="L18" t="n">
-        <v>155.88</v>
+        <v>140.89</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>28</v>
       </c>
       <c r="J19" t="n">
-        <v>3.45</v>
+        <v>3.18</v>
       </c>
       <c r="K19" t="n">
-        <v>-89.48</v>
+        <v>-82.36</v>
       </c>
       <c r="L19" t="n">
-        <v>89.54000000000001</v>
+        <v>82.42</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>-127.01</v>
+        <v>-124.69</v>
       </c>
       <c r="K20" t="n">
-        <v>-18.22</v>
+        <v>-17.89</v>
       </c>
       <c r="L20" t="n">
-        <v>128.31</v>
+        <v>125.96</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>29</v>
       </c>
       <c r="J21" t="n">
-        <v>119.42</v>
+        <v>114.76</v>
       </c>
       <c r="K21" t="n">
-        <v>13.1</v>
+        <v>12.59</v>
       </c>
       <c r="L21" t="n">
-        <v>120.14</v>
+        <v>115.45</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>31</v>
       </c>
       <c r="J22" t="n">
-        <v>-136.47</v>
+        <v>-129.39</v>
       </c>
       <c r="K22" t="n">
-        <v>-62.24</v>
+        <v>-59.02</v>
       </c>
       <c r="L22" t="n">
-        <v>149.99</v>
+        <v>142.22</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>25</v>
       </c>
       <c r="J23" t="n">
-        <v>64.19</v>
+        <v>65.09</v>
       </c>
       <c r="K23" t="n">
-        <v>102</v>
+        <v>103.43</v>
       </c>
       <c r="L23" t="n">
-        <v>120.52</v>
+        <v>122.21</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>120.65</v>
+        <v>122.65</v>
       </c>
       <c r="K24" t="n">
-        <v>-16.16</v>
+        <v>-16.43</v>
       </c>
       <c r="L24" t="n">
-        <v>121.73</v>
+        <v>123.74</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>28</v>
       </c>
       <c r="J25" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="K25" t="n">
-        <v>-170.78</v>
+        <v>-170.06</v>
       </c>
       <c r="L25" t="n">
-        <v>170.8</v>
+        <v>170.08</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>28</v>
       </c>
       <c r="J26" t="n">
-        <v>-358.93</v>
+        <v>-362.4</v>
       </c>
       <c r="K26" t="n">
-        <v>14.75</v>
+        <v>14.89</v>
       </c>
       <c r="L26" t="n">
-        <v>359.23</v>
+        <v>362.7</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>28</v>
       </c>
       <c r="J27" t="n">
-        <v>-189.1</v>
+        <v>-190.68</v>
       </c>
       <c r="K27" t="n">
-        <v>-171.19</v>
+        <v>-172.63</v>
       </c>
       <c r="L27" t="n">
-        <v>255.08</v>
+        <v>257.22</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>29</v>
       </c>
       <c r="J28" t="n">
-        <v>61.67</v>
+        <v>61.8</v>
       </c>
       <c r="K28" t="n">
-        <v>117.27</v>
+        <v>117.52</v>
       </c>
       <c r="L28" t="n">
-        <v>132.5</v>
+        <v>132.78</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>28</v>
       </c>
       <c r="J29" t="n">
-        <v>-29.14</v>
+        <v>-26.15</v>
       </c>
       <c r="K29" t="n">
-        <v>-37.67</v>
+        <v>-33.8</v>
       </c>
       <c r="L29" t="n">
-        <v>47.63</v>
+        <v>42.73</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>31</v>
       </c>
       <c r="J30" t="n">
-        <v>35.18</v>
+        <v>30.89</v>
       </c>
       <c r="K30" t="n">
-        <v>-32.23</v>
+        <v>-28.3</v>
       </c>
       <c r="L30" t="n">
-        <v>47.71</v>
+        <v>41.89</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>29</v>
       </c>
       <c r="J31" t="n">
-        <v>44.52</v>
+        <v>39.71</v>
       </c>
       <c r="K31" t="n">
-        <v>57.67</v>
+        <v>51.44</v>
       </c>
       <c r="L31" t="n">
-        <v>72.86</v>
+        <v>64.98</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>-64.03</v>
+        <v>-59.97</v>
       </c>
       <c r="K32" t="n">
-        <v>-63.97</v>
+        <v>-59.92</v>
       </c>
       <c r="L32" t="n">
-        <v>90.51000000000001</v>
+        <v>84.78</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>26</v>
       </c>
       <c r="J33" t="n">
-        <v>-78.06</v>
+        <v>-73.83</v>
       </c>
       <c r="K33" t="n">
-        <v>-4.11</v>
+        <v>-3.88</v>
       </c>
       <c r="L33" t="n">
-        <v>78.17</v>
+        <v>73.94</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>26</v>
       </c>
       <c r="J34" t="n">
-        <v>-107.8</v>
+        <v>-101.74</v>
       </c>
       <c r="K34" t="n">
-        <v>-12.44</v>
+        <v>-11.74</v>
       </c>
       <c r="L34" t="n">
-        <v>108.52</v>
+        <v>102.41</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>26</v>
       </c>
       <c r="J35" t="n">
-        <v>158.95</v>
+        <v>155.23</v>
       </c>
       <c r="K35" t="n">
-        <v>100.92</v>
+        <v>98.55</v>
       </c>
       <c r="L35" t="n">
-        <v>188.28</v>
+        <v>183.87</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>25</v>
       </c>
       <c r="J36" t="n">
-        <v>-114.43</v>
+        <v>-112.33</v>
       </c>
       <c r="K36" t="n">
-        <v>170.5</v>
+        <v>167.39</v>
       </c>
       <c r="L36" t="n">
-        <v>205.34</v>
+        <v>201.59</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>28</v>
       </c>
       <c r="J37" t="n">
-        <v>68.75</v>
+        <v>66.95</v>
       </c>
       <c r="K37" t="n">
-        <v>26.55</v>
+        <v>25.85</v>
       </c>
       <c r="L37" t="n">
-        <v>73.7</v>
+        <v>71.76000000000001</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>25</v>
       </c>
       <c r="J38" t="n">
-        <v>186.2</v>
+        <v>186.93</v>
       </c>
       <c r="K38" t="n">
-        <v>198.99</v>
+        <v>199.77</v>
       </c>
       <c r="L38" t="n">
-        <v>272.52</v>
+        <v>273.59</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>30</v>
       </c>
       <c r="J39" t="n">
-        <v>-48.13</v>
+        <v>-47.18</v>
       </c>
       <c r="K39" t="n">
-        <v>-98.06999999999999</v>
+        <v>-96.12</v>
       </c>
       <c r="L39" t="n">
-        <v>109.24</v>
+        <v>107.08</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>29</v>
       </c>
       <c r="J40" t="n">
-        <v>238.15</v>
+        <v>235.97</v>
       </c>
       <c r="K40" t="n">
-        <v>7.35</v>
+        <v>7.28</v>
       </c>
       <c r="L40" t="n">
-        <v>238.27</v>
+        <v>236.08</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>26</v>
       </c>
       <c r="J41" t="n">
-        <v>13.51</v>
+        <v>13.74</v>
       </c>
       <c r="K41" t="n">
-        <v>-152.04</v>
+        <v>-154.56</v>
       </c>
       <c r="L41" t="n">
-        <v>152.64</v>
+        <v>155.17</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>27</v>
       </c>
       <c r="J42" t="n">
-        <v>-145.54</v>
+        <v>-146.85</v>
       </c>
       <c r="K42" t="n">
-        <v>-379.31</v>
+        <v>-382.71</v>
       </c>
       <c r="L42" t="n">
-        <v>406.27</v>
+        <v>409.92</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>30</v>
       </c>
       <c r="J43" t="n">
-        <v>170.05</v>
+        <v>169.66</v>
       </c>
       <c r="K43" t="n">
-        <v>49.72</v>
+        <v>49.61</v>
       </c>
       <c r="L43" t="n">
-        <v>177.17</v>
+        <v>176.76</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>30</v>
       </c>
       <c r="J44" t="n">
-        <v>-41.34</v>
+        <v>-36.65</v>
       </c>
       <c r="K44" t="n">
-        <v>-56.32</v>
+        <v>-49.93</v>
       </c>
       <c r="L44" t="n">
-        <v>69.87</v>
+        <v>61.93</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>31</v>
       </c>
       <c r="J45" t="n">
-        <v>32.83</v>
+        <v>28.92</v>
       </c>
       <c r="K45" t="n">
-        <v>-13.06</v>
+        <v>-11.51</v>
       </c>
       <c r="L45" t="n">
-        <v>35.34</v>
+        <v>31.12</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>31</v>
       </c>
       <c r="J46" t="n">
-        <v>-52.04</v>
+        <v>-46.2</v>
       </c>
       <c r="K46" t="n">
-        <v>-56.8</v>
+        <v>-50.43</v>
       </c>
       <c r="L46" t="n">
-        <v>77.04000000000001</v>
+        <v>68.39</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>-71.17</v>
+        <v>-66.81</v>
       </c>
       <c r="K47" t="n">
-        <v>37.14</v>
+        <v>34.86</v>
       </c>
       <c r="L47" t="n">
-        <v>80.28</v>
+        <v>75.36</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>29</v>
       </c>
       <c r="J48" t="n">
-        <v>65.78</v>
+        <v>60.51</v>
       </c>
       <c r="K48" t="n">
-        <v>-97.47</v>
+        <v>-89.65000000000001</v>
       </c>
       <c r="L48" t="n">
-        <v>117.59</v>
+        <v>108.16</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>29</v>
       </c>
       <c r="J49" t="n">
-        <v>-7.81</v>
+        <v>-7.22</v>
       </c>
       <c r="K49" t="n">
-        <v>-119.65</v>
+        <v>-110.58</v>
       </c>
       <c r="L49" t="n">
-        <v>119.9</v>
+        <v>110.82</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>98.62</v>
+        <v>97.05</v>
       </c>
       <c r="K50" t="n">
-        <v>-55.59</v>
+        <v>-54.7</v>
       </c>
       <c r="L50" t="n">
-        <v>113.2</v>
+        <v>111.4</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>31</v>
       </c>
       <c r="J51" t="n">
-        <v>-34.8</v>
+        <v>-32.99</v>
       </c>
       <c r="K51" t="n">
-        <v>-116.54</v>
+        <v>-110.49</v>
       </c>
       <c r="L51" t="n">
-        <v>121.62</v>
+        <v>115.31</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>29</v>
       </c>
       <c r="J52" t="n">
-        <v>94.09999999999999</v>
+        <v>90.34</v>
       </c>
       <c r="K52" t="n">
-        <v>-49.19</v>
+        <v>-47.23</v>
       </c>
       <c r="L52" t="n">
-        <v>106.18</v>
+        <v>101.94</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>27</v>
       </c>
       <c r="J53" t="n">
-        <v>-61.86</v>
+        <v>-62.35</v>
       </c>
       <c r="K53" t="n">
-        <v>-78.26000000000001</v>
+        <v>-78.87</v>
       </c>
       <c r="L53" t="n">
-        <v>99.76000000000001</v>
+        <v>100.53</v>
       </c>
     </row>
     <row r="54">
@@ -2323,10 +2323,10 @@
         <v>11.3</v>
       </c>
       <c r="K54" t="n">
-        <v>-223.96</v>
+        <v>-224</v>
       </c>
       <c r="L54" t="n">
-        <v>224.24</v>
+        <v>224.28</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>28</v>
       </c>
       <c r="J55" t="n">
-        <v>30.66</v>
+        <v>30.45</v>
       </c>
       <c r="K55" t="n">
-        <v>-99.52</v>
+        <v>-98.83</v>
       </c>
       <c r="L55" t="n">
-        <v>104.14</v>
+        <v>103.42</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>28</v>
       </c>
       <c r="J56" t="n">
-        <v>229.3</v>
+        <v>230.74</v>
       </c>
       <c r="K56" t="n">
-        <v>371.15</v>
+        <v>373.47</v>
       </c>
       <c r="L56" t="n">
-        <v>436.27</v>
+        <v>439</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>30</v>
       </c>
       <c r="J57" t="n">
-        <v>-135.8</v>
+        <v>-135.09</v>
       </c>
       <c r="K57" t="n">
-        <v>21.53</v>
+        <v>21.42</v>
       </c>
       <c r="L57" t="n">
-        <v>137.5</v>
+        <v>136.78</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>25</v>
       </c>
       <c r="J58" t="n">
-        <v>233.16</v>
+        <v>239.9</v>
       </c>
       <c r="K58" t="n">
-        <v>-125.77</v>
+        <v>-129.41</v>
       </c>
       <c r="L58" t="n">
-        <v>264.92</v>
+        <v>272.58</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>26</v>
       </c>
       <c r="J59" t="n">
-        <v>-23.15</v>
+        <v>-21.01</v>
       </c>
       <c r="K59" t="n">
-        <v>122.07</v>
+        <v>110.74</v>
       </c>
       <c r="L59" t="n">
-        <v>124.24</v>
+        <v>112.72</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>31</v>
       </c>
       <c r="J60" t="n">
-        <v>-38.96</v>
+        <v>-34.32</v>
       </c>
       <c r="K60" t="n">
-        <v>-42.06</v>
+        <v>-37.05</v>
       </c>
       <c r="L60" t="n">
-        <v>57.33</v>
+        <v>50.5</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>29</v>
       </c>
       <c r="J61" t="n">
-        <v>53.57</v>
+        <v>47.84</v>
       </c>
       <c r="K61" t="n">
-        <v>-18.79</v>
+        <v>-16.78</v>
       </c>
       <c r="L61" t="n">
-        <v>56.76</v>
+        <v>50.7</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>29</v>
       </c>
       <c r="J62" t="n">
-        <v>59.07</v>
+        <v>54.2</v>
       </c>
       <c r="K62" t="n">
-        <v>25.42</v>
+        <v>23.33</v>
       </c>
       <c r="L62" t="n">
-        <v>64.3</v>
+        <v>59.01</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>117.55</v>
+        <v>111.18</v>
       </c>
       <c r="K63" t="n">
-        <v>45.92</v>
+        <v>43.43</v>
       </c>
       <c r="L63" t="n">
-        <v>126.2</v>
+        <v>119.36</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>31</v>
       </c>
       <c r="J64" t="n">
-        <v>-22.24</v>
+        <v>-20.28</v>
       </c>
       <c r="K64" t="n">
-        <v>95.65000000000001</v>
+        <v>87.22</v>
       </c>
       <c r="L64" t="n">
-        <v>98.2</v>
+        <v>89.55</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>28</v>
       </c>
       <c r="J65" t="n">
-        <v>-91.14</v>
+        <v>-88.02</v>
       </c>
       <c r="K65" t="n">
-        <v>74.87</v>
+        <v>72.31</v>
       </c>
       <c r="L65" t="n">
-        <v>117.95</v>
+        <v>113.91</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>28</v>
       </c>
       <c r="J66" t="n">
-        <v>70.3</v>
+        <v>68.12</v>
       </c>
       <c r="K66" t="n">
-        <v>-69.59</v>
+        <v>-67.43000000000001</v>
       </c>
       <c r="L66" t="n">
-        <v>98.92</v>
+        <v>95.84999999999999</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>28</v>
       </c>
       <c r="J67" t="n">
-        <v>-72.14</v>
+        <v>-69.67</v>
       </c>
       <c r="K67" t="n">
-        <v>-135.88</v>
+        <v>-131.23</v>
       </c>
       <c r="L67" t="n">
-        <v>153.85</v>
+        <v>148.58</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>-133.96</v>
+        <v>-135.11</v>
       </c>
       <c r="K68" t="n">
-        <v>127.08</v>
+        <v>128.18</v>
       </c>
       <c r="L68" t="n">
-        <v>184.65</v>
+        <v>186.23</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>30</v>
       </c>
       <c r="J69" t="n">
-        <v>148.93</v>
+        <v>147.33</v>
       </c>
       <c r="K69" t="n">
-        <v>-28.63</v>
+        <v>-28.32</v>
       </c>
       <c r="L69" t="n">
-        <v>151.66</v>
+        <v>150.03</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>118.35</v>
+        <v>119.42</v>
       </c>
       <c r="K70" t="n">
-        <v>68.93000000000001</v>
+        <v>69.55</v>
       </c>
       <c r="L70" t="n">
-        <v>136.97</v>
+        <v>138.2</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>28</v>
       </c>
       <c r="J71" t="n">
-        <v>239.4</v>
+        <v>242.49</v>
       </c>
       <c r="K71" t="n">
-        <v>-102.76</v>
+        <v>-104.08</v>
       </c>
       <c r="L71" t="n">
-        <v>260.52</v>
+        <v>263.89</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>26</v>
       </c>
       <c r="J72" t="n">
-        <v>42.23</v>
+        <v>42.87</v>
       </c>
       <c r="K72" t="n">
-        <v>163.36</v>
+        <v>165.81</v>
       </c>
       <c r="L72" t="n">
-        <v>168.73</v>
+        <v>171.26</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>-75.8</v>
+        <v>-77.31999999999999</v>
       </c>
       <c r="K73" t="n">
-        <v>-214.8</v>
+        <v>-219.12</v>
       </c>
       <c r="L73" t="n">
-        <v>227.78</v>
+        <v>232.36</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>30</v>
       </c>
       <c r="J74" t="n">
-        <v>51.42</v>
+        <v>45.86</v>
       </c>
       <c r="K74" t="n">
-        <v>-20.87</v>
+        <v>-18.61</v>
       </c>
       <c r="L74" t="n">
-        <v>55.49</v>
+        <v>49.49</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>30</v>
       </c>
       <c r="J75" t="n">
-        <v>-38.46</v>
+        <v>-34.09</v>
       </c>
       <c r="K75" t="n">
-        <v>-94.68000000000001</v>
+        <v>-83.93000000000001</v>
       </c>
       <c r="L75" t="n">
-        <v>102.19</v>
+        <v>90.59</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>28</v>
       </c>
       <c r="J76" t="n">
-        <v>3.03</v>
+        <v>2.73</v>
       </c>
       <c r="K76" t="n">
-        <v>149.44</v>
+        <v>134.85</v>
       </c>
       <c r="L76" t="n">
-        <v>149.47</v>
+        <v>134.88</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>27</v>
       </c>
       <c r="J77" t="n">
-        <v>-134.47</v>
+        <v>-125.99</v>
       </c>
       <c r="K77" t="n">
-        <v>-106.14</v>
+        <v>-99.45</v>
       </c>
       <c r="L77" t="n">
-        <v>171.32</v>
+        <v>160.51</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>182.93</v>
+        <v>174.32</v>
       </c>
       <c r="K78" t="n">
-        <v>-93.37</v>
+        <v>-88.97</v>
       </c>
       <c r="L78" t="n">
-        <v>205.38</v>
+        <v>195.72</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>24.82</v>
+        <v>23.57</v>
       </c>
       <c r="K79" t="n">
-        <v>86.45999999999999</v>
+        <v>82.08</v>
       </c>
       <c r="L79" t="n">
-        <v>89.95</v>
+        <v>85.39</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>26</v>
       </c>
       <c r="J80" t="n">
-        <v>126.83</v>
+        <v>124.04</v>
       </c>
       <c r="K80" t="n">
-        <v>18.82</v>
+        <v>18.4</v>
       </c>
       <c r="L80" t="n">
-        <v>128.22</v>
+        <v>125.4</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>29</v>
       </c>
       <c r="J81" t="n">
-        <v>75.78</v>
+        <v>72.75</v>
       </c>
       <c r="K81" t="n">
-        <v>-113.74</v>
+        <v>-109.2</v>
       </c>
       <c r="L81" t="n">
-        <v>136.67</v>
+        <v>131.21</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>31</v>
       </c>
       <c r="J82" t="n">
-        <v>-14.73</v>
+        <v>-14.15</v>
       </c>
       <c r="K82" t="n">
-        <v>66.98999999999999</v>
+        <v>64.33</v>
       </c>
       <c r="L82" t="n">
-        <v>68.59</v>
+        <v>65.87</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>31</v>
       </c>
       <c r="J83" t="n">
-        <v>-64.87</v>
+        <v>-63.55</v>
       </c>
       <c r="K83" t="n">
-        <v>-158.42</v>
+        <v>-155.21</v>
       </c>
       <c r="L83" t="n">
-        <v>171.19</v>
+        <v>167.72</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>26</v>
       </c>
       <c r="J84" t="n">
-        <v>-176.12</v>
+        <v>-176.68</v>
       </c>
       <c r="K84" t="n">
-        <v>-27.95</v>
+        <v>-28.04</v>
       </c>
       <c r="L84" t="n">
-        <v>178.33</v>
+        <v>178.89</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>27</v>
       </c>
       <c r="J85" t="n">
-        <v>-102.6</v>
+        <v>-102.46</v>
       </c>
       <c r="K85" t="n">
-        <v>-129.76</v>
+        <v>-129.59</v>
       </c>
       <c r="L85" t="n">
-        <v>165.43</v>
+        <v>165.21</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>29</v>
       </c>
       <c r="J86" t="n">
-        <v>59.17</v>
+        <v>59.02</v>
       </c>
       <c r="K86" t="n">
-        <v>105.04</v>
+        <v>104.76</v>
       </c>
       <c r="L86" t="n">
-        <v>120.56</v>
+        <v>120.24</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>26</v>
       </c>
       <c r="J87" t="n">
-        <v>138.01</v>
+        <v>140.36</v>
       </c>
       <c r="K87" t="n">
-        <v>-173.43</v>
+        <v>-176.38</v>
       </c>
       <c r="L87" t="n">
-        <v>221.64</v>
+        <v>225.41</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>31</v>
       </c>
       <c r="J88" t="n">
-        <v>67.14</v>
+        <v>66.12</v>
       </c>
       <c r="K88" t="n">
-        <v>90.25</v>
+        <v>88.88</v>
       </c>
       <c r="L88" t="n">
-        <v>112.48</v>
+        <v>110.78</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-10-01.xlsx
+++ b/output/2025-10-01.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.86</v>
+        <v>1.61</v>
       </c>
       <c r="F14" t="n">
-        <v>5.15</v>
+        <v>6.49</v>
       </c>
       <c r="G14" t="n">
-        <v>53.3</v>
+        <v>52.1</v>
       </c>
       <c r="H14" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>41.62</v>
+        <v>40.21</v>
       </c>
       <c r="K14" t="n">
-        <v>33.36</v>
+        <v>14.9</v>
       </c>
       <c r="L14" t="n">
-        <v>53.34</v>
+        <v>42.88</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07:19:05</t>
+          <t>07:18:44</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="F15" t="n">
-        <v>6.06</v>
+        <v>5.93</v>
       </c>
       <c r="G15" t="n">
-        <v>47.2</v>
+        <v>49.3</v>
       </c>
       <c r="H15" t="n">
-        <v>0.1</v>
+        <v>4.1</v>
       </c>
       <c r="I15" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>-46.23</v>
+        <v>30.73</v>
       </c>
       <c r="K15" t="n">
-        <v>-50.9</v>
+        <v>-5.77</v>
       </c>
       <c r="L15" t="n">
-        <v>68.77</v>
+        <v>31.27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07:20:02</t>
+          <t>07:21:05</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.05</v>
+        <v>2.03</v>
       </c>
       <c r="F16" t="n">
-        <v>5.92</v>
+        <v>5.39</v>
       </c>
       <c r="G16" t="n">
-        <v>59.7</v>
+        <v>42.6</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>-9.199999999999999</v>
+        <v>-52.3</v>
       </c>
       <c r="K16" t="n">
-        <v>56.04</v>
+        <v>14.51</v>
       </c>
       <c r="L16" t="n">
-        <v>56.79</v>
+        <v>54.28</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07:23:20</t>
+          <t>07:24:28</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.4</v>
+        <v>1.95</v>
       </c>
       <c r="F17" t="n">
-        <v>6.39</v>
+        <v>6.09</v>
       </c>
       <c r="G17" t="n">
-        <v>39.8</v>
+        <v>39.7</v>
       </c>
       <c r="H17" t="n">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>16.11</v>
+        <v>35.72</v>
       </c>
       <c r="K17" t="n">
-        <v>-38.97</v>
+        <v>50.11</v>
       </c>
       <c r="L17" t="n">
-        <v>42.17</v>
+        <v>61.53</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07:25:28</t>
+          <t>07:25:47</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="F18" t="n">
-        <v>6.13</v>
+        <v>6.37</v>
       </c>
       <c r="G18" t="n">
-        <v>41.7</v>
+        <v>60.5</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J18" t="n">
-        <v>-68.84999999999999</v>
+        <v>-90.84999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>-122.92</v>
+        <v>-45.96</v>
       </c>
       <c r="L18" t="n">
-        <v>140.89</v>
+        <v>101.81</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07:27:44</t>
+          <t>07:26:26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.08</v>
+        <v>2.21</v>
       </c>
       <c r="F19" t="n">
-        <v>5.93</v>
+        <v>5.69</v>
       </c>
       <c r="G19" t="n">
-        <v>51.6</v>
+        <v>58.2</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="I19" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>3.18</v>
+        <v>63.8</v>
       </c>
       <c r="K19" t="n">
-        <v>-82.36</v>
+        <v>56.3</v>
       </c>
       <c r="L19" t="n">
-        <v>82.42</v>
+        <v>85.09</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07:33:12</t>
+          <t>07:31:25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="F20" t="n">
-        <v>5.84</v>
+        <v>5.9</v>
       </c>
       <c r="G20" t="n">
-        <v>47.4</v>
+        <v>49.3</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I20" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>-124.69</v>
+        <v>-60.4</v>
       </c>
       <c r="K20" t="n">
-        <v>-17.89</v>
+        <v>-48.4</v>
       </c>
       <c r="L20" t="n">
-        <v>125.96</v>
+        <v>77.40000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07:34:50</t>
+          <t>07:32:57</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.02</v>
+        <v>1.86</v>
       </c>
       <c r="F21" t="n">
-        <v>6.01</v>
+        <v>5.95</v>
       </c>
       <c r="G21" t="n">
-        <v>41.2</v>
+        <v>31.5</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>114.76</v>
+        <v>19.41</v>
       </c>
       <c r="K21" t="n">
-        <v>12.59</v>
+        <v>-57.5</v>
       </c>
       <c r="L21" t="n">
-        <v>115.45</v>
+        <v>60.68</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07:36:02</t>
+          <t>07:34:21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.13</v>
+        <v>1.88</v>
       </c>
       <c r="F22" t="n">
-        <v>5.97</v>
+        <v>5.4</v>
       </c>
       <c r="G22" t="n">
-        <v>51.2</v>
+        <v>43.7</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="I22" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>-129.39</v>
+        <v>-59.3</v>
       </c>
       <c r="K22" t="n">
-        <v>-59.02</v>
+        <v>28.51</v>
       </c>
       <c r="L22" t="n">
-        <v>142.22</v>
+        <v>65.8</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07:41:27</t>
+          <t>07:38:23</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="F23" t="n">
-        <v>6.13</v>
+        <v>5.73</v>
       </c>
       <c r="G23" t="n">
-        <v>33.9</v>
+        <v>49.8</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I23" t="n">
         <v>25</v>
       </c>
       <c r="J23" t="n">
-        <v>65.09</v>
+        <v>-75.73</v>
       </c>
       <c r="K23" t="n">
-        <v>103.43</v>
+        <v>44.55</v>
       </c>
       <c r="L23" t="n">
-        <v>122.21</v>
+        <v>87.86</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07:42:58</t>
+          <t>07:39:47</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="F24" t="n">
-        <v>6.2</v>
+        <v>5.26</v>
       </c>
       <c r="G24" t="n">
-        <v>49.6</v>
+        <v>60.9</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="I24" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>122.65</v>
+        <v>125.37</v>
       </c>
       <c r="K24" t="n">
-        <v>-16.43</v>
+        <v>-125.73</v>
       </c>
       <c r="L24" t="n">
-        <v>123.74</v>
+        <v>177.55</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07:44:27</t>
+          <t>07:40:42</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.19</v>
+        <v>2.04</v>
       </c>
       <c r="F25" t="n">
-        <v>6.35</v>
+        <v>6.17</v>
       </c>
       <c r="G25" t="n">
-        <v>45.3</v>
+        <v>45.5</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>2.43</v>
+        <v>-1.19</v>
       </c>
       <c r="K25" t="n">
-        <v>-170.06</v>
+        <v>-62.57</v>
       </c>
       <c r="L25" t="n">
-        <v>170.08</v>
+        <v>62.58</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07:49:51</t>
+          <t>07:46:00</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.44</v>
+        <v>2.09</v>
       </c>
       <c r="F26" t="n">
-        <v>6.35</v>
+        <v>5.62</v>
       </c>
       <c r="G26" t="n">
-        <v>32.8</v>
+        <v>49</v>
       </c>
       <c r="H26" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>-362.4</v>
+        <v>-194.04</v>
       </c>
       <c r="K26" t="n">
-        <v>14.89</v>
+        <v>-46.51</v>
       </c>
       <c r="L26" t="n">
-        <v>362.7</v>
+        <v>199.54</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07:51:27</t>
+          <t>07:47:57</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="F27" t="n">
-        <v>5.85</v>
+        <v>6.14</v>
       </c>
       <c r="G27" t="n">
-        <v>44.9</v>
+        <v>40.6</v>
       </c>
       <c r="H27" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J27" t="n">
-        <v>-190.68</v>
+        <v>173.53</v>
       </c>
       <c r="K27" t="n">
-        <v>-172.63</v>
+        <v>41.01</v>
       </c>
       <c r="L27" t="n">
-        <v>257.22</v>
+        <v>178.31</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07:53:35</t>
+          <t>07:48:32</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.26</v>
+        <v>2.14</v>
       </c>
       <c r="F28" t="n">
-        <v>6.17</v>
+        <v>6.45</v>
       </c>
       <c r="G28" t="n">
-        <v>60</v>
+        <v>46.8</v>
       </c>
       <c r="H28" t="n">
-        <v>1.6</v>
+        <v>9.9</v>
       </c>
       <c r="I28" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="J28" t="n">
-        <v>61.8</v>
+        <v>-85.06</v>
       </c>
       <c r="K28" t="n">
-        <v>117.52</v>
+        <v>207.73</v>
       </c>
       <c r="L28" t="n">
-        <v>132.78</v>
+        <v>224.47</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08:03:44</t>
+          <t>07:56:57</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="F29" t="n">
-        <v>6.83</v>
+        <v>5.74</v>
       </c>
       <c r="G29" t="n">
-        <v>44.7</v>
+        <v>45.6</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>-26.15</v>
+        <v>18.12</v>
       </c>
       <c r="K29" t="n">
-        <v>-33.8</v>
+        <v>-28.23</v>
       </c>
       <c r="L29" t="n">
-        <v>42.73</v>
+        <v>33.55</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08:05:19</t>
+          <t>07:58:56</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>1.79</v>
+        <v>2.57</v>
       </c>
       <c r="F30" t="n">
-        <v>5.77</v>
+        <v>5.65</v>
       </c>
       <c r="G30" t="n">
-        <v>45.6</v>
+        <v>59.8</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="I30" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>30.89</v>
+        <v>11.2</v>
       </c>
       <c r="K30" t="n">
-        <v>-28.3</v>
+        <v>-54.37</v>
       </c>
       <c r="L30" t="n">
-        <v>41.89</v>
+        <v>55.51</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08:07:15</t>
+          <t>08:01:03</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.48</v>
+        <v>2.14</v>
       </c>
       <c r="F31" t="n">
-        <v>6.18</v>
+        <v>6.2</v>
       </c>
       <c r="G31" t="n">
-        <v>53.5</v>
+        <v>58.6</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="I31" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>39.71</v>
+        <v>49.27</v>
       </c>
       <c r="K31" t="n">
-        <v>51.44</v>
+        <v>-27.97</v>
       </c>
       <c r="L31" t="n">
-        <v>64.98</v>
+        <v>56.65</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08:11:14</t>
+          <t>08:07:32</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,13 +1381,13 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.12</v>
+        <v>2.39</v>
       </c>
       <c r="F32" t="n">
-        <v>6.11</v>
+        <v>6.81</v>
       </c>
       <c r="G32" t="n">
-        <v>44.5</v>
+        <v>53.4</v>
       </c>
       <c r="H32" t="n">
         <v>0</v>
@@ -1396,19 +1396,19 @@
         <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>-59.97</v>
+        <v>33.23</v>
       </c>
       <c r="K32" t="n">
-        <v>-59.92</v>
+        <v>7.37</v>
       </c>
       <c r="L32" t="n">
-        <v>84.78</v>
+        <v>34.04</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08:13:18</t>
+          <t>08:09:59</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.3</v>
+        <v>2.37</v>
       </c>
       <c r="F33" t="n">
-        <v>5.8</v>
+        <v>5.91</v>
       </c>
       <c r="G33" t="n">
-        <v>51.3</v>
+        <v>40.7</v>
       </c>
       <c r="H33" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J33" t="n">
-        <v>-73.83</v>
+        <v>-73.87</v>
       </c>
       <c r="K33" t="n">
-        <v>-3.88</v>
+        <v>-53.62</v>
       </c>
       <c r="L33" t="n">
-        <v>73.94</v>
+        <v>91.28</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08:14:23</t>
+          <t>08:11:06</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.7</v>
+        <v>2.11</v>
       </c>
       <c r="F34" t="n">
-        <v>5.84</v>
+        <v>6.16</v>
       </c>
       <c r="G34" t="n">
-        <v>47.8</v>
+        <v>42.2</v>
       </c>
       <c r="H34" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="I34" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>-101.74</v>
+        <v>65.98</v>
       </c>
       <c r="K34" t="n">
-        <v>-11.74</v>
+        <v>36.6</v>
       </c>
       <c r="L34" t="n">
-        <v>102.41</v>
+        <v>75.45</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08:19:26</t>
+          <t>08:16:12</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="F35" t="n">
-        <v>6.2</v>
+        <v>5.32</v>
       </c>
       <c r="G35" t="n">
-        <v>34.3</v>
+        <v>46.5</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J35" t="n">
-        <v>155.23</v>
+        <v>78.59</v>
       </c>
       <c r="K35" t="n">
-        <v>98.55</v>
+        <v>12.24</v>
       </c>
       <c r="L35" t="n">
-        <v>183.87</v>
+        <v>79.54000000000001</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08:21:03</t>
+          <t>08:16:56</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.37</v>
+        <v>2.11</v>
       </c>
       <c r="F36" t="n">
-        <v>6.14</v>
+        <v>6.19</v>
       </c>
       <c r="G36" t="n">
-        <v>51.5</v>
+        <v>43.8</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="I36" t="n">
         <v>25</v>
       </c>
       <c r="J36" t="n">
-        <v>-112.33</v>
+        <v>82.88</v>
       </c>
       <c r="K36" t="n">
-        <v>167.39</v>
+        <v>-45.53</v>
       </c>
       <c r="L36" t="n">
-        <v>201.59</v>
+        <v>94.56</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08:21:55</t>
+          <t>08:18:07</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.26</v>
+        <v>1.97</v>
       </c>
       <c r="F37" t="n">
-        <v>6.02</v>
+        <v>5.74</v>
       </c>
       <c r="G37" t="n">
-        <v>57.4</v>
+        <v>55.2</v>
       </c>
       <c r="H37" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="I37" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>66.95</v>
+        <v>-32.85</v>
       </c>
       <c r="K37" t="n">
-        <v>25.85</v>
+        <v>-61.52</v>
       </c>
       <c r="L37" t="n">
-        <v>71.76000000000001</v>
+        <v>69.73999999999999</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08:26:13</t>
+          <t>08:21:34</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,13 +1633,13 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.87</v>
+        <v>2.18</v>
       </c>
       <c r="F38" t="n">
-        <v>6.3</v>
+        <v>5.79</v>
       </c>
       <c r="G38" t="n">
-        <v>48.9</v>
+        <v>58.9</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
@@ -1648,19 +1648,19 @@
         <v>25</v>
       </c>
       <c r="J38" t="n">
-        <v>186.93</v>
+        <v>57.02</v>
       </c>
       <c r="K38" t="n">
-        <v>199.77</v>
+        <v>-79.51000000000001</v>
       </c>
       <c r="L38" t="n">
-        <v>273.59</v>
+        <v>97.84</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08:28:03</t>
+          <t>08:23:08</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.9</v>
+        <v>2.08</v>
       </c>
       <c r="F39" t="n">
-        <v>6.42</v>
+        <v>5.89</v>
       </c>
       <c r="G39" t="n">
-        <v>59.7</v>
+        <v>49.4</v>
       </c>
       <c r="H39" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="I39" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>-47.18</v>
+        <v>-156.11</v>
       </c>
       <c r="K39" t="n">
-        <v>-96.12</v>
+        <v>-8.4</v>
       </c>
       <c r="L39" t="n">
-        <v>107.08</v>
+        <v>156.33</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08:29:13</t>
+          <t>08:24:00</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.24</v>
+        <v>2.56</v>
       </c>
       <c r="F40" t="n">
-        <v>5.78</v>
+        <v>6.25</v>
       </c>
       <c r="G40" t="n">
-        <v>26.7</v>
+        <v>52.9</v>
       </c>
       <c r="H40" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="J40" t="n">
-        <v>235.97</v>
+        <v>128.36</v>
       </c>
       <c r="K40" t="n">
-        <v>7.28</v>
+        <v>21.2</v>
       </c>
       <c r="L40" t="n">
-        <v>236.08</v>
+        <v>130.09</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08:33:28</t>
+          <t>08:30:06</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.29</v>
+        <v>2.21</v>
       </c>
       <c r="F41" t="n">
-        <v>5.7</v>
+        <v>6.27</v>
       </c>
       <c r="G41" t="n">
-        <v>65.40000000000001</v>
+        <v>54.2</v>
       </c>
       <c r="H41" t="n">
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J41" t="n">
-        <v>13.74</v>
+        <v>-218.77</v>
       </c>
       <c r="K41" t="n">
-        <v>-154.56</v>
+        <v>93.08</v>
       </c>
       <c r="L41" t="n">
-        <v>155.17</v>
+        <v>237.75</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08:35:24</t>
+          <t>08:32:07</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="F42" t="n">
-        <v>5.83</v>
+        <v>6.4</v>
       </c>
       <c r="G42" t="n">
-        <v>48.9</v>
+        <v>47.2</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="I42" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>-146.85</v>
+        <v>2.1</v>
       </c>
       <c r="K42" t="n">
-        <v>-382.71</v>
+        <v>86.2</v>
       </c>
       <c r="L42" t="n">
-        <v>409.92</v>
+        <v>86.23</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08:38:00</t>
+          <t>08:33:52</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>1.93</v>
+        <v>2.6</v>
       </c>
       <c r="F43" t="n">
-        <v>5.72</v>
+        <v>6.15</v>
       </c>
       <c r="G43" t="n">
-        <v>45</v>
+        <v>57.8</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="I43" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>169.66</v>
+        <v>122.43</v>
       </c>
       <c r="K43" t="n">
-        <v>49.61</v>
+        <v>6.63</v>
       </c>
       <c r="L43" t="n">
-        <v>176.76</v>
+        <v>122.61</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08:49:42</t>
+          <t>08:41:59</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.62</v>
+        <v>2.24</v>
       </c>
       <c r="F44" t="n">
-        <v>6.05</v>
+        <v>5.62</v>
       </c>
       <c r="G44" t="n">
-        <v>40.7</v>
+        <v>53.2</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="I44" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>-36.65</v>
+        <v>58.26</v>
       </c>
       <c r="K44" t="n">
-        <v>-49.93</v>
+        <v>26.62</v>
       </c>
       <c r="L44" t="n">
-        <v>61.93</v>
+        <v>64.05</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:51:49</t>
+          <t>08:42:57</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.21</v>
+        <v>2.32</v>
       </c>
       <c r="F45" t="n">
-        <v>5.56</v>
+        <v>6.39</v>
       </c>
       <c r="G45" t="n">
-        <v>48.7</v>
+        <v>49.3</v>
       </c>
       <c r="H45" t="n">
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J45" t="n">
-        <v>28.92</v>
+        <v>-34.61</v>
       </c>
       <c r="K45" t="n">
-        <v>-11.51</v>
+        <v>-41.7</v>
       </c>
       <c r="L45" t="n">
-        <v>31.12</v>
+        <v>54.19</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08:52:39</t>
+          <t>08:43:56</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.2</v>
+        <v>2.47</v>
       </c>
       <c r="F46" t="n">
         <v>5.75</v>
       </c>
       <c r="G46" t="n">
-        <v>45.5</v>
+        <v>47.3</v>
       </c>
       <c r="H46" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>-46.2</v>
+        <v>45.06</v>
       </c>
       <c r="K46" t="n">
-        <v>-50.43</v>
+        <v>-4.85</v>
       </c>
       <c r="L46" t="n">
-        <v>68.39</v>
+        <v>45.32</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08:56:55</t>
+          <t>08:47:54</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,13 +2011,13 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.22</v>
+        <v>2.56</v>
       </c>
       <c r="F47" t="n">
-        <v>6.25</v>
+        <v>5.31</v>
       </c>
       <c r="G47" t="n">
-        <v>33</v>
+        <v>68.7</v>
       </c>
       <c r="H47" t="n">
         <v>0</v>
@@ -2026,19 +2026,19 @@
         <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>-66.81</v>
+        <v>0.98</v>
       </c>
       <c r="K47" t="n">
-        <v>34.86</v>
+        <v>-17.59</v>
       </c>
       <c r="L47" t="n">
-        <v>75.36</v>
+        <v>17.62</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08:58:34</t>
+          <t>08:49:03</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.31</v>
+        <v>2.43</v>
       </c>
       <c r="F48" t="n">
-        <v>5.67</v>
+        <v>6</v>
       </c>
       <c r="G48" t="n">
-        <v>46.7</v>
+        <v>56</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="I48" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J48" t="n">
-        <v>60.51</v>
+        <v>72.58</v>
       </c>
       <c r="K48" t="n">
-        <v>-89.65000000000001</v>
+        <v>24.8</v>
       </c>
       <c r="L48" t="n">
-        <v>108.16</v>
+        <v>76.7</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09:00:02</t>
+          <t>08:50:33</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.35</v>
+        <v>2.18</v>
       </c>
       <c r="F49" t="n">
-        <v>6.26</v>
+        <v>5.6</v>
       </c>
       <c r="G49" t="n">
-        <v>46.1</v>
+        <v>53.2</v>
       </c>
       <c r="H49" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>-7.22</v>
+        <v>26.95</v>
       </c>
       <c r="K49" t="n">
-        <v>-110.58</v>
+        <v>74.66</v>
       </c>
       <c r="L49" t="n">
-        <v>110.82</v>
+        <v>79.37</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09:06:02</t>
+          <t>08:55:05</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.34</v>
+        <v>2.46</v>
       </c>
       <c r="F50" t="n">
-        <v>6.13</v>
+        <v>5.75</v>
       </c>
       <c r="G50" t="n">
-        <v>33.1</v>
+        <v>62.9</v>
       </c>
       <c r="H50" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>97.05</v>
+        <v>-61.17</v>
       </c>
       <c r="K50" t="n">
-        <v>-54.7</v>
+        <v>52.86</v>
       </c>
       <c r="L50" t="n">
-        <v>111.4</v>
+        <v>80.84</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09:07:33</t>
+          <t>08:56:40</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.53</v>
+        <v>2.36</v>
       </c>
       <c r="F51" t="n">
-        <v>7.09</v>
+        <v>5.67</v>
       </c>
       <c r="G51" t="n">
-        <v>45.2</v>
+        <v>34.8</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="J51" t="n">
-        <v>-32.99</v>
+        <v>-66.02</v>
       </c>
       <c r="K51" t="n">
-        <v>-110.49</v>
+        <v>59.14</v>
       </c>
       <c r="L51" t="n">
-        <v>115.31</v>
+        <v>88.63</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09:08:51</t>
+          <t>08:57:46</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.31</v>
+        <v>2.15</v>
       </c>
       <c r="F52" t="n">
-        <v>6.46</v>
+        <v>6.6</v>
       </c>
       <c r="G52" t="n">
-        <v>61.7</v>
+        <v>55.2</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>90.34</v>
+        <v>87.02</v>
       </c>
       <c r="K52" t="n">
-        <v>-47.23</v>
+        <v>12.78</v>
       </c>
       <c r="L52" t="n">
-        <v>101.94</v>
+        <v>87.95</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09:13:44</t>
+          <t>09:01:15</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="F53" t="n">
-        <v>6.52</v>
+        <v>5.78</v>
       </c>
       <c r="G53" t="n">
-        <v>42.1</v>
+        <v>45.7</v>
       </c>
       <c r="H53" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>-62.35</v>
+        <v>123.87</v>
       </c>
       <c r="K53" t="n">
-        <v>-78.87</v>
+        <v>10.68</v>
       </c>
       <c r="L53" t="n">
-        <v>100.53</v>
+        <v>124.33</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09:14:36</t>
+          <t>09:02:20</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.72</v>
+        <v>2.3</v>
       </c>
       <c r="F54" t="n">
-        <v>6.23</v>
+        <v>6.21</v>
       </c>
       <c r="G54" t="n">
-        <v>55.9</v>
+        <v>31.7</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
       </c>
       <c r="I54" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J54" t="n">
-        <v>11.3</v>
+        <v>91.58</v>
       </c>
       <c r="K54" t="n">
-        <v>-224</v>
+        <v>-88.73999999999999</v>
       </c>
       <c r="L54" t="n">
-        <v>224.28</v>
+        <v>127.52</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09:15:37</t>
+          <t>09:03:44</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2.38</v>
+        <v>2.47</v>
       </c>
       <c r="F55" t="n">
-        <v>6.1</v>
+        <v>5.6</v>
       </c>
       <c r="G55" t="n">
-        <v>43.2</v>
+        <v>57</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="I55" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="J55" t="n">
-        <v>30.45</v>
+        <v>82.45</v>
       </c>
       <c r="K55" t="n">
-        <v>-98.83</v>
+        <v>-153.94</v>
       </c>
       <c r="L55" t="n">
-        <v>103.42</v>
+        <v>174.63</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09:19:22</t>
+          <t>09:08:16</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>3.46</v>
+        <v>2.4</v>
       </c>
       <c r="F56" t="n">
-        <v>5.63</v>
+        <v>5.98</v>
       </c>
       <c r="G56" t="n">
-        <v>48.3</v>
+        <v>54.7</v>
       </c>
       <c r="H56" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="I56" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>230.74</v>
+        <v>215.2</v>
       </c>
       <c r="K56" t="n">
-        <v>373.47</v>
+        <v>124.46</v>
       </c>
       <c r="L56" t="n">
-        <v>439</v>
+        <v>248.6</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09:20:55</t>
+          <t>09:09:58</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>2.17</v>
+        <v>2.54</v>
       </c>
       <c r="F57" t="n">
-        <v>5.84</v>
+        <v>6.03</v>
       </c>
       <c r="G57" t="n">
-        <v>62.7</v>
+        <v>46.6</v>
       </c>
       <c r="H57" t="n">
-        <v>0.1</v>
+        <v>4.3</v>
       </c>
       <c r="I57" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="J57" t="n">
-        <v>-135.09</v>
+        <v>35.42</v>
       </c>
       <c r="K57" t="n">
-        <v>21.42</v>
+        <v>192.95</v>
       </c>
       <c r="L57" t="n">
-        <v>136.78</v>
+        <v>196.18</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09:23:07</t>
+          <t>09:11:12</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.46</v>
+        <v>2.12</v>
       </c>
       <c r="F58" t="n">
-        <v>6.2</v>
+        <v>5.92</v>
       </c>
       <c r="G58" t="n">
-        <v>43.1</v>
+        <v>56.3</v>
       </c>
       <c r="H58" t="n">
-        <v>5.8</v>
+        <v>8.6</v>
       </c>
       <c r="I58" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="J58" t="n">
-        <v>239.9</v>
+        <v>4.74</v>
       </c>
       <c r="K58" t="n">
-        <v>-129.41</v>
+        <v>184.88</v>
       </c>
       <c r="L58" t="n">
-        <v>272.58</v>
+        <v>184.94</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09:31:01</t>
+          <t>09:22:13</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="F59" t="n">
-        <v>5.95</v>
+        <v>6.13</v>
       </c>
       <c r="G59" t="n">
-        <v>65.8</v>
+        <v>52.8</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="I59" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>-21.01</v>
+        <v>21.26</v>
       </c>
       <c r="K59" t="n">
-        <v>110.74</v>
+        <v>-34.77</v>
       </c>
       <c r="L59" t="n">
-        <v>112.72</v>
+        <v>40.75</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09:32:14</t>
+          <t>09:23:02</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.11</v>
+        <v>2.32</v>
       </c>
       <c r="F60" t="n">
-        <v>5.57</v>
+        <v>6.44</v>
       </c>
       <c r="G60" t="n">
-        <v>36.6</v>
+        <v>47.1</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="I60" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>-34.32</v>
+        <v>-50.22</v>
       </c>
       <c r="K60" t="n">
-        <v>-37.05</v>
+        <v>57.69</v>
       </c>
       <c r="L60" t="n">
-        <v>50.5</v>
+        <v>76.48999999999999</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09:33:55</t>
+          <t>09:25:01</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2602,31 +2602,31 @@
         <v>2.25</v>
       </c>
       <c r="F61" t="n">
-        <v>4.93</v>
+        <v>5.89</v>
       </c>
       <c r="G61" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="H61" t="n">
-        <v>0.9</v>
+        <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>47.84</v>
+        <v>-31.99</v>
       </c>
       <c r="K61" t="n">
-        <v>-16.78</v>
+        <v>-7.01</v>
       </c>
       <c r="L61" t="n">
-        <v>50.7</v>
+        <v>32.74</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09:39:42</t>
+          <t>09:31:02</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.2</v>
+        <v>2.41</v>
       </c>
       <c r="F62" t="n">
-        <v>5.99</v>
+        <v>5.78</v>
       </c>
       <c r="G62" t="n">
-        <v>46.5</v>
+        <v>41.3</v>
       </c>
       <c r="H62" t="n">
         <v>0</v>
       </c>
       <c r="I62" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>54.2</v>
+        <v>-68.90000000000001</v>
       </c>
       <c r="K62" t="n">
-        <v>23.33</v>
+        <v>47.96</v>
       </c>
       <c r="L62" t="n">
-        <v>59.01</v>
+        <v>83.95</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09:40:44</t>
+          <t>09:31:43</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.62</v>
+        <v>2.43</v>
       </c>
       <c r="F63" t="n">
-        <v>5.66</v>
+        <v>5.72</v>
       </c>
       <c r="G63" t="n">
-        <v>60.5</v>
+        <v>40.4</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J63" t="n">
-        <v>111.18</v>
+        <v>34.85</v>
       </c>
       <c r="K63" t="n">
-        <v>43.43</v>
+        <v>-13.27</v>
       </c>
       <c r="L63" t="n">
-        <v>119.36</v>
+        <v>37.29</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09:42:51</t>
+          <t>09:33:31</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>2.52</v>
+        <v>2.13</v>
       </c>
       <c r="F64" t="n">
-        <v>6.11</v>
+        <v>5.49</v>
       </c>
       <c r="G64" t="n">
-        <v>38.5</v>
+        <v>59.4</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="I64" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="J64" t="n">
-        <v>-20.28</v>
+        <v>-36.75</v>
       </c>
       <c r="K64" t="n">
-        <v>87.22</v>
+        <v>-66.34999999999999</v>
       </c>
       <c r="L64" t="n">
-        <v>89.55</v>
+        <v>75.84999999999999</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09:47:21</t>
+          <t>09:38:44</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="F65" t="n">
-        <v>5.64</v>
+        <v>5.48</v>
       </c>
       <c r="G65" t="n">
-        <v>36.4</v>
+        <v>46.8</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J65" t="n">
-        <v>-88.02</v>
+        <v>18.11</v>
       </c>
       <c r="K65" t="n">
-        <v>72.31</v>
+        <v>87.95</v>
       </c>
       <c r="L65" t="n">
-        <v>113.91</v>
+        <v>89.79000000000001</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09:49:02</t>
+          <t>09:39:56</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>2.46</v>
+        <v>2.31</v>
       </c>
       <c r="F66" t="n">
-        <v>6.36</v>
+        <v>6.55</v>
       </c>
       <c r="G66" t="n">
-        <v>40.8</v>
+        <v>45.3</v>
       </c>
       <c r="H66" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
       <c r="I66" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J66" t="n">
-        <v>68.12</v>
+        <v>-29.09</v>
       </c>
       <c r="K66" t="n">
-        <v>-67.43000000000001</v>
+        <v>-93.69</v>
       </c>
       <c r="L66" t="n">
-        <v>95.84999999999999</v>
+        <v>98.09999999999999</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09:51:33</t>
+          <t>09:41:18</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>2.72</v>
+        <v>2.2</v>
       </c>
       <c r="F67" t="n">
-        <v>5.5</v>
+        <v>5.34</v>
       </c>
       <c r="G67" t="n">
-        <v>75.3</v>
+        <v>44.6</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="I67" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="J67" t="n">
-        <v>-69.67</v>
+        <v>115.67</v>
       </c>
       <c r="K67" t="n">
-        <v>-131.23</v>
+        <v>-51.61</v>
       </c>
       <c r="L67" t="n">
-        <v>148.58</v>
+        <v>126.66</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09:56:34</t>
+          <t>09:46:00</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.27</v>
+        <v>2.45</v>
       </c>
       <c r="F68" t="n">
-        <v>5.8</v>
+        <v>6.13</v>
       </c>
       <c r="G68" t="n">
-        <v>36.4</v>
+        <v>45.8</v>
       </c>
       <c r="H68" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J68" t="n">
-        <v>-135.11</v>
+        <v>-125.91</v>
       </c>
       <c r="K68" t="n">
-        <v>128.18</v>
+        <v>-52.04</v>
       </c>
       <c r="L68" t="n">
-        <v>186.23</v>
+        <v>136.24</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09:57:42</t>
+          <t>09:46:33</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>2.33</v>
+        <v>2.42</v>
       </c>
       <c r="F69" t="n">
-        <v>5.62</v>
+        <v>6.18</v>
       </c>
       <c r="G69" t="n">
-        <v>51</v>
+        <v>44.1</v>
       </c>
       <c r="H69" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I69" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>147.33</v>
+        <v>-106.83</v>
       </c>
       <c r="K69" t="n">
-        <v>-28.32</v>
+        <v>-24.59</v>
       </c>
       <c r="L69" t="n">
-        <v>150.03</v>
+        <v>109.63</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09:59:38</t>
+          <t>09:48:45</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.35</v>
+        <v>2.51</v>
       </c>
       <c r="F70" t="n">
-        <v>6</v>
+        <v>6.36</v>
       </c>
       <c r="G70" t="n">
-        <v>48.9</v>
+        <v>48.4</v>
       </c>
       <c r="H70" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="I70" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>119.42</v>
+        <v>-75.02</v>
       </c>
       <c r="K70" t="n">
-        <v>69.55</v>
+        <v>-12.2</v>
       </c>
       <c r="L70" t="n">
-        <v>138.2</v>
+        <v>76.01000000000001</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>10:04:54</t>
+          <t>09:52:40</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.14</v>
+        <v>2.68</v>
       </c>
       <c r="F71" t="n">
-        <v>6.31</v>
+        <v>6.06</v>
       </c>
       <c r="G71" t="n">
-        <v>58.4</v>
+        <v>53.5</v>
       </c>
       <c r="H71" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
       <c r="I71" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J71" t="n">
-        <v>242.49</v>
+        <v>-40.7</v>
       </c>
       <c r="K71" t="n">
-        <v>-104.08</v>
+        <v>-29.28</v>
       </c>
       <c r="L71" t="n">
-        <v>263.89</v>
+        <v>50.14</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10:06:36</t>
+          <t>09:54:15</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="F72" t="n">
-        <v>6.62</v>
+        <v>6.48</v>
       </c>
       <c r="G72" t="n">
-        <v>42.2</v>
+        <v>41.1</v>
       </c>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="I72" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>42.87</v>
+        <v>-25.7</v>
       </c>
       <c r="K72" t="n">
-        <v>165.81</v>
+        <v>183.59</v>
       </c>
       <c r="L72" t="n">
-        <v>171.26</v>
+        <v>185.38</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10:07:58</t>
+          <t>09:55:19</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.38</v>
+        <v>2.64</v>
       </c>
       <c r="F73" t="n">
-        <v>5.84</v>
+        <v>5.41</v>
       </c>
       <c r="G73" t="n">
-        <v>52.6</v>
+        <v>44.5</v>
       </c>
       <c r="H73" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I73" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>-77.31999999999999</v>
+        <v>-260.45</v>
       </c>
       <c r="K73" t="n">
-        <v>-219.12</v>
+        <v>97.7</v>
       </c>
       <c r="L73" t="n">
-        <v>232.36</v>
+        <v>278.17</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10:15:37</t>
+          <t>10:06:24</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3148,31 +3148,31 @@
         <v>2.65</v>
       </c>
       <c r="F74" t="n">
-        <v>5.77</v>
+        <v>6.41</v>
       </c>
       <c r="G74" t="n">
-        <v>33.1</v>
+        <v>45.5</v>
       </c>
       <c r="H74" t="n">
-        <v>4.1</v>
+        <v>1.4</v>
       </c>
       <c r="I74" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>45.86</v>
+        <v>-49.3</v>
       </c>
       <c r="K74" t="n">
-        <v>-18.61</v>
+        <v>-5.02</v>
       </c>
       <c r="L74" t="n">
-        <v>49.49</v>
+        <v>49.56</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10:17:28</t>
+          <t>10:07:32</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3190,31 +3190,31 @@
         <v>2.57</v>
       </c>
       <c r="F75" t="n">
-        <v>6.2</v>
+        <v>5.94</v>
       </c>
       <c r="G75" t="n">
-        <v>50.9</v>
+        <v>52.4</v>
       </c>
       <c r="H75" t="n">
         <v>0</v>
       </c>
       <c r="I75" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>-34.09</v>
+        <v>-5.88</v>
       </c>
       <c r="K75" t="n">
-        <v>-83.93000000000001</v>
+        <v>37.01</v>
       </c>
       <c r="L75" t="n">
-        <v>90.59</v>
+        <v>37.47</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10:18:59</t>
+          <t>10:09:53</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>2.66</v>
+        <v>2.22</v>
       </c>
       <c r="F76" t="n">
-        <v>6.05</v>
+        <v>6.67</v>
       </c>
       <c r="G76" t="n">
-        <v>40.5</v>
+        <v>49</v>
       </c>
       <c r="H76" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>2.73</v>
+        <v>-38.93</v>
       </c>
       <c r="K76" t="n">
-        <v>134.85</v>
+        <v>-34.29</v>
       </c>
       <c r="L76" t="n">
-        <v>134.88</v>
+        <v>51.88</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10:23:27</t>
+          <t>10:15:48</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>2.7</v>
+        <v>2.54</v>
       </c>
       <c r="F77" t="n">
-        <v>5.39</v>
+        <v>6.59</v>
       </c>
       <c r="G77" t="n">
-        <v>50.1</v>
+        <v>65.3</v>
       </c>
       <c r="H77" t="n">
         <v>0</v>
       </c>
       <c r="I77" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>-125.99</v>
+        <v>-59.76</v>
       </c>
       <c r="K77" t="n">
-        <v>-99.45</v>
+        <v>63.95</v>
       </c>
       <c r="L77" t="n">
-        <v>160.51</v>
+        <v>87.53</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>10:24:41</t>
+          <t>10:17:59</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2.91</v>
+        <v>2.73</v>
       </c>
       <c r="F78" t="n">
-        <v>5.16</v>
+        <v>5.62</v>
       </c>
       <c r="G78" t="n">
-        <v>42.6</v>
+        <v>45.1</v>
       </c>
       <c r="H78" t="n">
-        <v>5.7</v>
+        <v>4.8</v>
       </c>
       <c r="I78" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J78" t="n">
-        <v>174.32</v>
+        <v>-71.53</v>
       </c>
       <c r="K78" t="n">
-        <v>-88.97</v>
+        <v>-50.83</v>
       </c>
       <c r="L78" t="n">
-        <v>195.72</v>
+        <v>87.75</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>10:26:43</t>
+          <t>10:20:18</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.87</v>
+        <v>2.62</v>
       </c>
       <c r="F79" t="n">
-        <v>6.23</v>
+        <v>5.8</v>
       </c>
       <c r="G79" t="n">
-        <v>41.9</v>
+        <v>38.4</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J79" t="n">
-        <v>23.57</v>
+        <v>57.22</v>
       </c>
       <c r="K79" t="n">
-        <v>82.08</v>
+        <v>-7.43</v>
       </c>
       <c r="L79" t="n">
-        <v>85.39</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>10:31:13</t>
+          <t>10:24:30</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="F80" t="n">
-        <v>5.61</v>
+        <v>6.19</v>
       </c>
       <c r="G80" t="n">
-        <v>65.40000000000001</v>
+        <v>48.3</v>
       </c>
       <c r="H80" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I80" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>124.04</v>
+        <v>54.34</v>
       </c>
       <c r="K80" t="n">
-        <v>18.4</v>
+        <v>57.55</v>
       </c>
       <c r="L80" t="n">
-        <v>125.4</v>
+        <v>79.15000000000001</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10:33:32</t>
+          <t>10:25:50</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2.64</v>
+        <v>2.95</v>
       </c>
       <c r="F81" t="n">
-        <v>5.92</v>
+        <v>5.75</v>
       </c>
       <c r="G81" t="n">
-        <v>48.4</v>
+        <v>46.5</v>
       </c>
       <c r="H81" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="I81" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>72.75</v>
+        <v>36.23</v>
       </c>
       <c r="K81" t="n">
-        <v>-109.2</v>
+        <v>-79.79000000000001</v>
       </c>
       <c r="L81" t="n">
-        <v>131.21</v>
+        <v>87.63</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10:34:39</t>
+          <t>10:27:55</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.13</v>
+        <v>2.18</v>
       </c>
       <c r="F82" t="n">
-        <v>5.66</v>
+        <v>5.63</v>
       </c>
       <c r="G82" t="n">
-        <v>53.2</v>
+        <v>53.9</v>
       </c>
       <c r="H82" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="I82" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>-14.15</v>
+        <v>-93.09</v>
       </c>
       <c r="K82" t="n">
-        <v>64.33</v>
+        <v>-85.05</v>
       </c>
       <c r="L82" t="n">
-        <v>65.87</v>
+        <v>126.09</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10:38:35</t>
+          <t>10:32:45</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.71</v>
+        <v>2.39</v>
       </c>
       <c r="F83" t="n">
-        <v>6.08</v>
+        <v>5.91</v>
       </c>
       <c r="G83" t="n">
-        <v>53.4</v>
+        <v>35.5</v>
       </c>
       <c r="H83" t="n">
-        <v>5.9</v>
+        <v>0.6</v>
       </c>
       <c r="I83" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>-63.55</v>
+        <v>-127.85</v>
       </c>
       <c r="K83" t="n">
-        <v>-155.21</v>
+        <v>27.49</v>
       </c>
       <c r="L83" t="n">
-        <v>167.72</v>
+        <v>130.77</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10:40:51</t>
+          <t>10:34:19</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2.68</v>
+        <v>2.12</v>
       </c>
       <c r="F84" t="n">
-        <v>5.65</v>
+        <v>6.27</v>
       </c>
       <c r="G84" t="n">
-        <v>53.6</v>
+        <v>31.3</v>
       </c>
       <c r="H84" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="I84" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>-176.68</v>
+        <v>-45.57</v>
       </c>
       <c r="K84" t="n">
-        <v>-28.04</v>
+        <v>122.14</v>
       </c>
       <c r="L84" t="n">
-        <v>178.89</v>
+        <v>130.37</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10:42:37</t>
+          <t>10:36:34</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>2.74</v>
+        <v>2.42</v>
       </c>
       <c r="F85" t="n">
-        <v>5.34</v>
+        <v>6.22</v>
       </c>
       <c r="G85" t="n">
-        <v>58.8</v>
+        <v>55.8</v>
       </c>
       <c r="H85" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>-102.46</v>
+        <v>-32.75</v>
       </c>
       <c r="K85" t="n">
-        <v>-129.59</v>
+        <v>-126.22</v>
       </c>
       <c r="L85" t="n">
-        <v>165.21</v>
+        <v>130.4</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10:47:39</t>
+          <t>10:41:32</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>2.48</v>
+        <v>2.26</v>
       </c>
       <c r="F86" t="n">
-        <v>5.58</v>
+        <v>5.29</v>
       </c>
       <c r="G86" t="n">
-        <v>49.4</v>
+        <v>50.1</v>
       </c>
       <c r="H86" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="I86" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="J86" t="n">
-        <v>59.02</v>
+        <v>-122.38</v>
       </c>
       <c r="K86" t="n">
-        <v>104.76</v>
+        <v>-80.48999999999999</v>
       </c>
       <c r="L86" t="n">
-        <v>120.24</v>
+        <v>146.48</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10:48:56</t>
+          <t>10:43:21</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="F87" t="n">
-        <v>6.18</v>
+        <v>6.08</v>
       </c>
       <c r="G87" t="n">
-        <v>62.5</v>
+        <v>46</v>
       </c>
       <c r="H87" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="I87" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>140.36</v>
+        <v>129.29</v>
       </c>
       <c r="K87" t="n">
-        <v>-176.38</v>
+        <v>-134.85</v>
       </c>
       <c r="L87" t="n">
-        <v>225.41</v>
+        <v>186.82</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10:49:47</t>
+          <t>10:44:10</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>2.49</v>
+        <v>2.63</v>
       </c>
       <c r="F88" t="n">
-        <v>6.24</v>
+        <v>6.69</v>
       </c>
       <c r="G88" t="n">
-        <v>46.3</v>
+        <v>49.6</v>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="I88" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J88" t="n">
-        <v>66.12</v>
+        <v>-127.79</v>
       </c>
       <c r="K88" t="n">
-        <v>88.88</v>
+        <v>-110.63</v>
       </c>
       <c r="L88" t="n">
-        <v>110.78</v>
+        <v>169.03</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-10-01.xlsx
+++ b/output/2025-10-01.xlsx
@@ -640,13 +640,13 @@
         <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>40.21</v>
+        <v>39.68</v>
       </c>
       <c r="K14" t="n">
-        <v>14.9</v>
+        <v>14.7</v>
       </c>
       <c r="L14" t="n">
-        <v>42.88</v>
+        <v>42.31</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>30.73</v>
+        <v>31.82</v>
       </c>
       <c r="K15" t="n">
-        <v>-5.77</v>
+        <v>-5.97</v>
       </c>
       <c r="L15" t="n">
-        <v>31.27</v>
+        <v>32.38</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>-52.3</v>
+        <v>-50.92</v>
       </c>
       <c r="K16" t="n">
-        <v>14.51</v>
+        <v>14.13</v>
       </c>
       <c r="L16" t="n">
-        <v>54.28</v>
+        <v>52.84</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>35.72</v>
+        <v>35.13</v>
       </c>
       <c r="K17" t="n">
-        <v>50.11</v>
+        <v>49.28</v>
       </c>
       <c r="L17" t="n">
-        <v>61.53</v>
+        <v>60.52</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>23</v>
       </c>
       <c r="J18" t="n">
-        <v>-90.84999999999999</v>
+        <v>-80.94</v>
       </c>
       <c r="K18" t="n">
-        <v>-45.96</v>
+        <v>-40.95</v>
       </c>
       <c r="L18" t="n">
-        <v>101.81</v>
+        <v>90.70999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>63.8</v>
+        <v>61.48</v>
       </c>
       <c r="K19" t="n">
-        <v>56.3</v>
+        <v>54.25</v>
       </c>
       <c r="L19" t="n">
-        <v>85.09</v>
+        <v>81.98999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>-60.4</v>
+        <v>-61.12</v>
       </c>
       <c r="K20" t="n">
-        <v>-48.4</v>
+        <v>-48.97</v>
       </c>
       <c r="L20" t="n">
-        <v>77.40000000000001</v>
+        <v>78.31</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>19.41</v>
+        <v>20.17</v>
       </c>
       <c r="K21" t="n">
-        <v>-57.5</v>
+        <v>-59.76</v>
       </c>
       <c r="L21" t="n">
-        <v>60.68</v>
+        <v>63.07</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>-59.3</v>
+        <v>-60.42</v>
       </c>
       <c r="K22" t="n">
-        <v>28.51</v>
+        <v>29.05</v>
       </c>
       <c r="L22" t="n">
-        <v>65.8</v>
+        <v>67.04000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>25</v>
       </c>
       <c r="J23" t="n">
-        <v>-75.73</v>
+        <v>-77.23</v>
       </c>
       <c r="K23" t="n">
-        <v>44.55</v>
+        <v>45.44</v>
       </c>
       <c r="L23" t="n">
-        <v>87.86</v>
+        <v>89.61</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>125.37</v>
+        <v>119.85</v>
       </c>
       <c r="K24" t="n">
-        <v>-125.73</v>
+        <v>-120.19</v>
       </c>
       <c r="L24" t="n">
-        <v>177.55</v>
+        <v>169.73</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.19</v>
+        <v>-1.28</v>
       </c>
       <c r="K25" t="n">
-        <v>-62.57</v>
+        <v>-67.28</v>
       </c>
       <c r="L25" t="n">
-        <v>62.58</v>
+        <v>67.29000000000001</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>-194.04</v>
+        <v>-188.5</v>
       </c>
       <c r="K26" t="n">
-        <v>-46.51</v>
+        <v>-45.18</v>
       </c>
       <c r="L26" t="n">
-        <v>199.54</v>
+        <v>193.84</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>24</v>
       </c>
       <c r="J27" t="n">
-        <v>173.53</v>
+        <v>170.5</v>
       </c>
       <c r="K27" t="n">
-        <v>41.01</v>
+        <v>40.3</v>
       </c>
       <c r="L27" t="n">
-        <v>178.31</v>
+        <v>175.2</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>19</v>
       </c>
       <c r="J28" t="n">
-        <v>-85.06</v>
+        <v>-82.44</v>
       </c>
       <c r="K28" t="n">
-        <v>207.73</v>
+        <v>201.34</v>
       </c>
       <c r="L28" t="n">
-        <v>224.47</v>
+        <v>217.56</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>18.12</v>
+        <v>18.87</v>
       </c>
       <c r="K29" t="n">
-        <v>-28.23</v>
+        <v>-29.4</v>
       </c>
       <c r="L29" t="n">
-        <v>33.55</v>
+        <v>34.93</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>11.2</v>
+        <v>11.06</v>
       </c>
       <c r="K30" t="n">
-        <v>-54.37</v>
+        <v>-53.71</v>
       </c>
       <c r="L30" t="n">
-        <v>55.51</v>
+        <v>54.83</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>49.27</v>
+        <v>47.88</v>
       </c>
       <c r="K31" t="n">
-        <v>-27.97</v>
+        <v>-27.18</v>
       </c>
       <c r="L31" t="n">
-        <v>56.65</v>
+        <v>55.06</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>33.23</v>
+        <v>35.97</v>
       </c>
       <c r="K32" t="n">
-        <v>7.37</v>
+        <v>7.98</v>
       </c>
       <c r="L32" t="n">
-        <v>34.04</v>
+        <v>36.84</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>19</v>
       </c>
       <c r="J33" t="n">
-        <v>-73.87</v>
+        <v>-71.12</v>
       </c>
       <c r="K33" t="n">
-        <v>-53.62</v>
+        <v>-51.62</v>
       </c>
       <c r="L33" t="n">
-        <v>91.28</v>
+        <v>87.88</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>65.98</v>
+        <v>63.99</v>
       </c>
       <c r="K34" t="n">
-        <v>36.6</v>
+        <v>35.5</v>
       </c>
       <c r="L34" t="n">
-        <v>75.45</v>
+        <v>73.18000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>25</v>
       </c>
       <c r="J35" t="n">
-        <v>78.59</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>12.24</v>
+        <v>12.2</v>
       </c>
       <c r="L35" t="n">
-        <v>79.54000000000001</v>
+        <v>79.29000000000001</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>25</v>
       </c>
       <c r="J36" t="n">
-        <v>82.88</v>
+        <v>81.19</v>
       </c>
       <c r="K36" t="n">
-        <v>-45.53</v>
+        <v>-44.6</v>
       </c>
       <c r="L36" t="n">
-        <v>94.56</v>
+        <v>92.64</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>-32.85</v>
+        <v>-33.59</v>
       </c>
       <c r="K37" t="n">
-        <v>-61.52</v>
+        <v>-62.91</v>
       </c>
       <c r="L37" t="n">
-        <v>69.73999999999999</v>
+        <v>71.31999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>25</v>
       </c>
       <c r="J38" t="n">
-        <v>57.02</v>
+        <v>57.46</v>
       </c>
       <c r="K38" t="n">
-        <v>-79.51000000000001</v>
+        <v>-80.12</v>
       </c>
       <c r="L38" t="n">
-        <v>97.84</v>
+        <v>98.59</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>-156.11</v>
+        <v>-149.97</v>
       </c>
       <c r="K39" t="n">
-        <v>-8.4</v>
+        <v>-8.07</v>
       </c>
       <c r="L39" t="n">
-        <v>156.33</v>
+        <v>150.19</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>19</v>
       </c>
       <c r="J40" t="n">
-        <v>128.36</v>
+        <v>127.69</v>
       </c>
       <c r="K40" t="n">
-        <v>21.2</v>
+        <v>21.09</v>
       </c>
       <c r="L40" t="n">
-        <v>130.09</v>
+        <v>129.42</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>23</v>
       </c>
       <c r="J41" t="n">
-        <v>-218.77</v>
+        <v>-209.79</v>
       </c>
       <c r="K41" t="n">
-        <v>93.08</v>
+        <v>89.26000000000001</v>
       </c>
       <c r="L41" t="n">
-        <v>237.75</v>
+        <v>227.99</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="K42" t="n">
-        <v>86.2</v>
+        <v>94.15000000000001</v>
       </c>
       <c r="L42" t="n">
-        <v>86.23</v>
+        <v>94.17</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>122.43</v>
+        <v>127.04</v>
       </c>
       <c r="K43" t="n">
-        <v>6.63</v>
+        <v>6.88</v>
       </c>
       <c r="L43" t="n">
-        <v>122.61</v>
+        <v>127.23</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>58.26</v>
+        <v>56.28</v>
       </c>
       <c r="K44" t="n">
-        <v>26.62</v>
+        <v>25.72</v>
       </c>
       <c r="L44" t="n">
-        <v>64.05</v>
+        <v>61.88</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>19</v>
       </c>
       <c r="J45" t="n">
-        <v>-34.61</v>
+        <v>-34.07</v>
       </c>
       <c r="K45" t="n">
-        <v>-41.7</v>
+        <v>-41.04</v>
       </c>
       <c r="L45" t="n">
-        <v>54.19</v>
+        <v>53.34</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>45.06</v>
+        <v>44.99</v>
       </c>
       <c r="K46" t="n">
-        <v>-4.85</v>
+        <v>-4.84</v>
       </c>
       <c r="L46" t="n">
-        <v>45.32</v>
+        <v>45.25</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>0.98</v>
+        <v>0.96</v>
       </c>
       <c r="K47" t="n">
-        <v>-17.59</v>
+        <v>-17.21</v>
       </c>
       <c r="L47" t="n">
-        <v>17.62</v>
+        <v>17.24</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>25</v>
       </c>
       <c r="J48" t="n">
-        <v>72.58</v>
+        <v>70.17</v>
       </c>
       <c r="K48" t="n">
-        <v>24.8</v>
+        <v>23.98</v>
       </c>
       <c r="L48" t="n">
-        <v>76.7</v>
+        <v>74.16</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>26.95</v>
+        <v>26.07</v>
       </c>
       <c r="K49" t="n">
-        <v>74.66</v>
+        <v>72.22</v>
       </c>
       <c r="L49" t="n">
-        <v>79.37</v>
+        <v>76.79000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>-61.17</v>
+        <v>-61.16</v>
       </c>
       <c r="K50" t="n">
-        <v>52.86</v>
+        <v>52.85</v>
       </c>
       <c r="L50" t="n">
-        <v>80.84</v>
+        <v>80.83</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>25</v>
       </c>
       <c r="J51" t="n">
-        <v>-66.02</v>
+        <v>-65.06999999999999</v>
       </c>
       <c r="K51" t="n">
-        <v>59.14</v>
+        <v>58.29</v>
       </c>
       <c r="L51" t="n">
-        <v>88.63</v>
+        <v>87.36</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>87.02</v>
+        <v>86.01000000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>12.78</v>
+        <v>12.64</v>
       </c>
       <c r="L52" t="n">
-        <v>87.95</v>
+        <v>86.93000000000001</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>123.87</v>
+        <v>122.2</v>
       </c>
       <c r="K53" t="n">
-        <v>10.68</v>
+        <v>10.53</v>
       </c>
       <c r="L53" t="n">
-        <v>124.33</v>
+        <v>122.65</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>21</v>
       </c>
       <c r="J54" t="n">
-        <v>91.58</v>
+        <v>90.20999999999999</v>
       </c>
       <c r="K54" t="n">
-        <v>-88.73999999999999</v>
+        <v>-87.42</v>
       </c>
       <c r="L54" t="n">
-        <v>127.52</v>
+        <v>125.62</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>19</v>
       </c>
       <c r="J55" t="n">
-        <v>82.45</v>
+        <v>79.28</v>
       </c>
       <c r="K55" t="n">
-        <v>-153.94</v>
+        <v>-148.03</v>
       </c>
       <c r="L55" t="n">
-        <v>174.63</v>
+        <v>167.92</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>215.2</v>
+        <v>205.16</v>
       </c>
       <c r="K56" t="n">
-        <v>124.46</v>
+        <v>118.65</v>
       </c>
       <c r="L56" t="n">
-        <v>248.6</v>
+        <v>237</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>21</v>
       </c>
       <c r="J57" t="n">
-        <v>35.42</v>
+        <v>34.74</v>
       </c>
       <c r="K57" t="n">
-        <v>192.95</v>
+        <v>189.23</v>
       </c>
       <c r="L57" t="n">
-        <v>196.18</v>
+        <v>192.39</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>20</v>
       </c>
       <c r="J58" t="n">
-        <v>4.74</v>
+        <v>4.68</v>
       </c>
       <c r="K58" t="n">
-        <v>184.88</v>
+        <v>182.38</v>
       </c>
       <c r="L58" t="n">
-        <v>184.94</v>
+        <v>182.44</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>21.26</v>
+        <v>21.88</v>
       </c>
       <c r="K59" t="n">
-        <v>-34.77</v>
+        <v>-35.78</v>
       </c>
       <c r="L59" t="n">
-        <v>40.75</v>
+        <v>41.94</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>-50.22</v>
+        <v>-47.85</v>
       </c>
       <c r="K60" t="n">
-        <v>57.69</v>
+        <v>54.97</v>
       </c>
       <c r="L60" t="n">
-        <v>76.48999999999999</v>
+        <v>72.88</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>-31.99</v>
+        <v>-33.08</v>
       </c>
       <c r="K61" t="n">
-        <v>-7.01</v>
+        <v>-7.25</v>
       </c>
       <c r="L61" t="n">
-        <v>32.74</v>
+        <v>33.87</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-68.90000000000001</v>
+        <v>-66.48</v>
       </c>
       <c r="K62" t="n">
-        <v>47.96</v>
+        <v>46.28</v>
       </c>
       <c r="L62" t="n">
-        <v>83.95</v>
+        <v>81</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>21</v>
       </c>
       <c r="J63" t="n">
-        <v>34.85</v>
+        <v>37.6</v>
       </c>
       <c r="K63" t="n">
-        <v>-13.27</v>
+        <v>-14.32</v>
       </c>
       <c r="L63" t="n">
-        <v>37.29</v>
+        <v>40.23</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>22</v>
       </c>
       <c r="J64" t="n">
-        <v>-36.75</v>
+        <v>-35.69</v>
       </c>
       <c r="K64" t="n">
-        <v>-66.34999999999999</v>
+        <v>-64.43000000000001</v>
       </c>
       <c r="L64" t="n">
-        <v>75.84999999999999</v>
+        <v>73.65000000000001</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>20</v>
       </c>
       <c r="J65" t="n">
-        <v>18.11</v>
+        <v>18.16</v>
       </c>
       <c r="K65" t="n">
-        <v>87.95</v>
+        <v>88.16</v>
       </c>
       <c r="L65" t="n">
-        <v>89.79000000000001</v>
+        <v>90.01000000000001</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>22</v>
       </c>
       <c r="J66" t="n">
-        <v>-29.09</v>
+        <v>-28.59</v>
       </c>
       <c r="K66" t="n">
-        <v>-93.69</v>
+        <v>-92.06</v>
       </c>
       <c r="L66" t="n">
-        <v>98.09999999999999</v>
+        <v>96.40000000000001</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>20</v>
       </c>
       <c r="J67" t="n">
-        <v>115.67</v>
+        <v>111.17</v>
       </c>
       <c r="K67" t="n">
-        <v>-51.61</v>
+        <v>-49.6</v>
       </c>
       <c r="L67" t="n">
-        <v>126.66</v>
+        <v>121.74</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>20</v>
       </c>
       <c r="J68" t="n">
-        <v>-125.91</v>
+        <v>-123.95</v>
       </c>
       <c r="K68" t="n">
-        <v>-52.04</v>
+        <v>-51.23</v>
       </c>
       <c r="L68" t="n">
-        <v>136.24</v>
+        <v>134.12</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>-106.83</v>
+        <v>-107.17</v>
       </c>
       <c r="K69" t="n">
-        <v>-24.59</v>
+        <v>-24.67</v>
       </c>
       <c r="L69" t="n">
-        <v>109.63</v>
+        <v>109.97</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>-75.02</v>
+        <v>-79.02</v>
       </c>
       <c r="K70" t="n">
-        <v>-12.2</v>
+        <v>-12.85</v>
       </c>
       <c r="L70" t="n">
-        <v>76.01000000000001</v>
+        <v>80.06</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>23</v>
       </c>
       <c r="J71" t="n">
-        <v>-40.7</v>
+        <v>-39.81</v>
       </c>
       <c r="K71" t="n">
-        <v>-29.28</v>
+        <v>-28.64</v>
       </c>
       <c r="L71" t="n">
-        <v>50.14</v>
+        <v>49.05</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>-25.7</v>
+        <v>-25.48</v>
       </c>
       <c r="K72" t="n">
-        <v>183.59</v>
+        <v>181.97</v>
       </c>
       <c r="L72" t="n">
-        <v>185.38</v>
+        <v>183.75</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>-260.45</v>
+        <v>-247.06</v>
       </c>
       <c r="K73" t="n">
-        <v>97.7</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="L73" t="n">
-        <v>278.17</v>
+        <v>263.87</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>-49.3</v>
+        <v>-49.13</v>
       </c>
       <c r="K74" t="n">
-        <v>-5.02</v>
+        <v>-5</v>
       </c>
       <c r="L74" t="n">
-        <v>49.56</v>
+        <v>49.38</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>-5.88</v>
+        <v>-6.08</v>
       </c>
       <c r="K75" t="n">
-        <v>37.01</v>
+        <v>38.28</v>
       </c>
       <c r="L75" t="n">
-        <v>37.47</v>
+        <v>38.76</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>-38.93</v>
+        <v>-38.08</v>
       </c>
       <c r="K76" t="n">
-        <v>-34.29</v>
+        <v>-33.55</v>
       </c>
       <c r="L76" t="n">
-        <v>51.88</v>
+        <v>50.75</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>-59.76</v>
+        <v>-57.57</v>
       </c>
       <c r="K77" t="n">
-        <v>63.95</v>
+        <v>61.61</v>
       </c>
       <c r="L77" t="n">
-        <v>87.53</v>
+        <v>84.31999999999999</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>19</v>
       </c>
       <c r="J78" t="n">
-        <v>-71.53</v>
+        <v>-69.59</v>
       </c>
       <c r="K78" t="n">
-        <v>-50.83</v>
+        <v>-49.45</v>
       </c>
       <c r="L78" t="n">
-        <v>87.75</v>
+        <v>85.37</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>21</v>
       </c>
       <c r="J79" t="n">
-        <v>57.22</v>
+        <v>58.05</v>
       </c>
       <c r="K79" t="n">
-        <v>-7.43</v>
+        <v>-7.54</v>
       </c>
       <c r="L79" t="n">
-        <v>57.7</v>
+        <v>58.54</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>54.34</v>
+        <v>54.92</v>
       </c>
       <c r="K80" t="n">
-        <v>57.55</v>
+        <v>58.18</v>
       </c>
       <c r="L80" t="n">
-        <v>79.15000000000001</v>
+        <v>80.01000000000001</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>36.23</v>
+        <v>36.56</v>
       </c>
       <c r="K81" t="n">
-        <v>-79.79000000000001</v>
+        <v>-80.52</v>
       </c>
       <c r="L81" t="n">
-        <v>87.63</v>
+        <v>88.43000000000001</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>-93.09</v>
+        <v>-89.51000000000001</v>
       </c>
       <c r="K82" t="n">
-        <v>-85.05</v>
+        <v>-81.78</v>
       </c>
       <c r="L82" t="n">
-        <v>126.09</v>
+        <v>121.25</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>-127.85</v>
+        <v>-126.7</v>
       </c>
       <c r="K83" t="n">
-        <v>27.49</v>
+        <v>27.24</v>
       </c>
       <c r="L83" t="n">
-        <v>130.77</v>
+        <v>129.59</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>-45.57</v>
+        <v>-44.86</v>
       </c>
       <c r="K84" t="n">
-        <v>122.14</v>
+        <v>120.24</v>
       </c>
       <c r="L84" t="n">
-        <v>130.37</v>
+        <v>128.34</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>-32.75</v>
+        <v>-32.28</v>
       </c>
       <c r="K85" t="n">
-        <v>-126.22</v>
+        <v>-124.37</v>
       </c>
       <c r="L85" t="n">
-        <v>130.4</v>
+        <v>128.49</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>19</v>
       </c>
       <c r="J86" t="n">
-        <v>-122.38</v>
+        <v>-125.44</v>
       </c>
       <c r="K86" t="n">
-        <v>-80.48999999999999</v>
+        <v>-82.5</v>
       </c>
       <c r="L86" t="n">
-        <v>146.48</v>
+        <v>150.14</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>129.29</v>
+        <v>127.14</v>
       </c>
       <c r="K87" t="n">
-        <v>-134.85</v>
+        <v>-132.61</v>
       </c>
       <c r="L87" t="n">
-        <v>186.82</v>
+        <v>183.71</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>19</v>
       </c>
       <c r="J88" t="n">
-        <v>-127.79</v>
+        <v>-128.76</v>
       </c>
       <c r="K88" t="n">
-        <v>-110.63</v>
+        <v>-111.46</v>
       </c>
       <c r="L88" t="n">
-        <v>169.03</v>
+        <v>170.3</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-10-01.xlsx
+++ b/output/2025-10-01.xlsx
@@ -640,13 +640,13 @@
         <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>39.68</v>
+        <v>39.07</v>
       </c>
       <c r="K14" t="n">
-        <v>14.7</v>
+        <v>14.48</v>
       </c>
       <c r="L14" t="n">
-        <v>42.31</v>
+        <v>41.66</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>31.82</v>
+        <v>33.08</v>
       </c>
       <c r="K15" t="n">
-        <v>-5.97</v>
+        <v>-6.21</v>
       </c>
       <c r="L15" t="n">
-        <v>32.38</v>
+        <v>33.65</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>-50.92</v>
+        <v>-49.33</v>
       </c>
       <c r="K16" t="n">
-        <v>14.13</v>
+        <v>13.69</v>
       </c>
       <c r="L16" t="n">
-        <v>52.84</v>
+        <v>51.2</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>35.13</v>
+        <v>34.45</v>
       </c>
       <c r="K17" t="n">
-        <v>49.28</v>
+        <v>48.34</v>
       </c>
       <c r="L17" t="n">
-        <v>60.52</v>
+        <v>59.36</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>23</v>
       </c>
       <c r="J18" t="n">
-        <v>-80.94</v>
+        <v>-76.54000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>-40.95</v>
+        <v>-38.72</v>
       </c>
       <c r="L18" t="n">
-        <v>90.70999999999999</v>
+        <v>85.78</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>61.48</v>
+        <v>58.82</v>
       </c>
       <c r="K19" t="n">
-        <v>54.25</v>
+        <v>51.9</v>
       </c>
       <c r="L19" t="n">
-        <v>81.98999999999999</v>
+        <v>78.45</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>-61.12</v>
+        <v>-61.93</v>
       </c>
       <c r="K20" t="n">
-        <v>-48.97</v>
+        <v>-49.62</v>
       </c>
       <c r="L20" t="n">
-        <v>78.31</v>
+        <v>79.36</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>20.17</v>
+        <v>21.05</v>
       </c>
       <c r="K21" t="n">
-        <v>-59.76</v>
+        <v>-62.34</v>
       </c>
       <c r="L21" t="n">
-        <v>63.07</v>
+        <v>65.8</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>-60.42</v>
+        <v>-61.7</v>
       </c>
       <c r="K22" t="n">
-        <v>29.05</v>
+        <v>29.66</v>
       </c>
       <c r="L22" t="n">
-        <v>67.04000000000001</v>
+        <v>68.45999999999999</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>25</v>
       </c>
       <c r="J23" t="n">
-        <v>-77.23</v>
+        <v>-78.95</v>
       </c>
       <c r="K23" t="n">
-        <v>45.44</v>
+        <v>46.45</v>
       </c>
       <c r="L23" t="n">
-        <v>89.61</v>
+        <v>91.59999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>119.85</v>
+        <v>113.54</v>
       </c>
       <c r="K24" t="n">
-        <v>-120.19</v>
+        <v>-113.87</v>
       </c>
       <c r="L24" t="n">
-        <v>169.73</v>
+        <v>160.8</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.28</v>
+        <v>-1.38</v>
       </c>
       <c r="K25" t="n">
-        <v>-67.28</v>
+        <v>-72.66</v>
       </c>
       <c r="L25" t="n">
-        <v>67.29000000000001</v>
+        <v>72.67</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>-188.5</v>
+        <v>-182.16</v>
       </c>
       <c r="K26" t="n">
-        <v>-45.18</v>
+        <v>-43.66</v>
       </c>
       <c r="L26" t="n">
-        <v>193.84</v>
+        <v>187.32</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>24</v>
       </c>
       <c r="J27" t="n">
-        <v>170.5</v>
+        <v>167.05</v>
       </c>
       <c r="K27" t="n">
-        <v>40.3</v>
+        <v>39.48</v>
       </c>
       <c r="L27" t="n">
-        <v>175.2</v>
+        <v>171.65</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>19</v>
       </c>
       <c r="J28" t="n">
-        <v>-82.44</v>
+        <v>-79.45</v>
       </c>
       <c r="K28" t="n">
-        <v>201.34</v>
+        <v>194.02</v>
       </c>
       <c r="L28" t="n">
-        <v>217.56</v>
+        <v>209.66</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>18.87</v>
+        <v>19.72</v>
       </c>
       <c r="K29" t="n">
-        <v>-29.4</v>
+        <v>-30.73</v>
       </c>
       <c r="L29" t="n">
-        <v>34.93</v>
+        <v>36.51</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>11.06</v>
+        <v>10.9</v>
       </c>
       <c r="K30" t="n">
-        <v>-53.71</v>
+        <v>-52.95</v>
       </c>
       <c r="L30" t="n">
-        <v>54.83</v>
+        <v>54.06</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>47.88</v>
+        <v>46.3</v>
       </c>
       <c r="K31" t="n">
-        <v>-27.18</v>
+        <v>-26.28</v>
       </c>
       <c r="L31" t="n">
-        <v>55.06</v>
+        <v>53.24</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>35.97</v>
+        <v>39.09</v>
       </c>
       <c r="K32" t="n">
-        <v>7.98</v>
+        <v>8.67</v>
       </c>
       <c r="L32" t="n">
-        <v>36.84</v>
+        <v>40.04</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>19</v>
       </c>
       <c r="J33" t="n">
-        <v>-71.12</v>
+        <v>-67.98</v>
       </c>
       <c r="K33" t="n">
-        <v>-51.62</v>
+        <v>-49.35</v>
       </c>
       <c r="L33" t="n">
-        <v>87.88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>63.99</v>
+        <v>61.73</v>
       </c>
       <c r="K34" t="n">
-        <v>35.5</v>
+        <v>34.24</v>
       </c>
       <c r="L34" t="n">
-        <v>73.18000000000001</v>
+        <v>70.59</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>25</v>
       </c>
       <c r="J35" t="n">
-        <v>78.34999999999999</v>
+        <v>78.06</v>
       </c>
       <c r="K35" t="n">
-        <v>12.2</v>
+        <v>12.15</v>
       </c>
       <c r="L35" t="n">
-        <v>79.29000000000001</v>
+        <v>79</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>25</v>
       </c>
       <c r="J36" t="n">
-        <v>81.19</v>
+        <v>79.27</v>
       </c>
       <c r="K36" t="n">
-        <v>-44.6</v>
+        <v>-43.55</v>
       </c>
       <c r="L36" t="n">
-        <v>92.64</v>
+        <v>90.44</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>-33.59</v>
+        <v>-34.44</v>
       </c>
       <c r="K37" t="n">
-        <v>-62.91</v>
+        <v>-64.5</v>
       </c>
       <c r="L37" t="n">
-        <v>71.31999999999999</v>
+        <v>73.12</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>25</v>
       </c>
       <c r="J38" t="n">
-        <v>57.46</v>
+        <v>57.96</v>
       </c>
       <c r="K38" t="n">
-        <v>-80.12</v>
+        <v>-80.81999999999999</v>
       </c>
       <c r="L38" t="n">
-        <v>98.59</v>
+        <v>99.45</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>-149.97</v>
+        <v>-142.96</v>
       </c>
       <c r="K39" t="n">
-        <v>-8.07</v>
+        <v>-7.69</v>
       </c>
       <c r="L39" t="n">
-        <v>150.19</v>
+        <v>143.17</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>19</v>
       </c>
       <c r="J40" t="n">
-        <v>127.69</v>
+        <v>126.92</v>
       </c>
       <c r="K40" t="n">
-        <v>21.09</v>
+        <v>20.96</v>
       </c>
       <c r="L40" t="n">
-        <v>129.42</v>
+        <v>128.64</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>23</v>
       </c>
       <c r="J41" t="n">
-        <v>-209.79</v>
+        <v>-199.54</v>
       </c>
       <c r="K41" t="n">
-        <v>89.26000000000001</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="L41" t="n">
-        <v>227.99</v>
+        <v>216.85</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>2.3</v>
+        <v>2.53</v>
       </c>
       <c r="K42" t="n">
-        <v>94.15000000000001</v>
+        <v>103.77</v>
       </c>
       <c r="L42" t="n">
-        <v>94.17</v>
+        <v>103.8</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>127.04</v>
+        <v>132.3</v>
       </c>
       <c r="K43" t="n">
-        <v>6.88</v>
+        <v>7.16</v>
       </c>
       <c r="L43" t="n">
-        <v>127.23</v>
+        <v>132.5</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>56.28</v>
+        <v>54.02</v>
       </c>
       <c r="K44" t="n">
-        <v>25.72</v>
+        <v>24.69</v>
       </c>
       <c r="L44" t="n">
-        <v>61.88</v>
+        <v>59.39</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>19</v>
       </c>
       <c r="J45" t="n">
-        <v>-34.07</v>
+        <v>-33.44</v>
       </c>
       <c r="K45" t="n">
-        <v>-41.04</v>
+        <v>-40.29</v>
       </c>
       <c r="L45" t="n">
-        <v>53.34</v>
+        <v>52.36</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>44.99</v>
+        <v>44.91</v>
       </c>
       <c r="K46" t="n">
-        <v>-4.84</v>
+        <v>-4.83</v>
       </c>
       <c r="L46" t="n">
-        <v>45.25</v>
+        <v>45.17</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>0.96</v>
+        <v>1.04</v>
       </c>
       <c r="K47" t="n">
-        <v>-17.21</v>
+        <v>-18.72</v>
       </c>
       <c r="L47" t="n">
-        <v>17.24</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>25</v>
       </c>
       <c r="J48" t="n">
-        <v>70.17</v>
+        <v>67.42</v>
       </c>
       <c r="K48" t="n">
-        <v>23.98</v>
+        <v>23.04</v>
       </c>
       <c r="L48" t="n">
-        <v>74.16</v>
+        <v>71.25</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>26.07</v>
+        <v>25.07</v>
       </c>
       <c r="K49" t="n">
-        <v>72.22</v>
+        <v>69.44</v>
       </c>
       <c r="L49" t="n">
-        <v>76.79000000000001</v>
+        <v>73.83</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>-61.16</v>
+        <v>-61.14</v>
       </c>
       <c r="K50" t="n">
-        <v>52.85</v>
+        <v>52.84</v>
       </c>
       <c r="L50" t="n">
-        <v>80.83</v>
+        <v>80.81</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>25</v>
       </c>
       <c r="J51" t="n">
-        <v>-65.06999999999999</v>
+        <v>-63.98</v>
       </c>
       <c r="K51" t="n">
-        <v>58.29</v>
+        <v>57.32</v>
       </c>
       <c r="L51" t="n">
-        <v>87.36</v>
+        <v>85.91</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>86.01000000000001</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="K52" t="n">
-        <v>12.64</v>
+        <v>12.47</v>
       </c>
       <c r="L52" t="n">
-        <v>86.93000000000001</v>
+        <v>85.77</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>122.2</v>
+        <v>120.29</v>
       </c>
       <c r="K53" t="n">
-        <v>10.53</v>
+        <v>10.37</v>
       </c>
       <c r="L53" t="n">
-        <v>122.65</v>
+        <v>120.74</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>21</v>
       </c>
       <c r="J54" t="n">
-        <v>90.20999999999999</v>
+        <v>88.65000000000001</v>
       </c>
       <c r="K54" t="n">
-        <v>-87.42</v>
+        <v>-85.91</v>
       </c>
       <c r="L54" t="n">
-        <v>125.62</v>
+        <v>123.45</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>19</v>
       </c>
       <c r="J55" t="n">
-        <v>79.28</v>
+        <v>75.67</v>
       </c>
       <c r="K55" t="n">
-        <v>-148.03</v>
+        <v>-141.28</v>
       </c>
       <c r="L55" t="n">
-        <v>167.92</v>
+        <v>160.26</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>205.16</v>
+        <v>193.69</v>
       </c>
       <c r="K56" t="n">
-        <v>118.65</v>
+        <v>112.01</v>
       </c>
       <c r="L56" t="n">
-        <v>237</v>
+        <v>223.74</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>21</v>
       </c>
       <c r="J57" t="n">
-        <v>34.74</v>
+        <v>33.96</v>
       </c>
       <c r="K57" t="n">
-        <v>189.23</v>
+        <v>184.97</v>
       </c>
       <c r="L57" t="n">
-        <v>192.39</v>
+        <v>188.07</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>20</v>
       </c>
       <c r="J58" t="n">
-        <v>4.68</v>
+        <v>4.6</v>
       </c>
       <c r="K58" t="n">
-        <v>182.38</v>
+        <v>179.53</v>
       </c>
       <c r="L58" t="n">
-        <v>182.44</v>
+        <v>179.59</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>21.88</v>
+        <v>22.59</v>
       </c>
       <c r="K59" t="n">
-        <v>-35.78</v>
+        <v>-36.93</v>
       </c>
       <c r="L59" t="n">
-        <v>41.94</v>
+        <v>43.29</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>-47.85</v>
+        <v>-45.14</v>
       </c>
       <c r="K60" t="n">
-        <v>54.97</v>
+        <v>51.87</v>
       </c>
       <c r="L60" t="n">
-        <v>72.88</v>
+        <v>68.76000000000001</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>-33.08</v>
+        <v>-34.34</v>
       </c>
       <c r="K61" t="n">
-        <v>-7.25</v>
+        <v>-7.52</v>
       </c>
       <c r="L61" t="n">
-        <v>33.87</v>
+        <v>35.15</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-66.48</v>
+        <v>-63.71</v>
       </c>
       <c r="K62" t="n">
-        <v>46.28</v>
+        <v>44.35</v>
       </c>
       <c r="L62" t="n">
-        <v>81</v>
+        <v>77.63</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>21</v>
       </c>
       <c r="J63" t="n">
-        <v>37.6</v>
+        <v>40.74</v>
       </c>
       <c r="K63" t="n">
-        <v>-14.32</v>
+        <v>-15.51</v>
       </c>
       <c r="L63" t="n">
-        <v>40.23</v>
+        <v>43.59</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>22</v>
       </c>
       <c r="J64" t="n">
-        <v>-35.69</v>
+        <v>-34.47</v>
       </c>
       <c r="K64" t="n">
-        <v>-64.43000000000001</v>
+        <v>-62.23</v>
       </c>
       <c r="L64" t="n">
-        <v>73.65000000000001</v>
+        <v>71.14</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>20</v>
       </c>
       <c r="J65" t="n">
-        <v>18.16</v>
+        <v>18.2</v>
       </c>
       <c r="K65" t="n">
-        <v>88.16</v>
+        <v>88.39</v>
       </c>
       <c r="L65" t="n">
-        <v>90.01000000000001</v>
+        <v>90.25</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>22</v>
       </c>
       <c r="J66" t="n">
-        <v>-28.59</v>
+        <v>-28.01</v>
       </c>
       <c r="K66" t="n">
-        <v>-92.06</v>
+        <v>-90.20999999999999</v>
       </c>
       <c r="L66" t="n">
-        <v>96.40000000000001</v>
+        <v>94.45</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>20</v>
       </c>
       <c r="J67" t="n">
-        <v>111.17</v>
+        <v>106.03</v>
       </c>
       <c r="K67" t="n">
-        <v>-49.6</v>
+        <v>-47.31</v>
       </c>
       <c r="L67" t="n">
-        <v>121.74</v>
+        <v>116.1</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>20</v>
       </c>
       <c r="J68" t="n">
-        <v>-123.95</v>
+        <v>-121.71</v>
       </c>
       <c r="K68" t="n">
-        <v>-51.23</v>
+        <v>-50.3</v>
       </c>
       <c r="L68" t="n">
-        <v>134.12</v>
+        <v>131.69</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>-107.17</v>
+        <v>-107.55</v>
       </c>
       <c r="K69" t="n">
-        <v>-24.67</v>
+        <v>-24.76</v>
       </c>
       <c r="L69" t="n">
-        <v>109.97</v>
+        <v>110.37</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>-79.02</v>
+        <v>-83.59999999999999</v>
       </c>
       <c r="K70" t="n">
-        <v>-12.85</v>
+        <v>-13.6</v>
       </c>
       <c r="L70" t="n">
-        <v>80.06</v>
+        <v>84.7</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>23</v>
       </c>
       <c r="J71" t="n">
-        <v>-39.81</v>
+        <v>-43.31</v>
       </c>
       <c r="K71" t="n">
-        <v>-28.64</v>
+        <v>-31.15</v>
       </c>
       <c r="L71" t="n">
-        <v>49.05</v>
+        <v>53.35</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>-25.48</v>
+        <v>-25.22</v>
       </c>
       <c r="K72" t="n">
-        <v>181.97</v>
+        <v>180.12</v>
       </c>
       <c r="L72" t="n">
-        <v>183.75</v>
+        <v>181.88</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>-247.06</v>
+        <v>-231.75</v>
       </c>
       <c r="K73" t="n">
-        <v>92.68000000000001</v>
+        <v>86.93000000000001</v>
       </c>
       <c r="L73" t="n">
-        <v>263.87</v>
+        <v>247.52</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>-49.13</v>
+        <v>-48.93</v>
       </c>
       <c r="K74" t="n">
-        <v>-5</v>
+        <v>-4.98</v>
       </c>
       <c r="L74" t="n">
-        <v>49.38</v>
+        <v>49.18</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>-6.08</v>
+        <v>-6.31</v>
       </c>
       <c r="K75" t="n">
-        <v>38.28</v>
+        <v>39.74</v>
       </c>
       <c r="L75" t="n">
-        <v>38.76</v>
+        <v>40.24</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>-38.08</v>
+        <v>-37.12</v>
       </c>
       <c r="K76" t="n">
-        <v>-33.55</v>
+        <v>-32.7</v>
       </c>
       <c r="L76" t="n">
-        <v>50.75</v>
+        <v>49.46</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>-57.57</v>
+        <v>-55.07</v>
       </c>
       <c r="K77" t="n">
-        <v>61.61</v>
+        <v>58.94</v>
       </c>
       <c r="L77" t="n">
-        <v>84.31999999999999</v>
+        <v>80.66</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>19</v>
       </c>
       <c r="J78" t="n">
-        <v>-69.59</v>
+        <v>-67.38</v>
       </c>
       <c r="K78" t="n">
-        <v>-49.45</v>
+        <v>-47.88</v>
       </c>
       <c r="L78" t="n">
-        <v>85.37</v>
+        <v>82.66</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>21</v>
       </c>
       <c r="J79" t="n">
-        <v>58.05</v>
+        <v>59</v>
       </c>
       <c r="K79" t="n">
-        <v>-7.54</v>
+        <v>-7.67</v>
       </c>
       <c r="L79" t="n">
-        <v>58.54</v>
+        <v>59.49</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>54.92</v>
+        <v>55.6</v>
       </c>
       <c r="K80" t="n">
-        <v>58.18</v>
+        <v>58.89</v>
       </c>
       <c r="L80" t="n">
-        <v>80.01000000000001</v>
+        <v>80.98999999999999</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>36.56</v>
+        <v>36.94</v>
       </c>
       <c r="K81" t="n">
-        <v>-80.52</v>
+        <v>-81.34999999999999</v>
       </c>
       <c r="L81" t="n">
-        <v>88.43000000000001</v>
+        <v>89.34</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>-89.51000000000001</v>
+        <v>-85.43000000000001</v>
       </c>
       <c r="K82" t="n">
-        <v>-81.78</v>
+        <v>-78.05</v>
       </c>
       <c r="L82" t="n">
-        <v>121.25</v>
+        <v>115.72</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>-126.7</v>
+        <v>-125.37</v>
       </c>
       <c r="K83" t="n">
-        <v>27.24</v>
+        <v>26.95</v>
       </c>
       <c r="L83" t="n">
-        <v>129.59</v>
+        <v>128.24</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>-44.86</v>
+        <v>-44.05</v>
       </c>
       <c r="K84" t="n">
-        <v>120.24</v>
+        <v>118.06</v>
       </c>
       <c r="L84" t="n">
-        <v>128.34</v>
+        <v>126.02</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>-32.28</v>
+        <v>-31.73</v>
       </c>
       <c r="K85" t="n">
-        <v>-124.37</v>
+        <v>-122.27</v>
       </c>
       <c r="L85" t="n">
-        <v>128.49</v>
+        <v>126.32</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>19</v>
       </c>
       <c r="J86" t="n">
-        <v>-125.44</v>
+        <v>-128.94</v>
       </c>
       <c r="K86" t="n">
-        <v>-82.5</v>
+        <v>-84.8</v>
       </c>
       <c r="L86" t="n">
-        <v>150.14</v>
+        <v>154.32</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>127.14</v>
+        <v>124.68</v>
       </c>
       <c r="K87" t="n">
-        <v>-132.61</v>
+        <v>-130.04</v>
       </c>
       <c r="L87" t="n">
-        <v>183.71</v>
+        <v>180.15</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>19</v>
       </c>
       <c r="J88" t="n">
-        <v>-128.76</v>
+        <v>-129.86</v>
       </c>
       <c r="K88" t="n">
-        <v>-111.46</v>
+        <v>-112.42</v>
       </c>
       <c r="L88" t="n">
-        <v>170.3</v>
+        <v>171.76</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-10-01.xlsx
+++ b/output/2025-10-01.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1.61</v>
+        <v>2.02</v>
       </c>
       <c r="F14" t="n">
-        <v>6.49</v>
+        <v>4.07</v>
       </c>
       <c r="G14" t="n">
-        <v>52.1</v>
+        <v>49.3</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="I14" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J14" t="n">
-        <v>39.07</v>
+        <v>-34.75</v>
       </c>
       <c r="K14" t="n">
-        <v>14.48</v>
+        <v>27.44</v>
       </c>
       <c r="L14" t="n">
-        <v>41.66</v>
+        <v>44.28</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07:18:44</t>
+          <t>07:20:26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="F15" t="n">
-        <v>5.93</v>
+        <v>3.66</v>
       </c>
       <c r="G15" t="n">
-        <v>49.3</v>
+        <v>42.6</v>
       </c>
       <c r="H15" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
         <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>33.08</v>
+        <v>-16.98</v>
       </c>
       <c r="K15" t="n">
-        <v>-6.21</v>
+        <v>-50.24</v>
       </c>
       <c r="L15" t="n">
-        <v>33.65</v>
+        <v>53.03</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07:21:05</t>
+          <t>07:21:37</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.03</v>
+        <v>2.17</v>
       </c>
       <c r="F16" t="n">
-        <v>5.39</v>
+        <v>4.74</v>
       </c>
       <c r="G16" t="n">
-        <v>42.6</v>
+        <v>42.7</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>-49.33</v>
+        <v>7.52</v>
       </c>
       <c r="K16" t="n">
-        <v>13.69</v>
+        <v>59.67</v>
       </c>
       <c r="L16" t="n">
-        <v>51.2</v>
+        <v>60.14</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07:24:28</t>
+          <t>07:26:45</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>1.95</v>
+        <v>2.26</v>
       </c>
       <c r="F17" t="n">
-        <v>6.09</v>
+        <v>3.56</v>
       </c>
       <c r="G17" t="n">
-        <v>39.7</v>
+        <v>60.5</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>34.45</v>
+        <v>-3.9</v>
       </c>
       <c r="K17" t="n">
-        <v>48.34</v>
+        <v>-76.72</v>
       </c>
       <c r="L17" t="n">
-        <v>59.36</v>
+        <v>76.81</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07:25:47</t>
+          <t>07:29:11</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="F18" t="n">
-        <v>6.37</v>
+        <v>4.15</v>
       </c>
       <c r="G18" t="n">
-        <v>60.5</v>
+        <v>54</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>-76.54000000000001</v>
+        <v>-40.17</v>
       </c>
       <c r="K18" t="n">
-        <v>-38.72</v>
+        <v>33.56</v>
       </c>
       <c r="L18" t="n">
-        <v>85.78</v>
+        <v>52.35</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07:26:26</t>
+          <t>07:29:49</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.21</v>
+        <v>2.41</v>
       </c>
       <c r="F19" t="n">
-        <v>5.69</v>
+        <v>5.17</v>
       </c>
       <c r="G19" t="n">
-        <v>58.2</v>
+        <v>49.3</v>
       </c>
       <c r="H19" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="I19" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>58.82</v>
+        <v>-68.11</v>
       </c>
       <c r="K19" t="n">
-        <v>51.9</v>
+        <v>-33.38</v>
       </c>
       <c r="L19" t="n">
-        <v>78.45</v>
+        <v>75.84999999999999</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07:31:25</t>
+          <t>07:34:31</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="F20" t="n">
-        <v>5.9</v>
+        <v>5.13</v>
       </c>
       <c r="G20" t="n">
-        <v>49.3</v>
+        <v>45.7</v>
       </c>
       <c r="H20" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="I20" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>-61.93</v>
+        <v>85.48</v>
       </c>
       <c r="K20" t="n">
-        <v>-49.62</v>
+        <v>-3.19</v>
       </c>
       <c r="L20" t="n">
-        <v>79.36</v>
+        <v>85.54000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07:32:57</t>
+          <t>07:35:15</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>1.86</v>
+        <v>2.17</v>
       </c>
       <c r="F21" t="n">
-        <v>5.95</v>
+        <v>4.29</v>
       </c>
       <c r="G21" t="n">
-        <v>31.5</v>
+        <v>51.9</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="I21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>21.05</v>
+        <v>-94.91</v>
       </c>
       <c r="K21" t="n">
-        <v>-62.34</v>
+        <v>20.73</v>
       </c>
       <c r="L21" t="n">
-        <v>65.8</v>
+        <v>97.15000000000001</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07:34:21</t>
+          <t>07:36:32</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>1.88</v>
+        <v>1.95</v>
       </c>
       <c r="F22" t="n">
-        <v>5.4</v>
+        <v>5.14</v>
       </c>
       <c r="G22" t="n">
-        <v>43.7</v>
+        <v>48.5</v>
       </c>
       <c r="H22" t="n">
-        <v>1.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>-61.7</v>
+        <v>21.54</v>
       </c>
       <c r="K22" t="n">
-        <v>29.66</v>
+        <v>-73.64</v>
       </c>
       <c r="L22" t="n">
-        <v>68.45999999999999</v>
+        <v>76.72</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07:38:23</t>
+          <t>07:40:29</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="F23" t="n">
-        <v>5.73</v>
+        <v>5.53</v>
       </c>
       <c r="G23" t="n">
-        <v>49.8</v>
+        <v>57.3</v>
       </c>
       <c r="H23" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>-78.95</v>
+        <v>-123.6</v>
       </c>
       <c r="K23" t="n">
-        <v>46.45</v>
+        <v>82.48</v>
       </c>
       <c r="L23" t="n">
-        <v>91.59999999999999</v>
+        <v>148.59</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07:39:47</t>
+          <t>07:42:42</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.15</v>
+        <v>2.46</v>
       </c>
       <c r="F24" t="n">
-        <v>5.26</v>
+        <v>5.46</v>
       </c>
       <c r="G24" t="n">
-        <v>60.9</v>
+        <v>56.9</v>
       </c>
       <c r="H24" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="I24" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J24" t="n">
-        <v>113.54</v>
+        <v>-37.54</v>
       </c>
       <c r="K24" t="n">
-        <v>-113.87</v>
+        <v>87.89</v>
       </c>
       <c r="L24" t="n">
-        <v>160.8</v>
+        <v>95.56999999999999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07:40:42</t>
+          <t>07:44:01</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.04</v>
+        <v>2.44</v>
       </c>
       <c r="F25" t="n">
-        <v>6.17</v>
+        <v>5.41</v>
       </c>
       <c r="G25" t="n">
-        <v>45.5</v>
+        <v>38.4</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="I25" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.38</v>
+        <v>-82.05</v>
       </c>
       <c r="K25" t="n">
-        <v>-72.66</v>
+        <v>-105.62</v>
       </c>
       <c r="L25" t="n">
-        <v>72.67</v>
+        <v>133.74</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07:46:00</t>
+          <t>07:47:51</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.09</v>
+        <v>1.78</v>
       </c>
       <c r="F26" t="n">
-        <v>5.62</v>
+        <v>6.21</v>
       </c>
       <c r="G26" t="n">
-        <v>49</v>
+        <v>53.4</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>-182.16</v>
+        <v>-159.13</v>
       </c>
       <c r="K26" t="n">
-        <v>-43.66</v>
+        <v>94.83</v>
       </c>
       <c r="L26" t="n">
-        <v>187.32</v>
+        <v>185.25</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07:47:57</t>
+          <t>07:49:50</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.36</v>
+        <v>2.41</v>
       </c>
       <c r="F27" t="n">
-        <v>6.14</v>
+        <v>6.56</v>
       </c>
       <c r="G27" t="n">
-        <v>40.6</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="I27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>167.05</v>
+        <v>196.92</v>
       </c>
       <c r="K27" t="n">
-        <v>39.48</v>
+        <v>-61.51</v>
       </c>
       <c r="L27" t="n">
-        <v>171.65</v>
+        <v>206.3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07:48:32</t>
+          <t>07:51:57</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="F28" t="n">
-        <v>6.45</v>
+        <v>5.09</v>
       </c>
       <c r="G28" t="n">
-        <v>46.8</v>
+        <v>53.5</v>
       </c>
       <c r="H28" t="n">
-        <v>9.9</v>
+        <v>0.9</v>
       </c>
       <c r="I28" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J28" t="n">
-        <v>-79.45</v>
+        <v>-56.96</v>
       </c>
       <c r="K28" t="n">
-        <v>194.02</v>
+        <v>-135.12</v>
       </c>
       <c r="L28" t="n">
-        <v>209.66</v>
+        <v>146.63</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07:56:57</t>
+          <t>08:04:40</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="F29" t="n">
-        <v>5.74</v>
+        <v>4.86</v>
       </c>
       <c r="G29" t="n">
-        <v>45.6</v>
+        <v>49.9</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J29" t="n">
-        <v>19.72</v>
+        <v>-39.16</v>
       </c>
       <c r="K29" t="n">
-        <v>-30.73</v>
+        <v>-23.06</v>
       </c>
       <c r="L29" t="n">
-        <v>36.51</v>
+        <v>45.45</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>07:58:56</t>
+          <t>08:06:34</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.57</v>
+        <v>2.26</v>
       </c>
       <c r="F30" t="n">
-        <v>5.65</v>
+        <v>5.44</v>
       </c>
       <c r="G30" t="n">
-        <v>59.8</v>
+        <v>63.7</v>
       </c>
       <c r="H30" t="n">
-        <v>0.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I30" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J30" t="n">
-        <v>10.9</v>
+        <v>47.93</v>
       </c>
       <c r="K30" t="n">
-        <v>-52.95</v>
+        <v>20.07</v>
       </c>
       <c r="L30" t="n">
-        <v>54.06</v>
+        <v>51.96</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08:01:03</t>
+          <t>08:08:08</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="F31" t="n">
-        <v>6.2</v>
+        <v>3.99</v>
       </c>
       <c r="G31" t="n">
-        <v>58.6</v>
+        <v>45.5</v>
       </c>
       <c r="H31" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>46.3</v>
+        <v>50.78</v>
       </c>
       <c r="K31" t="n">
-        <v>-26.28</v>
+        <v>35.8</v>
       </c>
       <c r="L31" t="n">
-        <v>53.24</v>
+        <v>62.13</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08:07:32</t>
+          <t>08:12:21</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.39</v>
+        <v>2.29</v>
       </c>
       <c r="F32" t="n">
-        <v>6.81</v>
+        <v>6.9</v>
       </c>
       <c r="G32" t="n">
-        <v>53.4</v>
+        <v>35</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="I32" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J32" t="n">
-        <v>39.09</v>
+        <v>-62.91</v>
       </c>
       <c r="K32" t="n">
-        <v>8.67</v>
+        <v>-10.6</v>
       </c>
       <c r="L32" t="n">
-        <v>40.04</v>
+        <v>63.79</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08:09:59</t>
+          <t>08:13:14</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.37</v>
+        <v>1.98</v>
       </c>
       <c r="F33" t="n">
-        <v>5.91</v>
+        <v>3.04</v>
       </c>
       <c r="G33" t="n">
-        <v>40.7</v>
+        <v>42.6</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="I33" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>-67.98</v>
+        <v>34.98</v>
       </c>
       <c r="K33" t="n">
-        <v>-49.35</v>
+        <v>26.34</v>
       </c>
       <c r="L33" t="n">
-        <v>84</v>
+        <v>43.79</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08:11:06</t>
+          <t>08:14:43</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,13 +1465,13 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.11</v>
+        <v>2.56</v>
       </c>
       <c r="F34" t="n">
-        <v>6.16</v>
+        <v>5.02</v>
       </c>
       <c r="G34" t="n">
-        <v>42.2</v>
+        <v>55.1</v>
       </c>
       <c r="H34" t="n">
         <v>0</v>
@@ -1480,19 +1480,19 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>61.73</v>
+        <v>-12.27</v>
       </c>
       <c r="K34" t="n">
-        <v>34.24</v>
+        <v>-75.53</v>
       </c>
       <c r="L34" t="n">
-        <v>70.59</v>
+        <v>76.52</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08:16:12</t>
+          <t>08:19:56</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="F35" t="n">
-        <v>5.32</v>
+        <v>5.44</v>
       </c>
       <c r="G35" t="n">
-        <v>46.5</v>
+        <v>62.8</v>
       </c>
       <c r="H35" t="n">
         <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J35" t="n">
-        <v>78.06</v>
+        <v>45.97</v>
       </c>
       <c r="K35" t="n">
-        <v>12.15</v>
+        <v>73.22</v>
       </c>
       <c r="L35" t="n">
-        <v>79</v>
+        <v>86.45</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08:16:56</t>
+          <t>08:22:12</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.11</v>
+        <v>2.53</v>
       </c>
       <c r="F36" t="n">
-        <v>6.19</v>
+        <v>4.39</v>
       </c>
       <c r="G36" t="n">
-        <v>43.8</v>
+        <v>54.9</v>
       </c>
       <c r="H36" t="n">
-        <v>6.9</v>
+        <v>0</v>
       </c>
       <c r="I36" t="n">
         <v>25</v>
       </c>
       <c r="J36" t="n">
-        <v>79.27</v>
+        <v>71.06</v>
       </c>
       <c r="K36" t="n">
-        <v>-43.55</v>
+        <v>-45.34</v>
       </c>
       <c r="L36" t="n">
-        <v>90.44</v>
+        <v>84.29000000000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08:18:07</t>
+          <t>08:23:52</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>1.97</v>
+        <v>2.48</v>
       </c>
       <c r="F37" t="n">
-        <v>5.74</v>
+        <v>5.16</v>
       </c>
       <c r="G37" t="n">
-        <v>55.2</v>
+        <v>43.5</v>
       </c>
       <c r="H37" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>-34.44</v>
+        <v>-27.76</v>
       </c>
       <c r="K37" t="n">
-        <v>-64.5</v>
+        <v>-99.8</v>
       </c>
       <c r="L37" t="n">
-        <v>73.12</v>
+        <v>103.59</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08:21:34</t>
+          <t>08:29:52</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.18</v>
+        <v>2.38</v>
       </c>
       <c r="F38" t="n">
-        <v>5.79</v>
+        <v>4.79</v>
       </c>
       <c r="G38" t="n">
-        <v>58.9</v>
+        <v>43.3</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="I38" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J38" t="n">
-        <v>57.96</v>
+        <v>65.48999999999999</v>
       </c>
       <c r="K38" t="n">
-        <v>-80.81999999999999</v>
+        <v>-32.63</v>
       </c>
       <c r="L38" t="n">
-        <v>99.45</v>
+        <v>73.17</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08:23:08</t>
+          <t>08:30:29</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.08</v>
+        <v>2.19</v>
       </c>
       <c r="F39" t="n">
-        <v>5.89</v>
+        <v>5.48</v>
       </c>
       <c r="G39" t="n">
-        <v>49.4</v>
+        <v>46.1</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="I39" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>-142.96</v>
+        <v>94.54000000000001</v>
       </c>
       <c r="K39" t="n">
-        <v>-7.69</v>
+        <v>-81.64</v>
       </c>
       <c r="L39" t="n">
-        <v>143.17</v>
+        <v>124.91</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08:24:00</t>
+          <t>08:32:54</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="F40" t="n">
-        <v>6.25</v>
+        <v>6.14</v>
       </c>
       <c r="G40" t="n">
-        <v>52.9</v>
+        <v>32.6</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="I40" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J40" t="n">
-        <v>126.92</v>
+        <v>90.95</v>
       </c>
       <c r="K40" t="n">
-        <v>20.96</v>
+        <v>103.99</v>
       </c>
       <c r="L40" t="n">
-        <v>128.64</v>
+        <v>138.15</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08:30:06</t>
+          <t>08:36:28</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.21</v>
+        <v>2.6</v>
       </c>
       <c r="F41" t="n">
-        <v>6.27</v>
+        <v>6.9</v>
       </c>
       <c r="G41" t="n">
-        <v>54.2</v>
+        <v>48.6</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="I41" t="n">
         <v>23</v>
       </c>
       <c r="J41" t="n">
-        <v>-199.54</v>
+        <v>9.25</v>
       </c>
       <c r="K41" t="n">
-        <v>84.90000000000001</v>
+        <v>195.51</v>
       </c>
       <c r="L41" t="n">
-        <v>216.85</v>
+        <v>195.73</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08:32:07</t>
+          <t>08:37:26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>2.44</v>
+        <v>2.13</v>
       </c>
       <c r="F42" t="n">
-        <v>6.4</v>
+        <v>5.93</v>
       </c>
       <c r="G42" t="n">
-        <v>47.2</v>
+        <v>55.8</v>
       </c>
       <c r="H42" t="n">
-        <v>3.4</v>
+        <v>6.7</v>
       </c>
       <c r="I42" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>2.53</v>
+        <v>121.71</v>
       </c>
       <c r="K42" t="n">
-        <v>103.77</v>
+        <v>170.15</v>
       </c>
       <c r="L42" t="n">
-        <v>103.8</v>
+        <v>209.2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08:33:52</t>
+          <t>08:38:26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.6</v>
+        <v>2.37</v>
       </c>
       <c r="F43" t="n">
-        <v>6.15</v>
+        <v>6.9</v>
       </c>
       <c r="G43" t="n">
-        <v>57.8</v>
+        <v>42.8</v>
       </c>
       <c r="H43" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="I43" t="n">
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>132.3</v>
+        <v>131.79</v>
       </c>
       <c r="K43" t="n">
-        <v>7.16</v>
+        <v>-120.65</v>
       </c>
       <c r="L43" t="n">
-        <v>132.5</v>
+        <v>178.67</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08:41:59</t>
+          <t>08:48:33</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.24</v>
+        <v>2.11</v>
       </c>
       <c r="F44" t="n">
-        <v>5.62</v>
+        <v>6.9</v>
       </c>
       <c r="G44" t="n">
-        <v>53.2</v>
+        <v>53.9</v>
       </c>
       <c r="H44" t="n">
-        <v>2.3</v>
+        <v>0.3</v>
       </c>
       <c r="I44" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J44" t="n">
-        <v>54.02</v>
+        <v>-14.2</v>
       </c>
       <c r="K44" t="n">
-        <v>24.69</v>
+        <v>3.54</v>
       </c>
       <c r="L44" t="n">
-        <v>59.39</v>
+        <v>14.64</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:42:57</t>
+          <t>08:50:49</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.32</v>
+        <v>2.51</v>
       </c>
       <c r="F45" t="n">
-        <v>6.39</v>
+        <v>5.08</v>
       </c>
       <c r="G45" t="n">
-        <v>49.3</v>
+        <v>48.3</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="I45" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J45" t="n">
-        <v>-33.44</v>
+        <v>-13.19</v>
       </c>
       <c r="K45" t="n">
-        <v>-40.29</v>
+        <v>-40.79</v>
       </c>
       <c r="L45" t="n">
-        <v>52.36</v>
+        <v>42.87</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08:43:56</t>
+          <t>08:52:16</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.47</v>
+        <v>2.05</v>
       </c>
       <c r="F46" t="n">
-        <v>5.75</v>
+        <v>5.24</v>
       </c>
       <c r="G46" t="n">
-        <v>47.3</v>
+        <v>37.5</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="I46" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>44.91</v>
+        <v>-32.91</v>
       </c>
       <c r="K46" t="n">
-        <v>-4.83</v>
+        <v>56.9</v>
       </c>
       <c r="L46" t="n">
-        <v>45.17</v>
+        <v>65.73</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08:47:54</t>
+          <t>08:55:48</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.56</v>
+        <v>2.01</v>
       </c>
       <c r="F47" t="n">
-        <v>5.31</v>
+        <v>5.35</v>
       </c>
       <c r="G47" t="n">
-        <v>68.7</v>
+        <v>41.6</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I47" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>1.04</v>
+        <v>56.51</v>
       </c>
       <c r="K47" t="n">
-        <v>-18.72</v>
+        <v>3.14</v>
       </c>
       <c r="L47" t="n">
-        <v>18.75</v>
+        <v>56.59</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08:49:03</t>
+          <t>08:57:24</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.43</v>
+        <v>2.39</v>
       </c>
       <c r="F48" t="n">
-        <v>6</v>
+        <v>6.9</v>
       </c>
       <c r="G48" t="n">
-        <v>56</v>
+        <v>55.1</v>
       </c>
       <c r="H48" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>67.42</v>
+        <v>-46.07</v>
       </c>
       <c r="K48" t="n">
-        <v>23.04</v>
+        <v>36.91</v>
       </c>
       <c r="L48" t="n">
-        <v>71.25</v>
+        <v>59.03</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08:50:33</t>
+          <t>08:59:35</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.18</v>
+        <v>2.15</v>
       </c>
       <c r="F49" t="n">
-        <v>5.6</v>
+        <v>6.83</v>
       </c>
       <c r="G49" t="n">
-        <v>53.2</v>
+        <v>37.3</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="I49" t="n">
         <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>25.07</v>
+        <v>78.39</v>
       </c>
       <c r="K49" t="n">
-        <v>69.44</v>
+        <v>-26.36</v>
       </c>
       <c r="L49" t="n">
-        <v>73.83</v>
+        <v>82.7</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>08:55:05</t>
+          <t>09:02:38</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.46</v>
+        <v>2.06</v>
       </c>
       <c r="F50" t="n">
-        <v>5.75</v>
+        <v>6.79</v>
       </c>
       <c r="G50" t="n">
-        <v>62.9</v>
+        <v>54.3</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I50" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>-61.14</v>
+        <v>-55.37</v>
       </c>
       <c r="K50" t="n">
-        <v>52.84</v>
+        <v>-94.88</v>
       </c>
       <c r="L50" t="n">
-        <v>80.81</v>
+        <v>109.85</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>08:56:40</t>
+          <t>09:04:00</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.36</v>
+        <v>2.2</v>
       </c>
       <c r="F51" t="n">
-        <v>5.67</v>
+        <v>4.05</v>
       </c>
       <c r="G51" t="n">
-        <v>34.8</v>
+        <v>35.9</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>-63.98</v>
+        <v>47.07</v>
       </c>
       <c r="K51" t="n">
-        <v>57.32</v>
+        <v>89.78</v>
       </c>
       <c r="L51" t="n">
-        <v>85.91</v>
+        <v>101.37</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>08:57:46</t>
+          <t>09:05:11</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,13 +2221,13 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="F52" t="n">
-        <v>6.6</v>
+        <v>5.82</v>
       </c>
       <c r="G52" t="n">
-        <v>55.2</v>
+        <v>54.5</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -2236,19 +2236,19 @@
         <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>84.84999999999999</v>
+        <v>-99.47</v>
       </c>
       <c r="K52" t="n">
-        <v>12.47</v>
+        <v>-22.57</v>
       </c>
       <c r="L52" t="n">
-        <v>85.77</v>
+        <v>102</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09:01:15</t>
+          <t>09:10:16</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>2.23</v>
+        <v>2.27</v>
       </c>
       <c r="F53" t="n">
-        <v>5.78</v>
+        <v>6.9</v>
       </c>
       <c r="G53" t="n">
-        <v>45.7</v>
+        <v>52.7</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
       </c>
       <c r="I53" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>120.29</v>
+        <v>-145.03</v>
       </c>
       <c r="K53" t="n">
-        <v>10.37</v>
+        <v>48.34</v>
       </c>
       <c r="L53" t="n">
-        <v>120.74</v>
+        <v>152.88</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09:02:20</t>
+          <t>09:12:21</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.3</v>
+        <v>2.57</v>
       </c>
       <c r="F54" t="n">
-        <v>6.21</v>
+        <v>5.13</v>
       </c>
       <c r="G54" t="n">
-        <v>31.7</v>
+        <v>61.4</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I54" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J54" t="n">
-        <v>88.65000000000001</v>
+        <v>62.31</v>
       </c>
       <c r="K54" t="n">
-        <v>-85.91</v>
+        <v>97.03</v>
       </c>
       <c r="L54" t="n">
-        <v>123.45</v>
+        <v>115.31</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09:03:44</t>
+          <t>09:13:32</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2.47</v>
+        <v>2.19</v>
       </c>
       <c r="F55" t="n">
-        <v>5.6</v>
+        <v>6.9</v>
       </c>
       <c r="G55" t="n">
-        <v>57</v>
+        <v>60.5</v>
       </c>
       <c r="H55" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="I55" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J55" t="n">
-        <v>75.67</v>
+        <v>104.98</v>
       </c>
       <c r="K55" t="n">
-        <v>-141.28</v>
+        <v>7.3</v>
       </c>
       <c r="L55" t="n">
-        <v>160.26</v>
+        <v>105.24</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09:08:16</t>
+          <t>09:18:32</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="F56" t="n">
-        <v>5.98</v>
+        <v>6.9</v>
       </c>
       <c r="G56" t="n">
-        <v>54.7</v>
+        <v>49.3</v>
       </c>
       <c r="H56" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="I56" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>193.69</v>
+        <v>182.62</v>
       </c>
       <c r="K56" t="n">
-        <v>112.01</v>
+        <v>-10.68</v>
       </c>
       <c r="L56" t="n">
-        <v>223.74</v>
+        <v>182.93</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09:09:58</t>
+          <t>09:19:21</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>2.54</v>
+        <v>2.41</v>
       </c>
       <c r="F57" t="n">
-        <v>6.03</v>
+        <v>6.89</v>
       </c>
       <c r="G57" t="n">
-        <v>46.6</v>
+        <v>49.6</v>
       </c>
       <c r="H57" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="I57" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J57" t="n">
-        <v>33.96</v>
+        <v>165.19</v>
       </c>
       <c r="K57" t="n">
-        <v>184.97</v>
+        <v>5.57</v>
       </c>
       <c r="L57" t="n">
-        <v>188.07</v>
+        <v>165.28</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09:11:12</t>
+          <t>09:21:20</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.12</v>
+        <v>2.55</v>
       </c>
       <c r="F58" t="n">
-        <v>5.92</v>
+        <v>6.9</v>
       </c>
       <c r="G58" t="n">
-        <v>56.3</v>
+        <v>42.2</v>
       </c>
       <c r="H58" t="n">
-        <v>8.6</v>
+        <v>3.3</v>
       </c>
       <c r="I58" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J58" t="n">
-        <v>4.6</v>
+        <v>107.47</v>
       </c>
       <c r="K58" t="n">
-        <v>179.53</v>
+        <v>119.54</v>
       </c>
       <c r="L58" t="n">
-        <v>179.59</v>
+        <v>160.75</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09:22:13</t>
+          <t>09:34:11</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.56</v>
+        <v>2.49</v>
       </c>
       <c r="F59" t="n">
-        <v>6.13</v>
+        <v>6.9</v>
       </c>
       <c r="G59" t="n">
-        <v>52.8</v>
+        <v>47.1</v>
       </c>
       <c r="H59" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="I59" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>22.59</v>
+        <v>-10.5</v>
       </c>
       <c r="K59" t="n">
-        <v>-36.93</v>
+        <v>51.94</v>
       </c>
       <c r="L59" t="n">
-        <v>43.29</v>
+        <v>52.99</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09:23:02</t>
+          <t>09:35:35</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="F60" t="n">
-        <v>6.44</v>
+        <v>6.9</v>
       </c>
       <c r="G60" t="n">
-        <v>47.1</v>
+        <v>57.9</v>
       </c>
       <c r="H60" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="I60" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>-45.14</v>
+        <v>-43.53</v>
       </c>
       <c r="K60" t="n">
-        <v>51.87</v>
+        <v>-6.76</v>
       </c>
       <c r="L60" t="n">
-        <v>68.76000000000001</v>
+        <v>44.05</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09:25:01</t>
+          <t>09:37:07</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="F61" t="n">
-        <v>5.89</v>
+        <v>5.34</v>
       </c>
       <c r="G61" t="n">
-        <v>48</v>
+        <v>57.9</v>
       </c>
       <c r="H61" t="n">
         <v>0</v>
       </c>
       <c r="I61" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>-34.34</v>
+        <v>-42.9</v>
       </c>
       <c r="K61" t="n">
-        <v>-7.52</v>
+        <v>-23.87</v>
       </c>
       <c r="L61" t="n">
-        <v>35.15</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09:31:02</t>
+          <t>09:41:14</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.41</v>
+        <v>2.51</v>
       </c>
       <c r="F62" t="n">
-        <v>5.78</v>
+        <v>6.9</v>
       </c>
       <c r="G62" t="n">
-        <v>41.3</v>
+        <v>52.6</v>
       </c>
       <c r="H62" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I62" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J62" t="n">
-        <v>-63.71</v>
+        <v>-33.66</v>
       </c>
       <c r="K62" t="n">
-        <v>44.35</v>
+        <v>-56.91</v>
       </c>
       <c r="L62" t="n">
-        <v>77.63</v>
+        <v>66.12</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09:31:43</t>
+          <t>09:43:05</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.43</v>
+        <v>2.31</v>
       </c>
       <c r="F63" t="n">
-        <v>5.72</v>
+        <v>6.9</v>
       </c>
       <c r="G63" t="n">
-        <v>40.4</v>
+        <v>44.2</v>
       </c>
       <c r="H63" t="n">
         <v>0</v>
       </c>
       <c r="I63" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J63" t="n">
-        <v>40.74</v>
+        <v>58.06</v>
       </c>
       <c r="K63" t="n">
-        <v>-15.51</v>
+        <v>-54.11</v>
       </c>
       <c r="L63" t="n">
-        <v>43.59</v>
+        <v>79.37</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09:33:31</t>
+          <t>09:44:38</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>2.13</v>
+        <v>2.87</v>
       </c>
       <c r="F64" t="n">
-        <v>5.49</v>
+        <v>5.24</v>
       </c>
       <c r="G64" t="n">
-        <v>59.4</v>
+        <v>40.8</v>
       </c>
       <c r="H64" t="n">
-        <v>2.6</v>
+        <v>7</v>
       </c>
       <c r="I64" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J64" t="n">
-        <v>-34.47</v>
+        <v>-53.23</v>
       </c>
       <c r="K64" t="n">
-        <v>-62.23</v>
+        <v>-20.57</v>
       </c>
       <c r="L64" t="n">
-        <v>71.14</v>
+        <v>57.06</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09:38:44</t>
+          <t>09:50:02</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2.78</v>
+        <v>2.21</v>
       </c>
       <c r="F65" t="n">
-        <v>5.48</v>
+        <v>6.43</v>
       </c>
       <c r="G65" t="n">
-        <v>46.8</v>
+        <v>48.5</v>
       </c>
       <c r="H65" t="n">
         <v>0</v>
       </c>
       <c r="I65" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J65" t="n">
-        <v>18.2</v>
+        <v>-25.03</v>
       </c>
       <c r="K65" t="n">
-        <v>88.39</v>
+        <v>98.52</v>
       </c>
       <c r="L65" t="n">
-        <v>90.25</v>
+        <v>101.65</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09:39:56</t>
+          <t>09:51:35</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>2.31</v>
+        <v>2.44</v>
       </c>
       <c r="F66" t="n">
-        <v>6.55</v>
+        <v>4.27</v>
       </c>
       <c r="G66" t="n">
-        <v>45.3</v>
+        <v>53.8</v>
       </c>
       <c r="H66" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="I66" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>-28.01</v>
+        <v>77.73</v>
       </c>
       <c r="K66" t="n">
-        <v>-90.20999999999999</v>
+        <v>-39.34</v>
       </c>
       <c r="L66" t="n">
-        <v>94.45</v>
+        <v>87.12</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09:41:18</t>
+          <t>09:53:24</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="F67" t="n">
-        <v>5.34</v>
+        <v>6.9</v>
       </c>
       <c r="G67" t="n">
-        <v>44.6</v>
+        <v>29.8</v>
       </c>
       <c r="H67" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="I67" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J67" t="n">
-        <v>106.03</v>
+        <v>-52.27</v>
       </c>
       <c r="K67" t="n">
-        <v>-47.31</v>
+        <v>67.06</v>
       </c>
       <c r="L67" t="n">
-        <v>116.1</v>
+        <v>85.02</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09:46:00</t>
+          <t>09:58:20</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="F68" t="n">
-        <v>6.13</v>
+        <v>5.69</v>
       </c>
       <c r="G68" t="n">
-        <v>45.8</v>
+        <v>41.1</v>
       </c>
       <c r="H68" t="n">
         <v>0</v>
       </c>
       <c r="I68" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>-121.71</v>
+        <v>120.65</v>
       </c>
       <c r="K68" t="n">
-        <v>-50.3</v>
+        <v>-44.79</v>
       </c>
       <c r="L68" t="n">
-        <v>131.69</v>
+        <v>128.69</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09:46:33</t>
+          <t>09:59:34</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="F69" t="n">
-        <v>6.18</v>
+        <v>5.19</v>
       </c>
       <c r="G69" t="n">
-        <v>44.1</v>
+        <v>63</v>
       </c>
       <c r="H69" t="n">
-        <v>4</v>
+        <v>1.2</v>
       </c>
       <c r="I69" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>-107.55</v>
+        <v>16.55</v>
       </c>
       <c r="K69" t="n">
-        <v>-24.76</v>
+        <v>111.78</v>
       </c>
       <c r="L69" t="n">
-        <v>110.37</v>
+        <v>113</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>09:48:45</t>
+          <t>10:01:36</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.51</v>
+        <v>2.73</v>
       </c>
       <c r="F70" t="n">
-        <v>6.36</v>
+        <v>6.9</v>
       </c>
       <c r="G70" t="n">
-        <v>48.4</v>
+        <v>53.2</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="I70" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>-83.59999999999999</v>
+        <v>140.45</v>
       </c>
       <c r="K70" t="n">
-        <v>-13.6</v>
+        <v>72.69</v>
       </c>
       <c r="L70" t="n">
-        <v>84.7</v>
+        <v>158.14</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>09:52:40</t>
+          <t>10:06:56</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.68</v>
+        <v>2.52</v>
       </c>
       <c r="F71" t="n">
-        <v>6.06</v>
+        <v>6.66</v>
       </c>
       <c r="G71" t="n">
-        <v>53.5</v>
+        <v>58.7</v>
       </c>
       <c r="H71" t="n">
-        <v>4.7</v>
+        <v>1.8</v>
       </c>
       <c r="I71" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J71" t="n">
-        <v>-43.31</v>
+        <v>89.91</v>
       </c>
       <c r="K71" t="n">
-        <v>-31.15</v>
+        <v>-139.71</v>
       </c>
       <c r="L71" t="n">
-        <v>53.35</v>
+        <v>166.14</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>09:54:15</t>
+          <t>10:08:04</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="F72" t="n">
-        <v>6.48</v>
+        <v>6.9</v>
       </c>
       <c r="G72" t="n">
-        <v>41.1</v>
+        <v>56.2</v>
       </c>
       <c r="H72" t="n">
-        <v>0.7</v>
+        <v>5.2</v>
       </c>
       <c r="I72" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J72" t="n">
-        <v>-25.22</v>
+        <v>-153.51</v>
       </c>
       <c r="K72" t="n">
-        <v>180.12</v>
+        <v>3.86</v>
       </c>
       <c r="L72" t="n">
-        <v>181.88</v>
+        <v>153.56</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>09:55:19</t>
+          <t>10:10:24</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.64</v>
+        <v>2.39</v>
       </c>
       <c r="F73" t="n">
-        <v>5.41</v>
+        <v>5.5</v>
       </c>
       <c r="G73" t="n">
-        <v>44.5</v>
+        <v>55.8</v>
       </c>
       <c r="H73" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="I73" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>-231.75</v>
+        <v>137.72</v>
       </c>
       <c r="K73" t="n">
-        <v>86.93000000000001</v>
+        <v>-51.64</v>
       </c>
       <c r="L73" t="n">
-        <v>247.52</v>
+        <v>147.08</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10:06:24</t>
+          <t>10:22:37</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>2.65</v>
+        <v>2.72</v>
       </c>
       <c r="F74" t="n">
-        <v>6.41</v>
+        <v>5.57</v>
       </c>
       <c r="G74" t="n">
-        <v>45.5</v>
+        <v>52.4</v>
       </c>
       <c r="H74" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="I74" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>-48.93</v>
+        <v>-46.45</v>
       </c>
       <c r="K74" t="n">
-        <v>-4.98</v>
+        <v>-18.02</v>
       </c>
       <c r="L74" t="n">
-        <v>49.18</v>
+        <v>49.82</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10:07:32</t>
+          <t>10:24:06</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="F75" t="n">
-        <v>5.94</v>
+        <v>6.9</v>
       </c>
       <c r="G75" t="n">
-        <v>52.4</v>
+        <v>37.5</v>
       </c>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I75" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>-6.31</v>
+        <v>-44.34</v>
       </c>
       <c r="K75" t="n">
-        <v>39.74</v>
+        <v>1.74</v>
       </c>
       <c r="L75" t="n">
-        <v>40.24</v>
+        <v>44.37</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10:09:53</t>
+          <t>10:25:31</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>2.22</v>
+        <v>2.85</v>
       </c>
       <c r="F76" t="n">
-        <v>6.67</v>
+        <v>5.97</v>
       </c>
       <c r="G76" t="n">
-        <v>49</v>
+        <v>50.5</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
       </c>
       <c r="I76" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J76" t="n">
-        <v>-37.12</v>
+        <v>4.81</v>
       </c>
       <c r="K76" t="n">
-        <v>-32.7</v>
+        <v>-57.66</v>
       </c>
       <c r="L76" t="n">
-        <v>49.46</v>
+        <v>57.86</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10:15:48</t>
+          <t>10:29:30</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>2.54</v>
+        <v>2.92</v>
       </c>
       <c r="F77" t="n">
-        <v>6.59</v>
+        <v>6.9</v>
       </c>
       <c r="G77" t="n">
-        <v>65.3</v>
+        <v>58.2</v>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="I77" t="n">
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>-55.07</v>
+        <v>70.62</v>
       </c>
       <c r="K77" t="n">
-        <v>58.94</v>
+        <v>-25.53</v>
       </c>
       <c r="L77" t="n">
-        <v>80.66</v>
+        <v>75.09999999999999</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>10:17:59</t>
+          <t>10:31:04</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2.73</v>
+        <v>2.35</v>
       </c>
       <c r="F78" t="n">
-        <v>5.62</v>
+        <v>4.19</v>
       </c>
       <c r="G78" t="n">
-        <v>45.1</v>
+        <v>53.5</v>
       </c>
       <c r="H78" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="I78" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>-67.38</v>
+        <v>-62.59</v>
       </c>
       <c r="K78" t="n">
-        <v>-47.88</v>
+        <v>-17.54</v>
       </c>
       <c r="L78" t="n">
-        <v>82.66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>10:20:18</t>
+          <t>10:33:29</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.62</v>
+        <v>2.28</v>
       </c>
       <c r="F79" t="n">
-        <v>5.8</v>
+        <v>5.51</v>
       </c>
       <c r="G79" t="n">
-        <v>38.4</v>
+        <v>47.2</v>
       </c>
       <c r="H79" t="n">
         <v>0</v>
       </c>
       <c r="I79" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>59</v>
+        <v>-75.5</v>
       </c>
       <c r="K79" t="n">
-        <v>-7.67</v>
+        <v>-2.7</v>
       </c>
       <c r="L79" t="n">
-        <v>59.49</v>
+        <v>75.55</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>10:24:30</t>
+          <t>10:38:14</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>2.48</v>
+        <v>2.64</v>
       </c>
       <c r="F80" t="n">
-        <v>6.19</v>
+        <v>6.9</v>
       </c>
       <c r="G80" t="n">
-        <v>48.3</v>
+        <v>66.7</v>
       </c>
       <c r="H80" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I80" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>55.6</v>
+        <v>56.08</v>
       </c>
       <c r="K80" t="n">
-        <v>58.89</v>
+        <v>60.04</v>
       </c>
       <c r="L80" t="n">
-        <v>80.98999999999999</v>
+        <v>82.15000000000001</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10:25:50</t>
+          <t>10:39:49</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2.95</v>
+        <v>2.49</v>
       </c>
       <c r="F81" t="n">
-        <v>5.75</v>
+        <v>6.9</v>
       </c>
       <c r="G81" t="n">
-        <v>46.5</v>
+        <v>34.7</v>
       </c>
       <c r="H81" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="I81" t="n">
         <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>36.94</v>
+        <v>-59.38</v>
       </c>
       <c r="K81" t="n">
-        <v>-81.34999999999999</v>
+        <v>73.81</v>
       </c>
       <c r="L81" t="n">
-        <v>89.34</v>
+        <v>94.73</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10:27:55</t>
+          <t>10:40:52</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,13 +3481,13 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.18</v>
+        <v>2.37</v>
       </c>
       <c r="F82" t="n">
-        <v>5.63</v>
+        <v>4.03</v>
       </c>
       <c r="G82" t="n">
-        <v>53.9</v>
+        <v>42.9</v>
       </c>
       <c r="H82" t="n">
         <v>0</v>
@@ -3496,19 +3496,19 @@
         <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>-85.43000000000001</v>
+        <v>-75.48999999999999</v>
       </c>
       <c r="K82" t="n">
-        <v>-78.05</v>
+        <v>26.15</v>
       </c>
       <c r="L82" t="n">
-        <v>115.72</v>
+        <v>79.89</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10:32:45</t>
+          <t>10:45:48</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.39</v>
+        <v>2.23</v>
       </c>
       <c r="F83" t="n">
-        <v>5.91</v>
+        <v>6.02</v>
       </c>
       <c r="G83" t="n">
-        <v>35.5</v>
+        <v>31.7</v>
       </c>
       <c r="H83" t="n">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="I83" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J83" t="n">
-        <v>-125.37</v>
+        <v>67.95</v>
       </c>
       <c r="K83" t="n">
-        <v>26.95</v>
+        <v>-151.44</v>
       </c>
       <c r="L83" t="n">
-        <v>128.24</v>
+        <v>165.98</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10:34:19</t>
+          <t>10:47:05</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2.12</v>
+        <v>2.69</v>
       </c>
       <c r="F84" t="n">
-        <v>6.27</v>
+        <v>6.72</v>
       </c>
       <c r="G84" t="n">
-        <v>31.3</v>
+        <v>44.1</v>
       </c>
       <c r="H84" t="n">
-        <v>3.1</v>
+        <v>5.6</v>
       </c>
       <c r="I84" t="n">
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>-44.05</v>
+        <v>-30.92</v>
       </c>
       <c r="K84" t="n">
-        <v>118.06</v>
+        <v>32.78</v>
       </c>
       <c r="L84" t="n">
-        <v>126.02</v>
+        <v>45.06</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10:36:34</t>
+          <t>10:48:16</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>2.42</v>
+        <v>2.72</v>
       </c>
       <c r="F85" t="n">
-        <v>6.22</v>
+        <v>6.9</v>
       </c>
       <c r="G85" t="n">
-        <v>55.8</v>
+        <v>37.1</v>
       </c>
       <c r="H85" t="n">
         <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J85" t="n">
-        <v>-31.73</v>
+        <v>148.97</v>
       </c>
       <c r="K85" t="n">
-        <v>-122.27</v>
+        <v>28.33</v>
       </c>
       <c r="L85" t="n">
-        <v>126.32</v>
+        <v>151.64</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10:41:32</t>
+          <t>10:53:38</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="F86" t="n">
-        <v>5.29</v>
+        <v>5.03</v>
       </c>
       <c r="G86" t="n">
-        <v>50.1</v>
+        <v>42</v>
       </c>
       <c r="H86" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="I86" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J86" t="n">
-        <v>-128.94</v>
+        <v>49.22</v>
       </c>
       <c r="K86" t="n">
-        <v>-84.8</v>
+        <v>190.64</v>
       </c>
       <c r="L86" t="n">
-        <v>154.32</v>
+        <v>196.9</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10:43:21</t>
+          <t>10:55:08</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2.38</v>
+        <v>2.49</v>
       </c>
       <c r="F87" t="n">
-        <v>6.08</v>
+        <v>6.9</v>
       </c>
       <c r="G87" t="n">
-        <v>46</v>
+        <v>52.3</v>
       </c>
       <c r="H87" t="n">
-        <v>6.3</v>
+        <v>0</v>
       </c>
       <c r="I87" t="n">
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>124.68</v>
+        <v>140.13</v>
       </c>
       <c r="K87" t="n">
-        <v>-130.04</v>
+        <v>67.66</v>
       </c>
       <c r="L87" t="n">
-        <v>180.15</v>
+        <v>155.61</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10:44:10</t>
+          <t>10:57:04</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>2.63</v>
+        <v>2.9</v>
       </c>
       <c r="F88" t="n">
-        <v>6.69</v>
+        <v>6.78</v>
       </c>
       <c r="G88" t="n">
-        <v>49.6</v>
+        <v>46.8</v>
       </c>
       <c r="H88" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>-129.86</v>
+        <v>-23.03</v>
       </c>
       <c r="K88" t="n">
-        <v>-112.42</v>
+        <v>179.17</v>
       </c>
       <c r="L88" t="n">
-        <v>171.76</v>
+        <v>180.64</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-10-01.xlsx
+++ b/output/2025-10-01.xlsx
@@ -682,13 +682,13 @@
         <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>-16.98</v>
+        <v>-17.31</v>
       </c>
       <c r="K15" t="n">
-        <v>-50.24</v>
+        <v>-51.23</v>
       </c>
       <c r="L15" t="n">
-        <v>53.03</v>
+        <v>54.07</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>21</v>
       </c>
       <c r="J16" t="n">
-        <v>7.52</v>
+        <v>7.95</v>
       </c>
       <c r="K16" t="n">
-        <v>59.67</v>
+        <v>63.05</v>
       </c>
       <c r="L16" t="n">
-        <v>60.14</v>
+        <v>63.54</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>-3.9</v>
+        <v>-3.82</v>
       </c>
       <c r="K17" t="n">
-        <v>-76.72</v>
+        <v>-75.15000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>76.81</v>
+        <v>75.25</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>-40.17</v>
+        <v>-37.61</v>
       </c>
       <c r="K18" t="n">
-        <v>33.56</v>
+        <v>31.42</v>
       </c>
       <c r="L18" t="n">
-        <v>52.35</v>
+        <v>49</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>-68.11</v>
+        <v>-66.72</v>
       </c>
       <c r="K19" t="n">
-        <v>-33.38</v>
+        <v>-32.7</v>
       </c>
       <c r="L19" t="n">
-        <v>75.84999999999999</v>
+        <v>74.31</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>85.48</v>
+        <v>88.77</v>
       </c>
       <c r="K20" t="n">
-        <v>-3.19</v>
+        <v>-3.31</v>
       </c>
       <c r="L20" t="n">
-        <v>85.54000000000001</v>
+        <v>88.83</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>-94.91</v>
+        <v>-98.56</v>
       </c>
       <c r="K21" t="n">
-        <v>20.73</v>
+        <v>21.53</v>
       </c>
       <c r="L21" t="n">
-        <v>97.15000000000001</v>
+        <v>100.88</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>21.54</v>
+        <v>21.96</v>
       </c>
       <c r="K22" t="n">
-        <v>-73.64</v>
+        <v>-75.08</v>
       </c>
       <c r="L22" t="n">
-        <v>76.72</v>
+        <v>78.23</v>
       </c>
     </row>
     <row r="23">
@@ -1060,13 +1060,13 @@
         <v>27</v>
       </c>
       <c r="J24" t="n">
-        <v>-37.54</v>
+        <v>-35.14</v>
       </c>
       <c r="K24" t="n">
-        <v>87.89</v>
+        <v>82.28</v>
       </c>
       <c r="L24" t="n">
-        <v>95.56999999999999</v>
+        <v>89.47</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>21</v>
       </c>
       <c r="J25" t="n">
-        <v>-82.05</v>
+        <v>-86.7</v>
       </c>
       <c r="K25" t="n">
-        <v>-105.62</v>
+        <v>-111.59</v>
       </c>
       <c r="L25" t="n">
-        <v>133.74</v>
+        <v>141.31</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>21</v>
       </c>
       <c r="J26" t="n">
-        <v>-159.13</v>
+        <v>-168.14</v>
       </c>
       <c r="K26" t="n">
-        <v>94.83</v>
+        <v>100.2</v>
       </c>
       <c r="L26" t="n">
-        <v>185.25</v>
+        <v>195.73</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>23</v>
       </c>
       <c r="J27" t="n">
-        <v>196.92</v>
+        <v>200.78</v>
       </c>
       <c r="K27" t="n">
-        <v>-61.51</v>
+        <v>-62.71</v>
       </c>
       <c r="L27" t="n">
-        <v>206.3</v>
+        <v>210.35</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>21</v>
       </c>
       <c r="J28" t="n">
-        <v>-56.96</v>
+        <v>-60.18</v>
       </c>
       <c r="K28" t="n">
-        <v>-135.12</v>
+        <v>-142.77</v>
       </c>
       <c r="L28" t="n">
-        <v>146.63</v>
+        <v>154.93</v>
       </c>
     </row>
     <row r="29">
@@ -1354,13 +1354,13 @@
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>50.78</v>
+        <v>49.74</v>
       </c>
       <c r="K31" t="n">
-        <v>35.8</v>
+        <v>35.07</v>
       </c>
       <c r="L31" t="n">
-        <v>62.13</v>
+        <v>60.86</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>26</v>
       </c>
       <c r="J32" t="n">
-        <v>-62.91</v>
+        <v>-60.29</v>
       </c>
       <c r="K32" t="n">
-        <v>-10.6</v>
+        <v>-10.16</v>
       </c>
       <c r="L32" t="n">
-        <v>63.79</v>
+        <v>61.14</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>34.98</v>
+        <v>32.75</v>
       </c>
       <c r="K33" t="n">
-        <v>26.34</v>
+        <v>24.66</v>
       </c>
       <c r="L33" t="n">
-        <v>43.79</v>
+        <v>40.99</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>-12.27</v>
+        <v>-12.51</v>
       </c>
       <c r="K34" t="n">
-        <v>-75.53</v>
+        <v>-77.01000000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>76.52</v>
+        <v>78.02</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>26</v>
       </c>
       <c r="J35" t="n">
-        <v>45.97</v>
+        <v>44.05</v>
       </c>
       <c r="K35" t="n">
-        <v>73.22</v>
+        <v>70.17</v>
       </c>
       <c r="L35" t="n">
-        <v>86.45</v>
+        <v>82.84999999999999</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>25</v>
       </c>
       <c r="J36" t="n">
-        <v>71.06</v>
+        <v>69.61</v>
       </c>
       <c r="K36" t="n">
-        <v>-45.34</v>
+        <v>-44.42</v>
       </c>
       <c r="L36" t="n">
-        <v>84.29000000000001</v>
+        <v>82.56999999999999</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>23</v>
       </c>
       <c r="J37" t="n">
-        <v>-27.76</v>
+        <v>-28.3</v>
       </c>
       <c r="K37" t="n">
-        <v>-99.8</v>
+        <v>-101.75</v>
       </c>
       <c r="L37" t="n">
-        <v>103.59</v>
+        <v>105.62</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>22</v>
       </c>
       <c r="J38" t="n">
-        <v>65.48999999999999</v>
+        <v>68.01000000000001</v>
       </c>
       <c r="K38" t="n">
-        <v>-32.63</v>
+        <v>-33.88</v>
       </c>
       <c r="L38" t="n">
-        <v>73.17</v>
+        <v>75.98</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>21</v>
       </c>
       <c r="J39" t="n">
-        <v>94.54000000000001</v>
+        <v>99.89</v>
       </c>
       <c r="K39" t="n">
-        <v>-81.64</v>
+        <v>-86.26000000000001</v>
       </c>
       <c r="L39" t="n">
-        <v>124.91</v>
+        <v>131.98</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>21</v>
       </c>
       <c r="J40" t="n">
-        <v>90.95</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>103.99</v>
+        <v>109.87</v>
       </c>
       <c r="L40" t="n">
-        <v>138.15</v>
+        <v>145.97</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>23</v>
       </c>
       <c r="J41" t="n">
-        <v>9.25</v>
+        <v>9.43</v>
       </c>
       <c r="K41" t="n">
-        <v>195.51</v>
+        <v>199.35</v>
       </c>
       <c r="L41" t="n">
-        <v>195.73</v>
+        <v>199.57</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>121.71</v>
+        <v>124.1</v>
       </c>
       <c r="K42" t="n">
-        <v>170.15</v>
+        <v>173.48</v>
       </c>
       <c r="L42" t="n">
-        <v>209.2</v>
+        <v>213.3</v>
       </c>
     </row>
     <row r="43">
@@ -1942,13 +1942,13 @@
         <v>21</v>
       </c>
       <c r="J45" t="n">
-        <v>-13.19</v>
+        <v>-13.94</v>
       </c>
       <c r="K45" t="n">
-        <v>-40.79</v>
+        <v>-43.1</v>
       </c>
       <c r="L45" t="n">
-        <v>42.87</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>-32.91</v>
+        <v>-32.24</v>
       </c>
       <c r="K46" t="n">
-        <v>56.9</v>
+        <v>55.74</v>
       </c>
       <c r="L46" t="n">
-        <v>65.73</v>
+        <v>64.39</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>56.51</v>
+        <v>57.61</v>
       </c>
       <c r="K47" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="L47" t="n">
-        <v>56.59</v>
+        <v>57.7</v>
       </c>
     </row>
     <row r="48">
@@ -2110,13 +2110,13 @@
         <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>78.39</v>
+        <v>82.83</v>
       </c>
       <c r="K49" t="n">
-        <v>-26.36</v>
+        <v>-27.85</v>
       </c>
       <c r="L49" t="n">
-        <v>82.7</v>
+        <v>87.38</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>26</v>
       </c>
       <c r="J50" t="n">
-        <v>-55.37</v>
+        <v>-53.07</v>
       </c>
       <c r="K50" t="n">
-        <v>-94.88</v>
+        <v>-90.92</v>
       </c>
       <c r="L50" t="n">
-        <v>109.85</v>
+        <v>105.28</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>47.07</v>
+        <v>48.88</v>
       </c>
       <c r="K51" t="n">
-        <v>89.78</v>
+        <v>93.23</v>
       </c>
       <c r="L51" t="n">
-        <v>101.37</v>
+        <v>105.27</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>-99.47</v>
+        <v>-101.42</v>
       </c>
       <c r="K52" t="n">
-        <v>-22.57</v>
+        <v>-23.01</v>
       </c>
       <c r="L52" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>-145.03</v>
+        <v>-142.07</v>
       </c>
       <c r="K53" t="n">
-        <v>48.34</v>
+        <v>47.36</v>
       </c>
       <c r="L53" t="n">
-        <v>152.88</v>
+        <v>149.76</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>27</v>
       </c>
       <c r="J54" t="n">
-        <v>62.31</v>
+        <v>58.33</v>
       </c>
       <c r="K54" t="n">
-        <v>97.03</v>
+        <v>90.83</v>
       </c>
       <c r="L54" t="n">
-        <v>115.31</v>
+        <v>107.95</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>27</v>
       </c>
       <c r="J55" t="n">
-        <v>104.98</v>
+        <v>98.28</v>
       </c>
       <c r="K55" t="n">
-        <v>7.3</v>
+        <v>6.84</v>
       </c>
       <c r="L55" t="n">
-        <v>105.24</v>
+        <v>98.52</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>182.62</v>
+        <v>178.89</v>
       </c>
       <c r="K56" t="n">
-        <v>-10.68</v>
+        <v>-10.46</v>
       </c>
       <c r="L56" t="n">
-        <v>182.93</v>
+        <v>179.2</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>27</v>
       </c>
       <c r="J57" t="n">
-        <v>165.19</v>
+        <v>154.64</v>
       </c>
       <c r="K57" t="n">
-        <v>5.57</v>
+        <v>5.22</v>
       </c>
       <c r="L57" t="n">
-        <v>165.28</v>
+        <v>154.73</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>26</v>
       </c>
       <c r="J58" t="n">
-        <v>107.47</v>
+        <v>102.99</v>
       </c>
       <c r="K58" t="n">
-        <v>119.54</v>
+        <v>114.56</v>
       </c>
       <c r="L58" t="n">
-        <v>160.75</v>
+        <v>154.05</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>25</v>
       </c>
       <c r="J59" t="n">
-        <v>-10.5</v>
+        <v>-10.29</v>
       </c>
       <c r="K59" t="n">
-        <v>51.94</v>
+        <v>50.88</v>
       </c>
       <c r="L59" t="n">
-        <v>52.99</v>
+        <v>51.91</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>26</v>
       </c>
       <c r="J60" t="n">
-        <v>-43.53</v>
+        <v>-41.72</v>
       </c>
       <c r="K60" t="n">
-        <v>-6.76</v>
+        <v>-6.47</v>
       </c>
       <c r="L60" t="n">
-        <v>44.05</v>
+        <v>42.22</v>
       </c>
     </row>
     <row r="61">
@@ -2656,13 +2656,13 @@
         <v>27</v>
       </c>
       <c r="J62" t="n">
-        <v>-33.66</v>
+        <v>-31.51</v>
       </c>
       <c r="K62" t="n">
-        <v>-56.91</v>
+        <v>-53.27</v>
       </c>
       <c r="L62" t="n">
-        <v>66.12</v>
+        <v>61.9</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>26</v>
       </c>
       <c r="J63" t="n">
-        <v>58.06</v>
+        <v>55.64</v>
       </c>
       <c r="K63" t="n">
-        <v>-54.11</v>
+        <v>-51.85</v>
       </c>
       <c r="L63" t="n">
-        <v>79.37</v>
+        <v>76.06</v>
       </c>
     </row>
     <row r="64">
@@ -2782,13 +2782,13 @@
         <v>26</v>
       </c>
       <c r="J65" t="n">
-        <v>-25.03</v>
+        <v>-23.99</v>
       </c>
       <c r="K65" t="n">
-        <v>98.52</v>
+        <v>94.41</v>
       </c>
       <c r="L65" t="n">
-        <v>101.65</v>
+        <v>97.41</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>23</v>
       </c>
       <c r="J66" t="n">
-        <v>77.73</v>
+        <v>79.25</v>
       </c>
       <c r="K66" t="n">
-        <v>-39.34</v>
+        <v>-40.11</v>
       </c>
       <c r="L66" t="n">
-        <v>87.12</v>
+        <v>88.83</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>21</v>
       </c>
       <c r="J67" t="n">
-        <v>-52.27</v>
+        <v>-55.23</v>
       </c>
       <c r="K67" t="n">
-        <v>67.06</v>
+        <v>70.84999999999999</v>
       </c>
       <c r="L67" t="n">
-        <v>85.02</v>
+        <v>89.83</v>
       </c>
     </row>
     <row r="68">
@@ -2950,13 +2950,13 @@
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>16.55</v>
+        <v>15.49</v>
       </c>
       <c r="K69" t="n">
-        <v>111.78</v>
+        <v>104.65</v>
       </c>
       <c r="L69" t="n">
-        <v>113</v>
+        <v>105.79</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>140.45</v>
+        <v>145.85</v>
       </c>
       <c r="K70" t="n">
-        <v>72.69</v>
+        <v>75.48</v>
       </c>
       <c r="L70" t="n">
-        <v>158.14</v>
+        <v>164.23</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>26</v>
       </c>
       <c r="J71" t="n">
-        <v>89.91</v>
+        <v>86.17</v>
       </c>
       <c r="K71" t="n">
-        <v>-139.71</v>
+        <v>-133.89</v>
       </c>
       <c r="L71" t="n">
-        <v>166.14</v>
+        <v>159.22</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>27</v>
       </c>
       <c r="J72" t="n">
-        <v>-153.51</v>
+        <v>-143.71</v>
       </c>
       <c r="K72" t="n">
-        <v>3.86</v>
+        <v>3.62</v>
       </c>
       <c r="L72" t="n">
-        <v>153.56</v>
+        <v>143.75</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>26</v>
       </c>
       <c r="J73" t="n">
-        <v>137.72</v>
+        <v>131.98</v>
       </c>
       <c r="K73" t="n">
-        <v>-51.64</v>
+        <v>-49.48</v>
       </c>
       <c r="L73" t="n">
-        <v>147.08</v>
+        <v>140.95</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>-46.45</v>
+        <v>-44.52</v>
       </c>
       <c r="K74" t="n">
-        <v>-18.02</v>
+        <v>-17.26</v>
       </c>
       <c r="L74" t="n">
-        <v>49.82</v>
+        <v>47.75</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>-44.34</v>
+        <v>-46.04</v>
       </c>
       <c r="K75" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="L75" t="n">
-        <v>44.37</v>
+        <v>46.08</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>23</v>
       </c>
       <c r="J76" t="n">
-        <v>4.81</v>
+        <v>4.91</v>
       </c>
       <c r="K76" t="n">
-        <v>-57.66</v>
+        <v>-58.79</v>
       </c>
       <c r="L76" t="n">
-        <v>57.86</v>
+        <v>59</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>70.62</v>
+        <v>72.01000000000001</v>
       </c>
       <c r="K77" t="n">
-        <v>-25.53</v>
+        <v>-26.04</v>
       </c>
       <c r="L77" t="n">
-        <v>75.09999999999999</v>
+        <v>76.56999999999999</v>
       </c>
     </row>
     <row r="78">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>-75.5</v>
+        <v>-76.98</v>
       </c>
       <c r="K79" t="n">
-        <v>-2.7</v>
+        <v>-2.75</v>
       </c>
       <c r="L79" t="n">
-        <v>75.55</v>
+        <v>77.03</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>22</v>
       </c>
       <c r="J80" t="n">
-        <v>56.08</v>
+        <v>58.23</v>
       </c>
       <c r="K80" t="n">
-        <v>60.04</v>
+        <v>62.35</v>
       </c>
       <c r="L80" t="n">
-        <v>82.15000000000001</v>
+        <v>85.31</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>-59.38</v>
+        <v>-62.74</v>
       </c>
       <c r="K81" t="n">
-        <v>73.81</v>
+        <v>77.98999999999999</v>
       </c>
       <c r="L81" t="n">
-        <v>94.73</v>
+        <v>100.09</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>-75.48999999999999</v>
+        <v>-79.76000000000001</v>
       </c>
       <c r="K82" t="n">
-        <v>26.15</v>
+        <v>27.63</v>
       </c>
       <c r="L82" t="n">
-        <v>79.89</v>
+        <v>84.41</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>23</v>
       </c>
       <c r="J83" t="n">
-        <v>67.95</v>
+        <v>69.28</v>
       </c>
       <c r="K83" t="n">
-        <v>-151.44</v>
+        <v>-154.4</v>
       </c>
       <c r="L83" t="n">
-        <v>165.98</v>
+        <v>169.24</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>-30.92</v>
+        <v>-32.67</v>
       </c>
       <c r="K84" t="n">
-        <v>32.78</v>
+        <v>34.64</v>
       </c>
       <c r="L84" t="n">
-        <v>45.06</v>
+        <v>47.61</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>27</v>
       </c>
       <c r="J85" t="n">
-        <v>148.97</v>
+        <v>139.46</v>
       </c>
       <c r="K85" t="n">
-        <v>28.33</v>
+        <v>26.52</v>
       </c>
       <c r="L85" t="n">
-        <v>151.64</v>
+        <v>141.96</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>27</v>
       </c>
       <c r="J86" t="n">
-        <v>49.22</v>
+        <v>46.08</v>
       </c>
       <c r="K86" t="n">
-        <v>190.64</v>
+        <v>178.48</v>
       </c>
       <c r="L86" t="n">
-        <v>196.9</v>
+        <v>184.33</v>
       </c>
     </row>
     <row r="87">
@@ -3748,13 +3748,13 @@
         <v>26</v>
       </c>
       <c r="J88" t="n">
-        <v>-23.03</v>
+        <v>-22.07</v>
       </c>
       <c r="K88" t="n">
-        <v>179.17</v>
+        <v>171.7</v>
       </c>
       <c r="L88" t="n">
-        <v>180.64</v>
+        <v>173.11</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-10-01.xlsx
+++ b/output/2025-10-01.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="F14" t="n">
-        <v>4.07</v>
+        <v>5.71</v>
       </c>
       <c r="G14" t="n">
-        <v>49.3</v>
+        <v>32.1</v>
       </c>
       <c r="H14" t="n">
-        <v>4.1</v>
+        <v>60.6</v>
       </c>
       <c r="I14" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J14" t="n">
-        <v>-34.75</v>
+        <v>12.22</v>
       </c>
       <c r="K14" t="n">
-        <v>27.44</v>
+        <v>-28.69</v>
       </c>
       <c r="L14" t="n">
-        <v>44.28</v>
+        <v>31.18</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07:20:26</t>
+          <t>07:20:29</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="F15" t="n">
-        <v>3.66</v>
+        <v>5.03</v>
       </c>
       <c r="G15" t="n">
-        <v>42.6</v>
+        <v>43.1</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="I15" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J15" t="n">
-        <v>-17.31</v>
+        <v>-38.7</v>
       </c>
       <c r="K15" t="n">
-        <v>-51.23</v>
+        <v>-1.78</v>
       </c>
       <c r="L15" t="n">
-        <v>54.07</v>
+        <v>38.74</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07:21:37</t>
+          <t>07:21:17</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>2.17</v>
+        <v>1.95</v>
       </c>
       <c r="F16" t="n">
-        <v>4.74</v>
+        <v>6.52</v>
       </c>
       <c r="G16" t="n">
-        <v>42.7</v>
+        <v>38.9</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>39.8</v>
       </c>
       <c r="I16" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J16" t="n">
-        <v>7.95</v>
+        <v>-26.68</v>
       </c>
       <c r="K16" t="n">
-        <v>63.05</v>
+        <v>-36.01</v>
       </c>
       <c r="L16" t="n">
-        <v>63.54</v>
+        <v>44.82</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07:26:45</t>
+          <t>07:25:27</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="F17" t="n">
-        <v>3.56</v>
+        <v>4.82</v>
       </c>
       <c r="G17" t="n">
-        <v>60.5</v>
+        <v>36.2</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>71.3</v>
       </c>
       <c r="I17" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J17" t="n">
-        <v>-3.82</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>-75.15000000000001</v>
+        <v>3.12</v>
       </c>
       <c r="L17" t="n">
-        <v>75.25</v>
+        <v>8.93</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07:29:11</t>
+          <t>07:26:51</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>1.87</v>
+        <v>2.13</v>
       </c>
       <c r="F18" t="n">
-        <v>4.15</v>
+        <v>6.79</v>
       </c>
       <c r="G18" t="n">
-        <v>54</v>
+        <v>39.5</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="I18" t="n">
         <v>27</v>
       </c>
       <c r="J18" t="n">
-        <v>-37.61</v>
+        <v>-0.67</v>
       </c>
       <c r="K18" t="n">
-        <v>31.42</v>
+        <v>-60.62</v>
       </c>
       <c r="L18" t="n">
-        <v>49</v>
+        <v>60.63</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07:29:49</t>
+          <t>07:27:54</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>2.41</v>
+        <v>1.85</v>
       </c>
       <c r="F19" t="n">
-        <v>5.17</v>
+        <v>6.58</v>
       </c>
       <c r="G19" t="n">
-        <v>49.3</v>
+        <v>56</v>
       </c>
       <c r="H19" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="I19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J19" t="n">
-        <v>-66.72</v>
+        <v>45.53</v>
       </c>
       <c r="K19" t="n">
-        <v>-32.7</v>
+        <v>-35.59</v>
       </c>
       <c r="L19" t="n">
-        <v>74.31</v>
+        <v>57.79</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07:34:31</t>
+          <t>07:32:13</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1.98</v>
+        <v>2.36</v>
       </c>
       <c r="F20" t="n">
-        <v>5.13</v>
+        <v>4.91</v>
       </c>
       <c r="G20" t="n">
-        <v>45.7</v>
+        <v>50</v>
       </c>
       <c r="H20" t="n">
-        <v>3.5</v>
+        <v>18.5</v>
       </c>
       <c r="I20" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J20" t="n">
-        <v>88.77</v>
+        <v>-94.87</v>
       </c>
       <c r="K20" t="n">
-        <v>-3.31</v>
+        <v>25.96</v>
       </c>
       <c r="L20" t="n">
-        <v>88.83</v>
+        <v>98.36</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07:35:15</t>
+          <t>07:33:47</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>2.17</v>
+        <v>1.97</v>
       </c>
       <c r="F21" t="n">
-        <v>4.29</v>
+        <v>3.01</v>
       </c>
       <c r="G21" t="n">
-        <v>51.9</v>
+        <v>41.4</v>
       </c>
       <c r="H21" t="n">
-        <v>3.5</v>
+        <v>41.5</v>
       </c>
       <c r="I21" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J21" t="n">
-        <v>-98.56</v>
+        <v>-18.7</v>
       </c>
       <c r="K21" t="n">
-        <v>21.53</v>
+        <v>-16.09</v>
       </c>
       <c r="L21" t="n">
-        <v>100.88</v>
+        <v>24.67</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07:36:32</t>
+          <t>07:35:42</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>1.95</v>
+        <v>2.2</v>
       </c>
       <c r="F22" t="n">
-        <v>5.14</v>
+        <v>6.9</v>
       </c>
       <c r="G22" t="n">
-        <v>48.5</v>
+        <v>47.6</v>
       </c>
       <c r="H22" t="n">
-        <v>8.300000000000001</v>
+        <v>16.8</v>
       </c>
       <c r="I22" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J22" t="n">
-        <v>21.96</v>
+        <v>99.54000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>-75.08</v>
+        <v>-9.300000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>78.23</v>
+        <v>99.97</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07:40:29</t>
+          <t>07:40:18</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1.93</v>
+        <v>2.16</v>
       </c>
       <c r="F23" t="n">
-        <v>5.53</v>
+        <v>4.97</v>
       </c>
       <c r="G23" t="n">
-        <v>57.3</v>
+        <v>54.9</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>24.2</v>
       </c>
       <c r="I23" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>-123.6</v>
+        <v>79.58</v>
       </c>
       <c r="K23" t="n">
-        <v>82.48</v>
+        <v>146.1</v>
       </c>
       <c r="L23" t="n">
-        <v>148.59</v>
+        <v>166.37</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07:42:42</t>
+          <t>07:41:34</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>2.46</v>
+        <v>3.18</v>
       </c>
       <c r="F24" t="n">
-        <v>5.46</v>
+        <v>6.9</v>
       </c>
       <c r="G24" t="n">
-        <v>56.9</v>
+        <v>47.1</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>43.8</v>
       </c>
       <c r="I24" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J24" t="n">
-        <v>-35.14</v>
+        <v>174.17</v>
       </c>
       <c r="K24" t="n">
-        <v>82.28</v>
+        <v>16.47</v>
       </c>
       <c r="L24" t="n">
-        <v>89.47</v>
+        <v>174.95</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07:44:01</t>
+          <t>07:42:54</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.44</v>
+        <v>2.01</v>
       </c>
       <c r="F25" t="n">
-        <v>5.41</v>
+        <v>2.98</v>
       </c>
       <c r="G25" t="n">
-        <v>38.4</v>
+        <v>52.5</v>
       </c>
       <c r="H25" t="n">
-        <v>2.6</v>
+        <v>28.2</v>
       </c>
       <c r="I25" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J25" t="n">
-        <v>-86.7</v>
+        <v>18.81</v>
       </c>
       <c r="K25" t="n">
-        <v>-111.59</v>
+        <v>-149.27</v>
       </c>
       <c r="L25" t="n">
-        <v>141.31</v>
+        <v>150.45</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07:47:51</t>
+          <t>07:47:05</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1.78</v>
+        <v>2.24</v>
       </c>
       <c r="F26" t="n">
-        <v>6.21</v>
+        <v>6.17</v>
       </c>
       <c r="G26" t="n">
-        <v>53.4</v>
+        <v>51.9</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>33.6</v>
       </c>
       <c r="I26" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="J26" t="n">
-        <v>-168.14</v>
+        <v>124.24</v>
       </c>
       <c r="K26" t="n">
-        <v>100.2</v>
+        <v>107.91</v>
       </c>
       <c r="L26" t="n">
-        <v>195.73</v>
+        <v>164.56</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07:49:50</t>
+          <t>07:48:18</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.41</v>
+        <v>2.16</v>
       </c>
       <c r="F27" t="n">
-        <v>6.56</v>
+        <v>2.61</v>
       </c>
       <c r="G27" t="n">
-        <v>68.90000000000001</v>
+        <v>54.1</v>
       </c>
       <c r="H27" t="n">
-        <v>1.6</v>
+        <v>31.2</v>
       </c>
       <c r="I27" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J27" t="n">
-        <v>200.78</v>
+        <v>-1.28</v>
       </c>
       <c r="K27" t="n">
-        <v>-62.71</v>
+        <v>189.19</v>
       </c>
       <c r="L27" t="n">
-        <v>210.35</v>
+        <v>189.19</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07:51:57</t>
+          <t>07:49:47</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="F28" t="n">
-        <v>5.09</v>
+        <v>4.79</v>
       </c>
       <c r="G28" t="n">
-        <v>53.5</v>
+        <v>56.6</v>
       </c>
       <c r="H28" t="n">
-        <v>0.9</v>
+        <v>32.5</v>
       </c>
       <c r="I28" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>-60.18</v>
+        <v>100.64</v>
       </c>
       <c r="K28" t="n">
-        <v>-142.77</v>
+        <v>-210.87</v>
       </c>
       <c r="L28" t="n">
-        <v>154.93</v>
+        <v>233.65</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08:04:40</t>
+          <t>07:59:48</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.26</v>
+        <v>2.43</v>
       </c>
       <c r="F29" t="n">
-        <v>4.86</v>
+        <v>5.37</v>
       </c>
       <c r="G29" t="n">
-        <v>49.9</v>
+        <v>33.6</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>24.5</v>
       </c>
       <c r="I29" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J29" t="n">
-        <v>-39.16</v>
+        <v>50.01</v>
       </c>
       <c r="K29" t="n">
-        <v>-23.06</v>
+        <v>-22.5</v>
       </c>
       <c r="L29" t="n">
-        <v>45.45</v>
+        <v>54.84</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08:06:34</t>
+          <t>08:01:45</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="F30" t="n">
-        <v>5.44</v>
+        <v>6.18</v>
       </c>
       <c r="G30" t="n">
-        <v>63.7</v>
+        <v>50.7</v>
       </c>
       <c r="H30" t="n">
-        <v>8.199999999999999</v>
+        <v>40.5</v>
       </c>
       <c r="I30" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J30" t="n">
-        <v>47.93</v>
+        <v>19.83</v>
       </c>
       <c r="K30" t="n">
-        <v>20.07</v>
+        <v>-39.18</v>
       </c>
       <c r="L30" t="n">
-        <v>51.96</v>
+        <v>43.91</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08:08:08</t>
+          <t>08:02:59</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.13</v>
+        <v>2.4</v>
       </c>
       <c r="F31" t="n">
-        <v>3.99</v>
+        <v>5.51</v>
       </c>
       <c r="G31" t="n">
-        <v>45.5</v>
+        <v>43.1</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>19.7</v>
       </c>
       <c r="I31" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>49.74</v>
+        <v>52.76</v>
       </c>
       <c r="K31" t="n">
-        <v>35.07</v>
+        <v>-1.39</v>
       </c>
       <c r="L31" t="n">
-        <v>60.86</v>
+        <v>52.78</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08:12:21</t>
+          <t>08:07:59</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.29</v>
+        <v>2.33</v>
       </c>
       <c r="F32" t="n">
         <v>6.9</v>
       </c>
       <c r="G32" t="n">
-        <v>35</v>
+        <v>50.5</v>
       </c>
       <c r="H32" t="n">
-        <v>5.5</v>
+        <v>40.2</v>
       </c>
       <c r="I32" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J32" t="n">
-        <v>-60.29</v>
+        <v>25</v>
       </c>
       <c r="K32" t="n">
-        <v>-10.16</v>
+        <v>69.26000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>61.14</v>
+        <v>73.64</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08:13:14</t>
+          <t>08:09:37</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>1.98</v>
+        <v>2.32</v>
       </c>
       <c r="F33" t="n">
-        <v>3.04</v>
+        <v>3.95</v>
       </c>
       <c r="G33" t="n">
-        <v>42.6</v>
+        <v>43.5</v>
       </c>
       <c r="H33" t="n">
-        <v>2.3</v>
+        <v>18.4</v>
       </c>
       <c r="I33" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J33" t="n">
-        <v>32.75</v>
+        <v>-68.88</v>
       </c>
       <c r="K33" t="n">
-        <v>24.66</v>
+        <v>-4.56</v>
       </c>
       <c r="L33" t="n">
-        <v>40.99</v>
+        <v>69.03</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08:14:43</t>
+          <t>08:12:25</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.56</v>
+        <v>2.03</v>
       </c>
       <c r="F34" t="n">
-        <v>5.02</v>
+        <v>6.89</v>
       </c>
       <c r="G34" t="n">
-        <v>55.1</v>
+        <v>52.3</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="I34" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J34" t="n">
-        <v>-12.51</v>
+        <v>-70.47</v>
       </c>
       <c r="K34" t="n">
-        <v>-77.01000000000001</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>78.02</v>
+        <v>70.95</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08:19:56</t>
+          <t>08:16:52</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>1.99</v>
+        <v>2.79</v>
       </c>
       <c r="F35" t="n">
-        <v>5.44</v>
+        <v>6.9</v>
       </c>
       <c r="G35" t="n">
-        <v>62.8</v>
+        <v>58.1</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>42.4</v>
       </c>
       <c r="I35" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="J35" t="n">
-        <v>44.05</v>
+        <v>-69.88</v>
       </c>
       <c r="K35" t="n">
-        <v>70.17</v>
+        <v>65.22</v>
       </c>
       <c r="L35" t="n">
-        <v>82.84999999999999</v>
+        <v>95.59</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08:22:12</t>
+          <t>08:18:25</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="F36" t="n">
-        <v>4.39</v>
+        <v>5.94</v>
       </c>
       <c r="G36" t="n">
-        <v>54.9</v>
+        <v>62.8</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>45.2</v>
       </c>
       <c r="I36" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J36" t="n">
-        <v>69.61</v>
+        <v>31.78</v>
       </c>
       <c r="K36" t="n">
-        <v>-44.42</v>
+        <v>108.66</v>
       </c>
       <c r="L36" t="n">
-        <v>82.56999999999999</v>
+        <v>113.21</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08:23:52</t>
+          <t>08:19:57</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.48</v>
+        <v>2.15</v>
       </c>
       <c r="F37" t="n">
-        <v>5.16</v>
+        <v>4.37</v>
       </c>
       <c r="G37" t="n">
-        <v>43.5</v>
+        <v>47</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>8.1</v>
       </c>
       <c r="I37" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J37" t="n">
-        <v>-28.3</v>
+        <v>-17.08</v>
       </c>
       <c r="K37" t="n">
-        <v>-101.75</v>
+        <v>111.57</v>
       </c>
       <c r="L37" t="n">
-        <v>105.62</v>
+        <v>112.87</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08:29:52</t>
+          <t>08:25:00</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.38</v>
+        <v>2.04</v>
       </c>
       <c r="F38" t="n">
-        <v>4.79</v>
+        <v>4.14</v>
       </c>
       <c r="G38" t="n">
-        <v>43.3</v>
+        <v>49.9</v>
       </c>
       <c r="H38" t="n">
-        <v>2.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J38" t="n">
-        <v>68.01000000000001</v>
+        <v>166.47</v>
       </c>
       <c r="K38" t="n">
-        <v>-33.88</v>
+        <v>-16.78</v>
       </c>
       <c r="L38" t="n">
-        <v>75.98</v>
+        <v>167.32</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08:30:29</t>
+          <t>08:26:28</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.19</v>
+        <v>2.34</v>
       </c>
       <c r="F39" t="n">
-        <v>5.48</v>
+        <v>5.55</v>
       </c>
       <c r="G39" t="n">
-        <v>46.1</v>
+        <v>60.3</v>
       </c>
       <c r="H39" t="n">
-        <v>2.5</v>
+        <v>9.9</v>
       </c>
       <c r="I39" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J39" t="n">
-        <v>99.89</v>
+        <v>143.67</v>
       </c>
       <c r="K39" t="n">
-        <v>-86.26000000000001</v>
+        <v>66.06</v>
       </c>
       <c r="L39" t="n">
-        <v>131.98</v>
+        <v>158.13</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08:32:54</t>
+          <t>08:27:40</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="F40" t="n">
-        <v>6.14</v>
+        <v>4.81</v>
       </c>
       <c r="G40" t="n">
-        <v>32.6</v>
+        <v>54.9</v>
       </c>
       <c r="H40" t="n">
-        <v>6.4</v>
+        <v>49.1</v>
       </c>
       <c r="I40" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J40" t="n">
-        <v>96.09999999999999</v>
+        <v>286.73</v>
       </c>
       <c r="K40" t="n">
-        <v>109.87</v>
+        <v>-13.52</v>
       </c>
       <c r="L40" t="n">
-        <v>145.97</v>
+        <v>287.04</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08:36:28</t>
+          <t>08:32:34</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.6</v>
+        <v>2.96</v>
       </c>
       <c r="F41" t="n">
-        <v>6.9</v>
+        <v>4.99</v>
       </c>
       <c r="G41" t="n">
-        <v>48.6</v>
+        <v>45.1</v>
       </c>
       <c r="H41" t="n">
-        <v>1.7</v>
+        <v>24.7</v>
       </c>
       <c r="I41" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J41" t="n">
-        <v>9.43</v>
+        <v>-50.86</v>
       </c>
       <c r="K41" t="n">
-        <v>199.35</v>
+        <v>202.54</v>
       </c>
       <c r="L41" t="n">
-        <v>199.57</v>
+        <v>208.82</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08:37:26</t>
+          <t>08:34:54</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>2.13</v>
+        <v>2.56</v>
       </c>
       <c r="F42" t="n">
-        <v>5.93</v>
+        <v>6.9</v>
       </c>
       <c r="G42" t="n">
-        <v>55.8</v>
+        <v>49.7</v>
       </c>
       <c r="H42" t="n">
-        <v>6.7</v>
+        <v>55.3</v>
       </c>
       <c r="I42" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J42" t="n">
-        <v>124.1</v>
+        <v>179.91</v>
       </c>
       <c r="K42" t="n">
-        <v>173.48</v>
+        <v>-48.56</v>
       </c>
       <c r="L42" t="n">
-        <v>213.3</v>
+        <v>186.35</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08:38:26</t>
+          <t>08:36:16</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.37</v>
+        <v>2.2</v>
       </c>
       <c r="F43" t="n">
-        <v>6.9</v>
+        <v>2.75</v>
       </c>
       <c r="G43" t="n">
-        <v>42.8</v>
+        <v>57.7</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>36.6</v>
       </c>
       <c r="I43" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J43" t="n">
-        <v>131.79</v>
+        <v>154.88</v>
       </c>
       <c r="K43" t="n">
-        <v>-120.65</v>
+        <v>-84.55</v>
       </c>
       <c r="L43" t="n">
-        <v>178.67</v>
+        <v>176.45</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08:48:33</t>
+          <t>08:48:31</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.11</v>
+        <v>2.33</v>
       </c>
       <c r="F44" t="n">
-        <v>6.9</v>
+        <v>5.5</v>
       </c>
       <c r="G44" t="n">
-        <v>53.9</v>
+        <v>46.6</v>
       </c>
       <c r="H44" t="n">
-        <v>0.3</v>
+        <v>37.7</v>
       </c>
       <c r="I44" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>-14.2</v>
+        <v>36.84</v>
       </c>
       <c r="K44" t="n">
-        <v>3.54</v>
+        <v>-11.64</v>
       </c>
       <c r="L44" t="n">
-        <v>14.64</v>
+        <v>38.63</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:50:49</t>
+          <t>08:49:12</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.51</v>
+        <v>2.16</v>
       </c>
       <c r="F45" t="n">
-        <v>5.08</v>
+        <v>6.9</v>
       </c>
       <c r="G45" t="n">
-        <v>48.3</v>
+        <v>43.8</v>
       </c>
       <c r="H45" t="n">
-        <v>3.4</v>
+        <v>46.1</v>
       </c>
       <c r="I45" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J45" t="n">
-        <v>-13.94</v>
+        <v>-9.58</v>
       </c>
       <c r="K45" t="n">
-        <v>-43.1</v>
+        <v>31.81</v>
       </c>
       <c r="L45" t="n">
-        <v>45.3</v>
+        <v>33.22</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08:52:16</t>
+          <t>08:50:30</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2.05</v>
+        <v>1.89</v>
       </c>
       <c r="F46" t="n">
-        <v>5.24</v>
+        <v>4.76</v>
       </c>
       <c r="G46" t="n">
-        <v>37.5</v>
+        <v>44.5</v>
       </c>
       <c r="H46" t="n">
-        <v>5.1</v>
+        <v>21.6</v>
       </c>
       <c r="I46" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J46" t="n">
-        <v>-32.24</v>
+        <v>-34.15</v>
       </c>
       <c r="K46" t="n">
-        <v>55.74</v>
+        <v>-7.57</v>
       </c>
       <c r="L46" t="n">
-        <v>64.39</v>
+        <v>34.98</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08:55:48</t>
+          <t>08:55:15</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.01</v>
+        <v>2.41</v>
       </c>
       <c r="F47" t="n">
-        <v>5.35</v>
+        <v>5.51</v>
       </c>
       <c r="G47" t="n">
-        <v>41.6</v>
+        <v>41.7</v>
       </c>
       <c r="H47" t="n">
-        <v>2.4</v>
+        <v>41.4</v>
       </c>
       <c r="I47" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J47" t="n">
-        <v>57.61</v>
+        <v>43.62</v>
       </c>
       <c r="K47" t="n">
-        <v>3.2</v>
+        <v>16.59</v>
       </c>
       <c r="L47" t="n">
-        <v>57.7</v>
+        <v>46.67</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08:57:24</t>
+          <t>08:56:25</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="F48" t="n">
-        <v>6.9</v>
+        <v>6.83</v>
       </c>
       <c r="G48" t="n">
-        <v>55.1</v>
+        <v>48.8</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>56.7</v>
       </c>
       <c r="I48" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J48" t="n">
-        <v>-46.07</v>
+        <v>54.78</v>
       </c>
       <c r="K48" t="n">
-        <v>36.91</v>
+        <v>-36.13</v>
       </c>
       <c r="L48" t="n">
-        <v>59.03</v>
+        <v>65.62</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08:59:35</t>
+          <t>08:57:27</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="F49" t="n">
-        <v>6.83</v>
+        <v>6.9</v>
       </c>
       <c r="G49" t="n">
-        <v>37.3</v>
+        <v>43.1</v>
       </c>
       <c r="H49" t="n">
-        <v>2.6</v>
+        <v>26.2</v>
       </c>
       <c r="I49" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J49" t="n">
-        <v>82.83</v>
+        <v>43.18</v>
       </c>
       <c r="K49" t="n">
-        <v>-27.85</v>
+        <v>-53.1</v>
       </c>
       <c r="L49" t="n">
-        <v>87.38</v>
+        <v>68.44</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09:02:38</t>
+          <t>09:01:41</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.06</v>
+        <v>2.42</v>
       </c>
       <c r="F50" t="n">
-        <v>6.79</v>
+        <v>5.34</v>
       </c>
       <c r="G50" t="n">
-        <v>54.3</v>
+        <v>47.1</v>
       </c>
       <c r="H50" t="n">
-        <v>0.5</v>
+        <v>46.3</v>
       </c>
       <c r="I50" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J50" t="n">
-        <v>-53.07</v>
+        <v>28</v>
       </c>
       <c r="K50" t="n">
-        <v>-90.92</v>
+        <v>93.42</v>
       </c>
       <c r="L50" t="n">
-        <v>105.28</v>
+        <v>97.53</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09:04:00</t>
+          <t>09:03:29</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="F51" t="n">
-        <v>4.05</v>
+        <v>4.72</v>
       </c>
       <c r="G51" t="n">
-        <v>35.9</v>
+        <v>40</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>29.4</v>
       </c>
       <c r="I51" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J51" t="n">
-        <v>48.88</v>
+        <v>-7.86</v>
       </c>
       <c r="K51" t="n">
-        <v>93.23</v>
+        <v>-111.68</v>
       </c>
       <c r="L51" t="n">
-        <v>105.27</v>
+        <v>111.95</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09:05:11</t>
+          <t>09:05:23</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="F52" t="n">
-        <v>5.82</v>
+        <v>6.03</v>
       </c>
       <c r="G52" t="n">
-        <v>54.5</v>
+        <v>42.6</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>37.5</v>
       </c>
       <c r="I52" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J52" t="n">
-        <v>-101.42</v>
+        <v>35.21</v>
       </c>
       <c r="K52" t="n">
-        <v>-23.01</v>
+        <v>56.14</v>
       </c>
       <c r="L52" t="n">
-        <v>104</v>
+        <v>66.27</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09:10:16</t>
+          <t>09:10:13</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>2.27</v>
+        <v>2.5</v>
       </c>
       <c r="F53" t="n">
-        <v>6.9</v>
+        <v>6.89</v>
       </c>
       <c r="G53" t="n">
-        <v>52.7</v>
+        <v>51.6</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="I53" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>-142.07</v>
+        <v>-67.67</v>
       </c>
       <c r="K53" t="n">
-        <v>47.36</v>
+        <v>-15.88</v>
       </c>
       <c r="L53" t="n">
-        <v>149.76</v>
+        <v>69.51000000000001</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09:12:21</t>
+          <t>09:12:18</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="F54" t="n">
-        <v>5.13</v>
+        <v>6.9</v>
       </c>
       <c r="G54" t="n">
-        <v>61.4</v>
+        <v>37.9</v>
       </c>
       <c r="H54" t="n">
-        <v>2.4</v>
+        <v>15.6</v>
       </c>
       <c r="I54" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="J54" t="n">
-        <v>58.33</v>
+        <v>129.26</v>
       </c>
       <c r="K54" t="n">
-        <v>90.83</v>
+        <v>-82.06</v>
       </c>
       <c r="L54" t="n">
-        <v>107.95</v>
+        <v>153.11</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09:13:32</t>
+          <t>09:15:14</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2.19</v>
+        <v>2.63</v>
       </c>
       <c r="F55" t="n">
         <v>6.9</v>
       </c>
       <c r="G55" t="n">
-        <v>60.5</v>
+        <v>37.7</v>
       </c>
       <c r="H55" t="n">
-        <v>0.6</v>
+        <v>31.8</v>
       </c>
       <c r="I55" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="J55" t="n">
-        <v>98.28</v>
+        <v>157.65</v>
       </c>
       <c r="K55" t="n">
-        <v>6.84</v>
+        <v>50.44</v>
       </c>
       <c r="L55" t="n">
-        <v>98.52</v>
+        <v>165.53</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09:18:32</t>
+          <t>09:18:19</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.31</v>
+        <v>2.45</v>
       </c>
       <c r="F56" t="n">
         <v>6.9</v>
       </c>
       <c r="G56" t="n">
-        <v>49.3</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="H56" t="n">
-        <v>3.4</v>
+        <v>43.2</v>
       </c>
       <c r="I56" t="n">
         <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>178.89</v>
+        <v>-65.68000000000001</v>
       </c>
       <c r="K56" t="n">
-        <v>-10.46</v>
+        <v>191.3</v>
       </c>
       <c r="L56" t="n">
-        <v>179.2</v>
+        <v>202.26</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09:19:21</t>
+          <t>09:19:49</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="F57" t="n">
-        <v>6.89</v>
+        <v>5.22</v>
       </c>
       <c r="G57" t="n">
-        <v>49.6</v>
+        <v>42.5</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>50.6</v>
       </c>
       <c r="I57" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J57" t="n">
-        <v>154.64</v>
+        <v>202.23</v>
       </c>
       <c r="K57" t="n">
-        <v>5.22</v>
+        <v>54.61</v>
       </c>
       <c r="L57" t="n">
-        <v>154.73</v>
+        <v>209.47</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09:21:20</t>
+          <t>09:21:03</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.55</v>
+        <v>2.3</v>
       </c>
       <c r="F58" t="n">
         <v>6.9</v>
       </c>
       <c r="G58" t="n">
-        <v>42.2</v>
+        <v>44.6</v>
       </c>
       <c r="H58" t="n">
-        <v>3.3</v>
+        <v>45.1</v>
       </c>
       <c r="I58" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J58" t="n">
-        <v>102.99</v>
+        <v>53.19</v>
       </c>
       <c r="K58" t="n">
-        <v>114.56</v>
+        <v>160.42</v>
       </c>
       <c r="L58" t="n">
-        <v>154.05</v>
+        <v>169.01</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09:34:11</t>
+          <t>09:30:31</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.49</v>
+        <v>2.35</v>
       </c>
       <c r="F59" t="n">
         <v>6.9</v>
       </c>
       <c r="G59" t="n">
-        <v>47.1</v>
+        <v>46.2</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>57.2</v>
       </c>
       <c r="I59" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J59" t="n">
-        <v>-10.29</v>
+        <v>-28.14</v>
       </c>
       <c r="K59" t="n">
-        <v>50.88</v>
+        <v>17.98</v>
       </c>
       <c r="L59" t="n">
-        <v>51.91</v>
+        <v>33.39</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09:35:35</t>
+          <t>09:31:26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.25</v>
+        <v>2.43</v>
       </c>
       <c r="F60" t="n">
-        <v>6.9</v>
+        <v>5.74</v>
       </c>
       <c r="G60" t="n">
-        <v>57.9</v>
+        <v>37.6</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>13.7</v>
       </c>
       <c r="I60" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J60" t="n">
-        <v>-41.72</v>
+        <v>26.64</v>
       </c>
       <c r="K60" t="n">
-        <v>-6.47</v>
+        <v>22.6</v>
       </c>
       <c r="L60" t="n">
-        <v>42.22</v>
+        <v>34.93</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09:37:07</t>
+          <t>09:33:44</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="F61" t="n">
-        <v>5.34</v>
+        <v>6.9</v>
       </c>
       <c r="G61" t="n">
-        <v>57.9</v>
+        <v>60.9</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>50.9</v>
       </c>
       <c r="I61" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>-42.9</v>
+        <v>-52.97</v>
       </c>
       <c r="K61" t="n">
-        <v>-23.87</v>
+        <v>-12.87</v>
       </c>
       <c r="L61" t="n">
-        <v>49.1</v>
+        <v>54.51</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09:41:14</t>
+          <t>09:38:04</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.51</v>
+        <v>2.2</v>
       </c>
       <c r="F62" t="n">
         <v>6.9</v>
       </c>
       <c r="G62" t="n">
-        <v>52.6</v>
+        <v>51.5</v>
       </c>
       <c r="H62" t="n">
-        <v>0.1</v>
+        <v>3.1</v>
       </c>
       <c r="I62" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J62" t="n">
-        <v>-31.51</v>
+        <v>13.95</v>
       </c>
       <c r="K62" t="n">
-        <v>-53.27</v>
+        <v>83.34</v>
       </c>
       <c r="L62" t="n">
-        <v>61.9</v>
+        <v>84.5</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09:43:05</t>
+          <t>09:39:41</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="F63" t="n">
         <v>6.9</v>
       </c>
       <c r="G63" t="n">
-        <v>44.2</v>
+        <v>48.9</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="I63" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>55.64</v>
+        <v>12.43</v>
       </c>
       <c r="K63" t="n">
-        <v>-51.85</v>
+        <v>-64.29000000000001</v>
       </c>
       <c r="L63" t="n">
-        <v>76.06</v>
+        <v>65.48</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09:44:38</t>
+          <t>09:42:06</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>2.87</v>
+        <v>2.49</v>
       </c>
       <c r="F64" t="n">
-        <v>5.24</v>
+        <v>5.71</v>
       </c>
       <c r="G64" t="n">
-        <v>40.8</v>
+        <v>52.1</v>
       </c>
       <c r="H64" t="n">
-        <v>7</v>
+        <v>58.5</v>
       </c>
       <c r="I64" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="J64" t="n">
-        <v>-53.23</v>
+        <v>-33.51</v>
       </c>
       <c r="K64" t="n">
-        <v>-20.57</v>
+        <v>-61.31</v>
       </c>
       <c r="L64" t="n">
-        <v>57.06</v>
+        <v>69.87</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09:50:02</t>
+          <t>09:47:52</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2.21</v>
+        <v>2.5</v>
       </c>
       <c r="F65" t="n">
-        <v>6.43</v>
+        <v>6.23</v>
       </c>
       <c r="G65" t="n">
-        <v>48.5</v>
+        <v>49.9</v>
       </c>
       <c r="H65" t="n">
-        <v>0</v>
+        <v>24.6</v>
       </c>
       <c r="I65" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J65" t="n">
-        <v>-23.99</v>
+        <v>-109.85</v>
       </c>
       <c r="K65" t="n">
-        <v>94.41</v>
+        <v>49.94</v>
       </c>
       <c r="L65" t="n">
-        <v>97.41</v>
+        <v>120.67</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09:51:35</t>
+          <t>09:49:50</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>2.44</v>
+        <v>2.66</v>
       </c>
       <c r="F66" t="n">
-        <v>4.27</v>
+        <v>6.52</v>
       </c>
       <c r="G66" t="n">
-        <v>53.8</v>
+        <v>43.1</v>
       </c>
       <c r="H66" t="n">
-        <v>0</v>
+        <v>37.7</v>
       </c>
       <c r="I66" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J66" t="n">
-        <v>79.25</v>
+        <v>25.32</v>
       </c>
       <c r="K66" t="n">
-        <v>-40.11</v>
+        <v>-129.33</v>
       </c>
       <c r="L66" t="n">
-        <v>88.83</v>
+        <v>131.79</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09:53:24</t>
+          <t>09:51:52</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>2.15</v>
+        <v>2.64</v>
       </c>
       <c r="F67" t="n">
         <v>6.9</v>
       </c>
       <c r="G67" t="n">
-        <v>29.8</v>
+        <v>53.2</v>
       </c>
       <c r="H67" t="n">
-        <v>0</v>
+        <v>23.1</v>
       </c>
       <c r="I67" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J67" t="n">
-        <v>-55.23</v>
+        <v>61.9</v>
       </c>
       <c r="K67" t="n">
-        <v>70.84999999999999</v>
+        <v>-32.82</v>
       </c>
       <c r="L67" t="n">
-        <v>89.83</v>
+        <v>70.06</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09:58:20</t>
+          <t>09:56:44</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="F68" t="n">
-        <v>5.69</v>
+        <v>3.56</v>
       </c>
       <c r="G68" t="n">
-        <v>41.1</v>
+        <v>56.5</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>28.9</v>
       </c>
       <c r="I68" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J68" t="n">
-        <v>120.65</v>
+        <v>147.81</v>
       </c>
       <c r="K68" t="n">
-        <v>-44.79</v>
+        <v>-12.09</v>
       </c>
       <c r="L68" t="n">
-        <v>128.69</v>
+        <v>148.3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09:59:34</t>
+          <t>09:58:50</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>2.56</v>
+        <v>2.39</v>
       </c>
       <c r="F69" t="n">
-        <v>5.19</v>
+        <v>5.36</v>
       </c>
       <c r="G69" t="n">
-        <v>63</v>
+        <v>59.1</v>
       </c>
       <c r="H69" t="n">
-        <v>1.2</v>
+        <v>32.1</v>
       </c>
       <c r="I69" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="J69" t="n">
-        <v>15.49</v>
+        <v>106.65</v>
       </c>
       <c r="K69" t="n">
-        <v>104.65</v>
+        <v>-123.13</v>
       </c>
       <c r="L69" t="n">
-        <v>105.79</v>
+        <v>162.89</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>10:01:36</t>
+          <t>10:01:27</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.73</v>
+        <v>2.29</v>
       </c>
       <c r="F70" t="n">
         <v>6.9</v>
       </c>
       <c r="G70" t="n">
-        <v>53.2</v>
+        <v>45.5</v>
       </c>
       <c r="H70" t="n">
-        <v>4.5</v>
+        <v>46.2</v>
       </c>
       <c r="I70" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J70" t="n">
-        <v>145.85</v>
+        <v>-27.39</v>
       </c>
       <c r="K70" t="n">
-        <v>75.48</v>
+        <v>-122.3</v>
       </c>
       <c r="L70" t="n">
-        <v>164.23</v>
+        <v>125.33</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>10:06:56</t>
+          <t>10:05:40</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.52</v>
+        <v>2.39</v>
       </c>
       <c r="F71" t="n">
-        <v>6.66</v>
+        <v>6.01</v>
       </c>
       <c r="G71" t="n">
-        <v>58.7</v>
+        <v>53.7</v>
       </c>
       <c r="H71" t="n">
-        <v>1.8</v>
+        <v>61.3</v>
       </c>
       <c r="I71" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J71" t="n">
-        <v>86.17</v>
+        <v>-108.01</v>
       </c>
       <c r="K71" t="n">
-        <v>-133.89</v>
+        <v>164.43</v>
       </c>
       <c r="L71" t="n">
-        <v>159.22</v>
+        <v>196.73</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10:08:04</t>
+          <t>10:07:32</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>2.73</v>
+        <v>2.49</v>
       </c>
       <c r="F72" t="n">
         <v>6.9</v>
       </c>
       <c r="G72" t="n">
-        <v>56.2</v>
+        <v>41.4</v>
       </c>
       <c r="H72" t="n">
-        <v>5.2</v>
+        <v>32.7</v>
       </c>
       <c r="I72" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J72" t="n">
-        <v>-143.71</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="K72" t="n">
-        <v>3.62</v>
+        <v>146.38</v>
       </c>
       <c r="L72" t="n">
-        <v>143.75</v>
+        <v>171.09</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10:10:24</t>
+          <t>10:09:38</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.39</v>
+        <v>2.29</v>
       </c>
       <c r="F73" t="n">
-        <v>5.5</v>
+        <v>6.55</v>
       </c>
       <c r="G73" t="n">
-        <v>55.8</v>
+        <v>46.3</v>
       </c>
       <c r="H73" t="n">
-        <v>3.6</v>
+        <v>54.3</v>
       </c>
       <c r="I73" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J73" t="n">
-        <v>131.98</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="K73" t="n">
-        <v>-49.48</v>
+        <v>162.81</v>
       </c>
       <c r="L73" t="n">
-        <v>140.95</v>
+        <v>163.03</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10:22:37</t>
+          <t>10:18:56</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>2.72</v>
+        <v>2.32</v>
       </c>
       <c r="F74" t="n">
-        <v>5.57</v>
+        <v>6.9</v>
       </c>
       <c r="G74" t="n">
-        <v>52.4</v>
+        <v>54.4</v>
       </c>
       <c r="H74" t="n">
-        <v>0</v>
+        <v>24.6</v>
       </c>
       <c r="I74" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>-44.52</v>
+        <v>-28.59</v>
       </c>
       <c r="K74" t="n">
-        <v>-17.26</v>
+        <v>-19.91</v>
       </c>
       <c r="L74" t="n">
-        <v>47.75</v>
+        <v>34.84</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10:24:06</t>
+          <t>10:20:12</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
       <c r="F75" t="n">
-        <v>6.9</v>
+        <v>6.57</v>
       </c>
       <c r="G75" t="n">
-        <v>37.5</v>
+        <v>43.5</v>
       </c>
       <c r="H75" t="n">
-        <v>3</v>
+        <v>69.5</v>
       </c>
       <c r="I75" t="n">
         <v>22</v>
       </c>
       <c r="J75" t="n">
-        <v>-46.04</v>
+        <v>13.33</v>
       </c>
       <c r="K75" t="n">
-        <v>1.8</v>
+        <v>51.75</v>
       </c>
       <c r="L75" t="n">
-        <v>46.08</v>
+        <v>53.44</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10:25:31</t>
+          <t>10:22:11</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>2.85</v>
+        <v>2.77</v>
       </c>
       <c r="F76" t="n">
-        <v>5.97</v>
+        <v>6.9</v>
       </c>
       <c r="G76" t="n">
-        <v>50.5</v>
+        <v>53.9</v>
       </c>
       <c r="H76" t="n">
-        <v>0</v>
+        <v>24.4</v>
       </c>
       <c r="I76" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J76" t="n">
-        <v>4.91</v>
+        <v>48.91</v>
       </c>
       <c r="K76" t="n">
-        <v>-58.79</v>
+        <v>27.26</v>
       </c>
       <c r="L76" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10:29:30</t>
+          <t>10:26:36</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>2.92</v>
+        <v>2.51</v>
       </c>
       <c r="F77" t="n">
         <v>6.9</v>
       </c>
       <c r="G77" t="n">
-        <v>58.2</v>
+        <v>54.1</v>
       </c>
       <c r="H77" t="n">
-        <v>6.3</v>
+        <v>28.8</v>
       </c>
       <c r="I77" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J77" t="n">
-        <v>72.01000000000001</v>
+        <v>3.43</v>
       </c>
       <c r="K77" t="n">
-        <v>-26.04</v>
+        <v>-60.96</v>
       </c>
       <c r="L77" t="n">
-        <v>76.56999999999999</v>
+        <v>61.06</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>10:31:04</t>
+          <t>10:27:27</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2.35</v>
+        <v>2.41</v>
       </c>
       <c r="F78" t="n">
-        <v>4.19</v>
+        <v>5.13</v>
       </c>
       <c r="G78" t="n">
-        <v>53.5</v>
+        <v>49.4</v>
       </c>
       <c r="H78" t="n">
-        <v>0</v>
+        <v>36.6</v>
       </c>
       <c r="I78" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J78" t="n">
-        <v>-62.59</v>
+        <v>-24.65</v>
       </c>
       <c r="K78" t="n">
-        <v>-17.54</v>
+        <v>70.61</v>
       </c>
       <c r="L78" t="n">
-        <v>65</v>
+        <v>74.79000000000001</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>10:33:29</t>
+          <t>10:29:13</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="F79" t="n">
-        <v>5.51</v>
+        <v>6.48</v>
       </c>
       <c r="G79" t="n">
-        <v>47.2</v>
+        <v>47.4</v>
       </c>
       <c r="H79" t="n">
-        <v>0</v>
+        <v>23.4</v>
       </c>
       <c r="I79" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J79" t="n">
-        <v>-76.98</v>
+        <v>-17.15</v>
       </c>
       <c r="K79" t="n">
-        <v>-2.75</v>
+        <v>-59.97</v>
       </c>
       <c r="L79" t="n">
-        <v>77.03</v>
+        <v>62.37</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>10:38:14</t>
+          <t>10:34:35</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>2.64</v>
+        <v>2.17</v>
       </c>
       <c r="F80" t="n">
-        <v>6.9</v>
+        <v>5.04</v>
       </c>
       <c r="G80" t="n">
-        <v>66.7</v>
+        <v>57.9</v>
       </c>
       <c r="H80" t="n">
-        <v>3</v>
+        <v>34.7</v>
       </c>
       <c r="I80" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J80" t="n">
-        <v>58.23</v>
+        <v>-110.53</v>
       </c>
       <c r="K80" t="n">
-        <v>62.35</v>
+        <v>40.11</v>
       </c>
       <c r="L80" t="n">
-        <v>85.31</v>
+        <v>117.59</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10:39:49</t>
+          <t>10:36:55</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2.49</v>
+        <v>2.33</v>
       </c>
       <c r="F81" t="n">
-        <v>6.9</v>
+        <v>4.33</v>
       </c>
       <c r="G81" t="n">
-        <v>34.7</v>
+        <v>55.1</v>
       </c>
       <c r="H81" t="n">
-        <v>0</v>
+        <v>69.2</v>
       </c>
       <c r="I81" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J81" t="n">
-        <v>-62.74</v>
+        <v>-14.32</v>
       </c>
       <c r="K81" t="n">
-        <v>77.98999999999999</v>
+        <v>96.79000000000001</v>
       </c>
       <c r="L81" t="n">
-        <v>100.09</v>
+        <v>97.84</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10:40:52</t>
+          <t>10:38:55</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.37</v>
+        <v>2.83</v>
       </c>
       <c r="F82" t="n">
-        <v>4.03</v>
+        <v>6.9</v>
       </c>
       <c r="G82" t="n">
-        <v>42.9</v>
+        <v>49.2</v>
       </c>
       <c r="H82" t="n">
-        <v>0</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="I82" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J82" t="n">
-        <v>-79.76000000000001</v>
+        <v>88.16</v>
       </c>
       <c r="K82" t="n">
-        <v>27.63</v>
+        <v>17.71</v>
       </c>
       <c r="L82" t="n">
-        <v>84.41</v>
+        <v>89.92</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10:45:48</t>
+          <t>10:42:51</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.23</v>
+        <v>2.7</v>
       </c>
       <c r="F83" t="n">
-        <v>6.02</v>
+        <v>6.9</v>
       </c>
       <c r="G83" t="n">
-        <v>31.7</v>
+        <v>47.6</v>
       </c>
       <c r="H83" t="n">
-        <v>0.9</v>
+        <v>85</v>
       </c>
       <c r="I83" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J83" t="n">
-        <v>69.28</v>
+        <v>102.25</v>
       </c>
       <c r="K83" t="n">
-        <v>-154.4</v>
+        <v>-397.51</v>
       </c>
       <c r="L83" t="n">
-        <v>169.24</v>
+        <v>410.45</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10:47:05</t>
+          <t>10:43:58</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2.69</v>
+        <v>2.63</v>
       </c>
       <c r="F84" t="n">
-        <v>6.72</v>
+        <v>6.9</v>
       </c>
       <c r="G84" t="n">
-        <v>44.1</v>
+        <v>42.7</v>
       </c>
       <c r="H84" t="n">
-        <v>5.6</v>
+        <v>3</v>
       </c>
       <c r="I84" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J84" t="n">
-        <v>-32.67</v>
+        <v>-105.03</v>
       </c>
       <c r="K84" t="n">
-        <v>34.64</v>
+        <v>-109.87</v>
       </c>
       <c r="L84" t="n">
-        <v>47.61</v>
+        <v>152</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10:48:16</t>
+          <t>10:46:11</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>2.72</v>
+        <v>2.29</v>
       </c>
       <c r="F85" t="n">
         <v>6.9</v>
       </c>
       <c r="G85" t="n">
-        <v>37.1</v>
+        <v>51.9</v>
       </c>
       <c r="H85" t="n">
-        <v>0</v>
+        <v>30.1</v>
       </c>
       <c r="I85" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J85" t="n">
-        <v>139.46</v>
+        <v>55.64</v>
       </c>
       <c r="K85" t="n">
-        <v>26.52</v>
+        <v>117.1</v>
       </c>
       <c r="L85" t="n">
-        <v>141.96</v>
+        <v>129.65</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10:53:38</t>
+          <t>10:51:26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>2.22</v>
+        <v>2.48</v>
       </c>
       <c r="F86" t="n">
-        <v>5.03</v>
+        <v>5.87</v>
       </c>
       <c r="G86" t="n">
-        <v>42</v>
+        <v>55.9</v>
       </c>
       <c r="H86" t="n">
-        <v>0</v>
+        <v>35.4</v>
       </c>
       <c r="I86" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J86" t="n">
-        <v>46.08</v>
+        <v>97.02</v>
       </c>
       <c r="K86" t="n">
-        <v>178.48</v>
+        <v>-211.86</v>
       </c>
       <c r="L86" t="n">
-        <v>184.33</v>
+        <v>233.01</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10:55:08</t>
+          <t>10:53:02</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2.49</v>
+        <v>2.89</v>
       </c>
       <c r="F87" t="n">
         <v>6.9</v>
       </c>
       <c r="G87" t="n">
-        <v>52.3</v>
+        <v>51.7</v>
       </c>
       <c r="H87" t="n">
-        <v>0</v>
+        <v>41.8</v>
       </c>
       <c r="I87" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J87" t="n">
-        <v>140.13</v>
+        <v>-67.73999999999999</v>
       </c>
       <c r="K87" t="n">
-        <v>67.66</v>
+        <v>-244.71</v>
       </c>
       <c r="L87" t="n">
-        <v>155.61</v>
+        <v>253.92</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10:57:04</t>
+          <t>10:53:33</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="F88" t="n">
-        <v>6.78</v>
+        <v>6.9</v>
       </c>
       <c r="G88" t="n">
-        <v>46.8</v>
+        <v>63.5</v>
       </c>
       <c r="H88" t="n">
-        <v>0</v>
+        <v>19.2</v>
       </c>
       <c r="I88" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J88" t="n">
-        <v>-22.07</v>
+        <v>-27.34</v>
       </c>
       <c r="K88" t="n">
-        <v>171.7</v>
+        <v>146.9</v>
       </c>
       <c r="L88" t="n">
-        <v>173.11</v>
+        <v>149.43</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-10-01.xlsx
+++ b/output/2025-10-01.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1</v>
+        <v>1.92</v>
       </c>
       <c r="F14" t="n">
-        <v>5.71</v>
+        <v>3.6</v>
       </c>
       <c r="G14" t="n">
-        <v>32.1</v>
+        <v>46.8</v>
       </c>
       <c r="H14" t="n">
-        <v>60.6</v>
+        <v>22.3</v>
       </c>
       <c r="I14" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>12.22</v>
+        <v>0.83</v>
       </c>
       <c r="K14" t="n">
-        <v>-28.69</v>
+        <v>-40.34</v>
       </c>
       <c r="L14" t="n">
-        <v>31.18</v>
+        <v>40.34</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>07:20:29</t>
+          <t>07:18:54</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>2.16</v>
+        <v>1.93</v>
       </c>
       <c r="F15" t="n">
-        <v>5.03</v>
+        <v>4.75</v>
       </c>
       <c r="G15" t="n">
-        <v>43.1</v>
+        <v>44.7</v>
       </c>
       <c r="H15" t="n">
-        <v>70.09999999999999</v>
+        <v>30.4</v>
       </c>
       <c r="I15" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J15" t="n">
-        <v>-38.7</v>
+        <v>-28.76</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.78</v>
+        <v>-26.47</v>
       </c>
       <c r="L15" t="n">
-        <v>38.74</v>
+        <v>39.09</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>07:21:17</t>
+          <t>07:21:22</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1.95</v>
+        <v>1.69</v>
       </c>
       <c r="F16" t="n">
-        <v>6.52</v>
+        <v>3.06</v>
       </c>
       <c r="G16" t="n">
-        <v>38.9</v>
+        <v>59.2</v>
       </c>
       <c r="H16" t="n">
-        <v>39.8</v>
+        <v>24</v>
       </c>
       <c r="I16" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J16" t="n">
-        <v>-26.68</v>
+        <v>-30.21</v>
       </c>
       <c r="K16" t="n">
-        <v>-36.01</v>
+        <v>6.16</v>
       </c>
       <c r="L16" t="n">
-        <v>44.82</v>
+        <v>30.83</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>07:25:27</t>
+          <t>07:25:41</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="F17" t="n">
-        <v>4.82</v>
+        <v>4.99</v>
       </c>
       <c r="G17" t="n">
-        <v>36.2</v>
+        <v>39.5</v>
       </c>
       <c r="H17" t="n">
-        <v>71.3</v>
+        <v>39.3</v>
       </c>
       <c r="I17" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J17" t="n">
-        <v>8.369999999999999</v>
+        <v>-37.58</v>
       </c>
       <c r="K17" t="n">
-        <v>3.12</v>
+        <v>-56.06</v>
       </c>
       <c r="L17" t="n">
-        <v>8.93</v>
+        <v>67.5</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>07:26:51</t>
+          <t>07:28:03</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>2.13</v>
+        <v>1.92</v>
       </c>
       <c r="F18" t="n">
-        <v>6.79</v>
+        <v>3.95</v>
       </c>
       <c r="G18" t="n">
-        <v>39.5</v>
+        <v>41.3</v>
       </c>
       <c r="H18" t="n">
-        <v>35</v>
+        <v>20.3</v>
       </c>
       <c r="I18" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.67</v>
+        <v>-27.19</v>
       </c>
       <c r="K18" t="n">
-        <v>-60.62</v>
+        <v>55.77</v>
       </c>
       <c r="L18" t="n">
-        <v>60.63</v>
+        <v>62.05</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>07:27:54</t>
+          <t>07:30:25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="F19" t="n">
-        <v>6.58</v>
+        <v>3.32</v>
       </c>
       <c r="G19" t="n">
-        <v>56</v>
+        <v>41.7</v>
       </c>
       <c r="H19" t="n">
-        <v>2.1</v>
+        <v>27.6</v>
       </c>
       <c r="I19" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J19" t="n">
-        <v>45.53</v>
+        <v>0.16</v>
       </c>
       <c r="K19" t="n">
-        <v>-35.59</v>
+        <v>-39.92</v>
       </c>
       <c r="L19" t="n">
-        <v>57.79</v>
+        <v>39.92</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>07:32:13</t>
+          <t>07:35:30</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>2.36</v>
+        <v>2.28</v>
       </c>
       <c r="F20" t="n">
-        <v>4.91</v>
+        <v>6.9</v>
       </c>
       <c r="G20" t="n">
-        <v>50</v>
+        <v>58.7</v>
       </c>
       <c r="H20" t="n">
-        <v>18.5</v>
+        <v>11.5</v>
       </c>
       <c r="I20" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J20" t="n">
-        <v>-94.87</v>
+        <v>57.68</v>
       </c>
       <c r="K20" t="n">
-        <v>25.96</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>98.36</v>
+        <v>58.52</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>07:33:47</t>
+          <t>07:37:54</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>1.97</v>
+        <v>2.19</v>
       </c>
       <c r="F21" t="n">
-        <v>3.01</v>
+        <v>4.07</v>
       </c>
       <c r="G21" t="n">
-        <v>41.4</v>
+        <v>41.2</v>
       </c>
       <c r="H21" t="n">
-        <v>41.5</v>
+        <v>26.1</v>
       </c>
       <c r="I21" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="J21" t="n">
-        <v>-18.7</v>
+        <v>89.98</v>
       </c>
       <c r="K21" t="n">
-        <v>-16.09</v>
+        <v>6.45</v>
       </c>
       <c r="L21" t="n">
-        <v>24.67</v>
+        <v>90.22</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>07:35:42</t>
+          <t>07:39:23</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="F22" t="n">
-        <v>6.9</v>
+        <v>5.42</v>
       </c>
       <c r="G22" t="n">
-        <v>47.6</v>
+        <v>50</v>
       </c>
       <c r="H22" t="n">
-        <v>16.8</v>
+        <v>40.3</v>
       </c>
       <c r="I22" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="J22" t="n">
-        <v>99.54000000000001</v>
+        <v>-37.23</v>
       </c>
       <c r="K22" t="n">
-        <v>-9.300000000000001</v>
+        <v>-70.39</v>
       </c>
       <c r="L22" t="n">
-        <v>99.97</v>
+        <v>79.63</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>07:40:18</t>
+          <t>07:44:07</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="F23" t="n">
-        <v>4.97</v>
+        <v>6.9</v>
       </c>
       <c r="G23" t="n">
-        <v>54.9</v>
+        <v>44.4</v>
       </c>
       <c r="H23" t="n">
-        <v>24.2</v>
+        <v>39.3</v>
       </c>
       <c r="I23" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J23" t="n">
-        <v>79.58</v>
+        <v>100.73</v>
       </c>
       <c r="K23" t="n">
-        <v>146.1</v>
+        <v>-129.85</v>
       </c>
       <c r="L23" t="n">
-        <v>166.37</v>
+        <v>164.34</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>07:41:34</t>
+          <t>07:45:38</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>3.18</v>
+        <v>2.03</v>
       </c>
       <c r="F24" t="n">
         <v>6.9</v>
       </c>
       <c r="G24" t="n">
-        <v>47.1</v>
+        <v>42.9</v>
       </c>
       <c r="H24" t="n">
-        <v>43.8</v>
+        <v>54.9</v>
       </c>
       <c r="I24" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>174.17</v>
+        <v>130.48</v>
       </c>
       <c r="K24" t="n">
-        <v>16.47</v>
+        <v>40.76</v>
       </c>
       <c r="L24" t="n">
-        <v>174.95</v>
+        <v>136.7</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>07:42:54</t>
+          <t>07:46:55</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>2.01</v>
+        <v>2.41</v>
       </c>
       <c r="F25" t="n">
-        <v>2.98</v>
+        <v>6.9</v>
       </c>
       <c r="G25" t="n">
-        <v>52.5</v>
+        <v>55.1</v>
       </c>
       <c r="H25" t="n">
-        <v>28.2</v>
+        <v>29.5</v>
       </c>
       <c r="I25" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J25" t="n">
-        <v>18.81</v>
+        <v>79.8</v>
       </c>
       <c r="K25" t="n">
-        <v>-149.27</v>
+        <v>-112.34</v>
       </c>
       <c r="L25" t="n">
-        <v>150.45</v>
+        <v>137.8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>07:47:05</t>
+          <t>07:50:24</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="F26" t="n">
-        <v>6.17</v>
+        <v>5.28</v>
       </c>
       <c r="G26" t="n">
-        <v>51.9</v>
+        <v>57.8</v>
       </c>
       <c r="H26" t="n">
-        <v>33.6</v>
+        <v>13.7</v>
       </c>
       <c r="I26" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>124.24</v>
+        <v>193.01</v>
       </c>
       <c r="K26" t="n">
-        <v>107.91</v>
+        <v>-178.65</v>
       </c>
       <c r="L26" t="n">
-        <v>164.56</v>
+        <v>262.99</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>07:48:18</t>
+          <t>07:52:22</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>2.16</v>
+        <v>2.21</v>
       </c>
       <c r="F27" t="n">
-        <v>2.61</v>
+        <v>6.08</v>
       </c>
       <c r="G27" t="n">
-        <v>54.1</v>
+        <v>39.7</v>
       </c>
       <c r="H27" t="n">
-        <v>31.2</v>
+        <v>24.5</v>
       </c>
       <c r="I27" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J27" t="n">
-        <v>-1.28</v>
+        <v>-200.87</v>
       </c>
       <c r="K27" t="n">
-        <v>189.19</v>
+        <v>127.13</v>
       </c>
       <c r="L27" t="n">
-        <v>189.19</v>
+        <v>237.72</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>07:49:47</t>
+          <t>07:53:50</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>2.2</v>
+        <v>2.38</v>
       </c>
       <c r="F28" t="n">
-        <v>4.79</v>
+        <v>6.54</v>
       </c>
       <c r="G28" t="n">
-        <v>56.6</v>
+        <v>56.9</v>
       </c>
       <c r="H28" t="n">
-        <v>32.5</v>
+        <v>24.9</v>
       </c>
       <c r="I28" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J28" t="n">
-        <v>100.64</v>
+        <v>164.29</v>
       </c>
       <c r="K28" t="n">
-        <v>-210.87</v>
+        <v>74.12</v>
       </c>
       <c r="L28" t="n">
-        <v>233.65</v>
+        <v>180.23</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>07:59:48</t>
+          <t>08:03:52</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.43</v>
+        <v>1.97</v>
       </c>
       <c r="F29" t="n">
-        <v>5.37</v>
+        <v>6.39</v>
       </c>
       <c r="G29" t="n">
-        <v>33.6</v>
+        <v>39.1</v>
       </c>
       <c r="H29" t="n">
-        <v>24.5</v>
+        <v>26.5</v>
       </c>
       <c r="I29" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J29" t="n">
-        <v>50.01</v>
+        <v>-9.15</v>
       </c>
       <c r="K29" t="n">
-        <v>-22.5</v>
+        <v>18.42</v>
       </c>
       <c r="L29" t="n">
-        <v>54.84</v>
+        <v>20.57</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>08:01:45</t>
+          <t>08:04:57</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>2.34</v>
+        <v>1.94</v>
       </c>
       <c r="F30" t="n">
-        <v>6.18</v>
+        <v>5.1</v>
       </c>
       <c r="G30" t="n">
-        <v>50.7</v>
+        <v>59.8</v>
       </c>
       <c r="H30" t="n">
-        <v>40.5</v>
+        <v>42.9</v>
       </c>
       <c r="I30" t="n">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="J30" t="n">
-        <v>19.83</v>
+        <v>-25.34</v>
       </c>
       <c r="K30" t="n">
-        <v>-39.18</v>
+        <v>-22.49</v>
       </c>
       <c r="L30" t="n">
-        <v>43.91</v>
+        <v>33.88</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>08:02:59</t>
+          <t>08:06:52</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>2.4</v>
+        <v>2.21</v>
       </c>
       <c r="F31" t="n">
-        <v>5.51</v>
+        <v>6.9</v>
       </c>
       <c r="G31" t="n">
-        <v>43.1</v>
+        <v>52.4</v>
       </c>
       <c r="H31" t="n">
-        <v>19.7</v>
+        <v>13</v>
       </c>
       <c r="I31" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
       <c r="J31" t="n">
-        <v>52.76</v>
+        <v>-37.37</v>
       </c>
       <c r="K31" t="n">
-        <v>-1.39</v>
+        <v>25.6</v>
       </c>
       <c r="L31" t="n">
-        <v>52.78</v>
+        <v>45.3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>08:07:59</t>
+          <t>08:10:35</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>2.33</v>
+        <v>2.26</v>
       </c>
       <c r="F32" t="n">
-        <v>6.9</v>
+        <v>5.98</v>
       </c>
       <c r="G32" t="n">
-        <v>50.5</v>
+        <v>52.4</v>
       </c>
       <c r="H32" t="n">
-        <v>40.2</v>
+        <v>2.4</v>
       </c>
       <c r="I32" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J32" t="n">
-        <v>25</v>
+        <v>-10.64</v>
       </c>
       <c r="K32" t="n">
-        <v>69.26000000000001</v>
+        <v>35.99</v>
       </c>
       <c r="L32" t="n">
-        <v>73.64</v>
+        <v>37.53</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>08:09:37</t>
+          <t>08:11:45</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>2.32</v>
+        <v>1.99</v>
       </c>
       <c r="F33" t="n">
-        <v>3.95</v>
+        <v>5.87</v>
       </c>
       <c r="G33" t="n">
-        <v>43.5</v>
+        <v>55.7</v>
       </c>
       <c r="H33" t="n">
-        <v>18.4</v>
+        <v>25.9</v>
       </c>
       <c r="I33" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J33" t="n">
-        <v>-68.88</v>
+        <v>-5.29</v>
       </c>
       <c r="K33" t="n">
-        <v>-4.56</v>
+        <v>54.9</v>
       </c>
       <c r="L33" t="n">
-        <v>69.03</v>
+        <v>55.15</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>08:12:25</t>
+          <t>08:12:57</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.03</v>
+        <v>1.99</v>
       </c>
       <c r="F34" t="n">
-        <v>6.89</v>
+        <v>6.9</v>
       </c>
       <c r="G34" t="n">
-        <v>52.3</v>
+        <v>51.7</v>
       </c>
       <c r="H34" t="n">
-        <v>22</v>
+        <v>51.5</v>
       </c>
       <c r="I34" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J34" t="n">
-        <v>-70.47</v>
+        <v>-20.58</v>
       </c>
       <c r="K34" t="n">
-        <v>8.210000000000001</v>
+        <v>-48.8</v>
       </c>
       <c r="L34" t="n">
-        <v>70.95</v>
+        <v>52.96</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>08:16:52</t>
+          <t>08:18:48</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>2.79</v>
+        <v>3.19</v>
       </c>
       <c r="F35" t="n">
-        <v>6.9</v>
+        <v>4.95</v>
       </c>
       <c r="G35" t="n">
-        <v>58.1</v>
+        <v>35.4</v>
       </c>
       <c r="H35" t="n">
-        <v>42.4</v>
+        <v>36</v>
       </c>
       <c r="I35" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J35" t="n">
-        <v>-69.88</v>
+        <v>30.05</v>
       </c>
       <c r="K35" t="n">
-        <v>65.22</v>
+        <v>-119.48</v>
       </c>
       <c r="L35" t="n">
-        <v>95.59</v>
+        <v>123.2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>08:18:25</t>
+          <t>08:20:28</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>2.45</v>
+        <v>2.59</v>
       </c>
       <c r="F36" t="n">
-        <v>5.94</v>
+        <v>6.74</v>
       </c>
       <c r="G36" t="n">
-        <v>62.8</v>
+        <v>52.9</v>
       </c>
       <c r="H36" t="n">
-        <v>45.2</v>
+        <v>40.4</v>
       </c>
       <c r="I36" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J36" t="n">
-        <v>31.78</v>
+        <v>-114.89</v>
       </c>
       <c r="K36" t="n">
-        <v>108.66</v>
+        <v>40.02</v>
       </c>
       <c r="L36" t="n">
-        <v>113.21</v>
+        <v>121.66</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>08:19:57</t>
+          <t>08:22:09</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>2.15</v>
+        <v>2.39</v>
       </c>
       <c r="F37" t="n">
-        <v>4.37</v>
+        <v>6.9</v>
       </c>
       <c r="G37" t="n">
-        <v>47</v>
+        <v>48.4</v>
       </c>
       <c r="H37" t="n">
-        <v>8.1</v>
+        <v>58.4</v>
       </c>
       <c r="I37" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J37" t="n">
-        <v>-17.08</v>
+        <v>-39.48</v>
       </c>
       <c r="K37" t="n">
-        <v>111.57</v>
+        <v>107.62</v>
       </c>
       <c r="L37" t="n">
-        <v>112.87</v>
+        <v>114.63</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>08:25:00</t>
+          <t>08:27:05</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>2.04</v>
+        <v>2.4</v>
       </c>
       <c r="F38" t="n">
-        <v>4.14</v>
+        <v>6.9</v>
       </c>
       <c r="G38" t="n">
-        <v>49.9</v>
+        <v>44.5</v>
       </c>
       <c r="H38" t="n">
-        <v>71.90000000000001</v>
+        <v>56.4</v>
       </c>
       <c r="I38" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J38" t="n">
-        <v>166.47</v>
+        <v>-43.26</v>
       </c>
       <c r="K38" t="n">
-        <v>-16.78</v>
+        <v>-141.2</v>
       </c>
       <c r="L38" t="n">
-        <v>167.32</v>
+        <v>147.68</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>08:26:28</t>
+          <t>08:29:13</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>2.34</v>
+        <v>2.17</v>
       </c>
       <c r="F39" t="n">
-        <v>5.55</v>
+        <v>3.52</v>
       </c>
       <c r="G39" t="n">
-        <v>60.3</v>
+        <v>62.3</v>
       </c>
       <c r="H39" t="n">
-        <v>9.9</v>
+        <v>40.9</v>
       </c>
       <c r="I39" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J39" t="n">
-        <v>143.67</v>
+        <v>97.28</v>
       </c>
       <c r="K39" t="n">
-        <v>66.06</v>
+        <v>-57.54</v>
       </c>
       <c r="L39" t="n">
-        <v>158.13</v>
+        <v>113.02</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>08:27:40</t>
+          <t>08:30:31</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>2.51</v>
+        <v>2.01</v>
       </c>
       <c r="F40" t="n">
-        <v>4.81</v>
+        <v>4.35</v>
       </c>
       <c r="G40" t="n">
-        <v>54.9</v>
+        <v>52.8</v>
       </c>
       <c r="H40" t="n">
-        <v>49.1</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J40" t="n">
-        <v>286.73</v>
+        <v>114.51</v>
       </c>
       <c r="K40" t="n">
-        <v>-13.52</v>
+        <v>-59.57</v>
       </c>
       <c r="L40" t="n">
-        <v>287.04</v>
+        <v>129.08</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>08:32:34</t>
+          <t>08:35:13</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>2.96</v>
+        <v>2.11</v>
       </c>
       <c r="F41" t="n">
-        <v>4.99</v>
+        <v>6.35</v>
       </c>
       <c r="G41" t="n">
-        <v>45.1</v>
+        <v>59</v>
       </c>
       <c r="H41" t="n">
-        <v>24.7</v>
+        <v>65.09999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J41" t="n">
-        <v>-50.86</v>
+        <v>113.66</v>
       </c>
       <c r="K41" t="n">
-        <v>202.54</v>
+        <v>146.02</v>
       </c>
       <c r="L41" t="n">
-        <v>208.82</v>
+        <v>185.04</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>08:34:54</t>
+          <t>08:37:11</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>2.56</v>
+        <v>2.31</v>
       </c>
       <c r="F42" t="n">
-        <v>6.9</v>
+        <v>5.41</v>
       </c>
       <c r="G42" t="n">
-        <v>49.7</v>
+        <v>55.8</v>
       </c>
       <c r="H42" t="n">
-        <v>55.3</v>
+        <v>44.6</v>
       </c>
       <c r="I42" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>179.91</v>
+        <v>29.29</v>
       </c>
       <c r="K42" t="n">
-        <v>-48.56</v>
+        <v>-86.37</v>
       </c>
       <c r="L42" t="n">
-        <v>186.35</v>
+        <v>91.2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>08:36:16</t>
+          <t>08:38:41</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="F43" t="n">
-        <v>2.75</v>
+        <v>5.68</v>
       </c>
       <c r="G43" t="n">
-        <v>57.7</v>
+        <v>53.4</v>
       </c>
       <c r="H43" t="n">
-        <v>36.6</v>
+        <v>4</v>
       </c>
       <c r="I43" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J43" t="n">
-        <v>154.88</v>
+        <v>-103.62</v>
       </c>
       <c r="K43" t="n">
-        <v>-84.55</v>
+        <v>-140.27</v>
       </c>
       <c r="L43" t="n">
-        <v>176.45</v>
+        <v>174.39</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>08:48:31</t>
+          <t>08:49:54</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>2.33</v>
+        <v>2.52</v>
       </c>
       <c r="F44" t="n">
-        <v>5.5</v>
+        <v>4.91</v>
       </c>
       <c r="G44" t="n">
-        <v>46.6</v>
+        <v>53.2</v>
       </c>
       <c r="H44" t="n">
-        <v>37.7</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I44" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J44" t="n">
-        <v>36.84</v>
+        <v>-39.7</v>
       </c>
       <c r="K44" t="n">
-        <v>-11.64</v>
+        <v>-12.24</v>
       </c>
       <c r="L44" t="n">
-        <v>38.63</v>
+        <v>41.55</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>08:49:12</t>
+          <t>08:51:32</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.16</v>
+        <v>2.13</v>
       </c>
       <c r="F45" t="n">
-        <v>6.9</v>
+        <v>3.51</v>
       </c>
       <c r="G45" t="n">
-        <v>43.8</v>
+        <v>58.3</v>
       </c>
       <c r="H45" t="n">
-        <v>46.1</v>
+        <v>61.2</v>
       </c>
       <c r="I45" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>-9.58</v>
+        <v>-24.76</v>
       </c>
       <c r="K45" t="n">
-        <v>31.81</v>
+        <v>26.01</v>
       </c>
       <c r="L45" t="n">
-        <v>33.22</v>
+        <v>35.91</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>08:50:30</t>
+          <t>08:53:36</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>1.89</v>
+        <v>2.21</v>
       </c>
       <c r="F46" t="n">
-        <v>4.76</v>
+        <v>4.13</v>
       </c>
       <c r="G46" t="n">
-        <v>44.5</v>
+        <v>47.5</v>
       </c>
       <c r="H46" t="n">
-        <v>21.6</v>
+        <v>14.6</v>
       </c>
       <c r="I46" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J46" t="n">
-        <v>-34.15</v>
+        <v>4.15</v>
       </c>
       <c r="K46" t="n">
-        <v>-7.57</v>
+        <v>-42.14</v>
       </c>
       <c r="L46" t="n">
-        <v>34.98</v>
+        <v>42.34</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>08:55:15</t>
+          <t>08:58:31</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>2.41</v>
+        <v>2.11</v>
       </c>
       <c r="F47" t="n">
-        <v>5.51</v>
+        <v>6.79</v>
       </c>
       <c r="G47" t="n">
-        <v>41.7</v>
+        <v>48.9</v>
       </c>
       <c r="H47" t="n">
-        <v>41.4</v>
+        <v>12.5</v>
       </c>
       <c r="I47" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J47" t="n">
-        <v>43.62</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="K47" t="n">
-        <v>16.59</v>
+        <v>64.81999999999999</v>
       </c>
       <c r="L47" t="n">
-        <v>46.67</v>
+        <v>65.38</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>08:56:25</t>
+          <t>09:00:58</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>2.4</v>
+        <v>2.29</v>
       </c>
       <c r="F48" t="n">
-        <v>6.83</v>
+        <v>6.9</v>
       </c>
       <c r="G48" t="n">
-        <v>48.8</v>
+        <v>47.7</v>
       </c>
       <c r="H48" t="n">
-        <v>56.7</v>
+        <v>57.2</v>
       </c>
       <c r="I48" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J48" t="n">
-        <v>54.78</v>
+        <v>16.71</v>
       </c>
       <c r="K48" t="n">
-        <v>-36.13</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="L48" t="n">
-        <v>65.62</v>
+        <v>72.06</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>08:57:27</t>
+          <t>09:02:14</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>2.13</v>
+        <v>2.19</v>
       </c>
       <c r="F49" t="n">
-        <v>6.9</v>
+        <v>4.98</v>
       </c>
       <c r="G49" t="n">
-        <v>43.1</v>
+        <v>52.4</v>
       </c>
       <c r="H49" t="n">
-        <v>26.2</v>
+        <v>45.8</v>
       </c>
       <c r="I49" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J49" t="n">
-        <v>43.18</v>
+        <v>-45.66</v>
       </c>
       <c r="K49" t="n">
-        <v>-53.1</v>
+        <v>22.67</v>
       </c>
       <c r="L49" t="n">
-        <v>68.44</v>
+        <v>50.98</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>09:01:41</t>
+          <t>09:06:49</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2.42</v>
+        <v>2.33</v>
       </c>
       <c r="F50" t="n">
-        <v>5.34</v>
+        <v>6.72</v>
       </c>
       <c r="G50" t="n">
-        <v>47.1</v>
+        <v>43.7</v>
       </c>
       <c r="H50" t="n">
-        <v>46.3</v>
+        <v>52.1</v>
       </c>
       <c r="I50" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J50" t="n">
-        <v>28</v>
+        <v>-20.71</v>
       </c>
       <c r="K50" t="n">
-        <v>93.42</v>
+        <v>-105.12</v>
       </c>
       <c r="L50" t="n">
-        <v>97.53</v>
+        <v>107.14</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>09:03:29</t>
+          <t>09:09:00</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>2.14</v>
+        <v>3.09</v>
       </c>
       <c r="F51" t="n">
-        <v>4.72</v>
+        <v>6.9</v>
       </c>
       <c r="G51" t="n">
-        <v>40</v>
+        <v>57.7</v>
       </c>
       <c r="H51" t="n">
-        <v>29.4</v>
+        <v>62.9</v>
       </c>
       <c r="I51" t="n">
         <v>27</v>
       </c>
       <c r="J51" t="n">
-        <v>-7.86</v>
+        <v>-77.18000000000001</v>
       </c>
       <c r="K51" t="n">
-        <v>-111.68</v>
+        <v>-57.74</v>
       </c>
       <c r="L51" t="n">
-        <v>111.95</v>
+        <v>96.39</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>09:05:23</t>
+          <t>09:11:06</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="F52" t="n">
-        <v>6.03</v>
+        <v>6.9</v>
       </c>
       <c r="G52" t="n">
-        <v>42.6</v>
+        <v>55.5</v>
       </c>
       <c r="H52" t="n">
-        <v>37.5</v>
+        <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J52" t="n">
-        <v>35.21</v>
+        <v>83.42</v>
       </c>
       <c r="K52" t="n">
-        <v>56.14</v>
+        <v>25.1</v>
       </c>
       <c r="L52" t="n">
-        <v>66.27</v>
+        <v>87.11</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>09:10:13</t>
+          <t>09:15:23</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>2.5</v>
+        <v>2.21</v>
       </c>
       <c r="F53" t="n">
-        <v>6.89</v>
+        <v>5.91</v>
       </c>
       <c r="G53" t="n">
-        <v>51.6</v>
+        <v>43.8</v>
       </c>
       <c r="H53" t="n">
-        <v>1.6</v>
+        <v>22.6</v>
       </c>
       <c r="I53" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J53" t="n">
-        <v>-67.67</v>
+        <v>129.25</v>
       </c>
       <c r="K53" t="n">
-        <v>-15.88</v>
+        <v>-61.16</v>
       </c>
       <c r="L53" t="n">
-        <v>69.51000000000001</v>
+        <v>142.99</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>09:12:18</t>
+          <t>09:17:22</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>2.38</v>
+        <v>2.6</v>
       </c>
       <c r="F54" t="n">
-        <v>6.9</v>
+        <v>5.05</v>
       </c>
       <c r="G54" t="n">
-        <v>37.9</v>
+        <v>65.2</v>
       </c>
       <c r="H54" t="n">
-        <v>15.6</v>
+        <v>53.1</v>
       </c>
       <c r="I54" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J54" t="n">
-        <v>129.26</v>
+        <v>-93.12</v>
       </c>
       <c r="K54" t="n">
-        <v>-82.06</v>
+        <v>-86.59</v>
       </c>
       <c r="L54" t="n">
-        <v>153.11</v>
+        <v>127.16</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>09:15:14</t>
+          <t>09:19:27</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>2.63</v>
+        <v>2.33</v>
       </c>
       <c r="F55" t="n">
         <v>6.9</v>
       </c>
       <c r="G55" t="n">
-        <v>37.7</v>
+        <v>49.2</v>
       </c>
       <c r="H55" t="n">
-        <v>31.8</v>
+        <v>55.6</v>
       </c>
       <c r="I55" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="J55" t="n">
-        <v>157.65</v>
+        <v>136.22</v>
       </c>
       <c r="K55" t="n">
-        <v>50.44</v>
+        <v>-62.51</v>
       </c>
       <c r="L55" t="n">
-        <v>165.53</v>
+        <v>149.87</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>09:18:19</t>
+          <t>09:25:34</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="F56" t="n">
         <v>6.9</v>
       </c>
       <c r="G56" t="n">
-        <v>64.59999999999999</v>
+        <v>40.9</v>
       </c>
       <c r="H56" t="n">
-        <v>43.2</v>
+        <v>32.1</v>
       </c>
       <c r="I56" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J56" t="n">
-        <v>-65.68000000000001</v>
+        <v>80.05</v>
       </c>
       <c r="K56" t="n">
-        <v>191.3</v>
+        <v>-126.42</v>
       </c>
       <c r="L56" t="n">
-        <v>202.26</v>
+        <v>149.63</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>09:19:49</t>
+          <t>09:27:21</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>2.35</v>
+        <v>2.07</v>
       </c>
       <c r="F57" t="n">
-        <v>5.22</v>
+        <v>6.9</v>
       </c>
       <c r="G57" t="n">
-        <v>42.5</v>
+        <v>67.8</v>
       </c>
       <c r="H57" t="n">
-        <v>50.6</v>
+        <v>38.7</v>
       </c>
       <c r="I57" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J57" t="n">
-        <v>202.23</v>
+        <v>59.11</v>
       </c>
       <c r="K57" t="n">
-        <v>54.61</v>
+        <v>-209.6</v>
       </c>
       <c r="L57" t="n">
-        <v>209.47</v>
+        <v>217.77</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>09:21:03</t>
+          <t>09:29:43</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="F58" t="n">
-        <v>6.9</v>
+        <v>5.83</v>
       </c>
       <c r="G58" t="n">
-        <v>44.6</v>
+        <v>47.5</v>
       </c>
       <c r="H58" t="n">
-        <v>45.1</v>
+        <v>34.9</v>
       </c>
       <c r="I58" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J58" t="n">
-        <v>53.19</v>
+        <v>160.34</v>
       </c>
       <c r="K58" t="n">
-        <v>160.42</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="L58" t="n">
-        <v>169.01</v>
+        <v>173.74</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>09:30:31</t>
+          <t>09:39:36</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>2.35</v>
+        <v>2.48</v>
       </c>
       <c r="F59" t="n">
         <v>6.9</v>
       </c>
       <c r="G59" t="n">
-        <v>46.2</v>
+        <v>45.5</v>
       </c>
       <c r="H59" t="n">
-        <v>57.2</v>
+        <v>28.3</v>
       </c>
       <c r="I59" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J59" t="n">
-        <v>-28.14</v>
+        <v>-12.06</v>
       </c>
       <c r="K59" t="n">
-        <v>17.98</v>
+        <v>-46.76</v>
       </c>
       <c r="L59" t="n">
-        <v>33.39</v>
+        <v>48.29</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>09:31:26</t>
+          <t>09:40:57</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="F60" t="n">
-        <v>5.74</v>
+        <v>4.89</v>
       </c>
       <c r="G60" t="n">
-        <v>37.6</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="H60" t="n">
-        <v>13.7</v>
+        <v>49.4</v>
       </c>
       <c r="I60" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J60" t="n">
-        <v>26.64</v>
+        <v>16.19</v>
       </c>
       <c r="K60" t="n">
-        <v>22.6</v>
+        <v>37.07</v>
       </c>
       <c r="L60" t="n">
-        <v>34.93</v>
+        <v>40.45</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>09:33:44</t>
+          <t>09:42:40</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>2.48</v>
+        <v>2.1</v>
       </c>
       <c r="F61" t="n">
         <v>6.9</v>
       </c>
       <c r="G61" t="n">
-        <v>60.9</v>
+        <v>43.8</v>
       </c>
       <c r="H61" t="n">
-        <v>50.9</v>
+        <v>58</v>
       </c>
       <c r="I61" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J61" t="n">
-        <v>-52.97</v>
+        <v>46.48</v>
       </c>
       <c r="K61" t="n">
-        <v>-12.87</v>
+        <v>36.1</v>
       </c>
       <c r="L61" t="n">
-        <v>54.51</v>
+        <v>58.85</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>09:38:04</t>
+          <t>09:48:30</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>2.2</v>
+        <v>2.52</v>
       </c>
       <c r="F62" t="n">
         <v>6.9</v>
       </c>
       <c r="G62" t="n">
-        <v>51.5</v>
+        <v>47.7</v>
       </c>
       <c r="H62" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="I62" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J62" t="n">
-        <v>13.95</v>
+        <v>-35.49</v>
       </c>
       <c r="K62" t="n">
-        <v>83.34</v>
+        <v>-63.32</v>
       </c>
       <c r="L62" t="n">
-        <v>84.5</v>
+        <v>72.58</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>09:39:41</t>
+          <t>09:50:13</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>2.32</v>
+        <v>2.55</v>
       </c>
       <c r="F63" t="n">
         <v>6.9</v>
       </c>
       <c r="G63" t="n">
-        <v>48.9</v>
+        <v>55</v>
       </c>
       <c r="H63" t="n">
-        <v>49</v>
+        <v>42.4</v>
       </c>
       <c r="I63" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="J63" t="n">
-        <v>12.43</v>
+        <v>-51.26</v>
       </c>
       <c r="K63" t="n">
-        <v>-64.29000000000001</v>
+        <v>-45.96</v>
       </c>
       <c r="L63" t="n">
-        <v>65.48</v>
+        <v>68.84</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>09:42:06</t>
+          <t>09:51:38</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>2.49</v>
+        <v>2.43</v>
       </c>
       <c r="F64" t="n">
-        <v>5.71</v>
+        <v>6.9</v>
       </c>
       <c r="G64" t="n">
-        <v>52.1</v>
+        <v>42</v>
       </c>
       <c r="H64" t="n">
-        <v>58.5</v>
+        <v>25.3</v>
       </c>
       <c r="I64" t="n">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="J64" t="n">
-        <v>-33.51</v>
+        <v>-67.12</v>
       </c>
       <c r="K64" t="n">
-        <v>-61.31</v>
+        <v>34.56</v>
       </c>
       <c r="L64" t="n">
-        <v>69.87</v>
+        <v>75.48999999999999</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>09:47:52</t>
+          <t>09:56:50</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="F65" t="n">
-        <v>6.23</v>
+        <v>6.9</v>
       </c>
       <c r="G65" t="n">
-        <v>49.9</v>
+        <v>49.7</v>
       </c>
       <c r="H65" t="n">
-        <v>24.6</v>
+        <v>41.4</v>
       </c>
       <c r="I65" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J65" t="n">
-        <v>-109.85</v>
+        <v>51.23</v>
       </c>
       <c r="K65" t="n">
-        <v>49.94</v>
+        <v>97.77</v>
       </c>
       <c r="L65" t="n">
-        <v>120.67</v>
+        <v>110.38</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>09:49:50</t>
+          <t>09:59:10</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>2.66</v>
+        <v>2.43</v>
       </c>
       <c r="F66" t="n">
-        <v>6.52</v>
+        <v>6.9</v>
       </c>
       <c r="G66" t="n">
-        <v>43.1</v>
+        <v>52.2</v>
       </c>
       <c r="H66" t="n">
-        <v>37.7</v>
+        <v>38.4</v>
       </c>
       <c r="I66" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J66" t="n">
-        <v>25.32</v>
+        <v>-73.19</v>
       </c>
       <c r="K66" t="n">
-        <v>-129.33</v>
+        <v>39.09</v>
       </c>
       <c r="L66" t="n">
-        <v>131.79</v>
+        <v>82.97</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>09:51:52</t>
+          <t>10:00:51</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>2.64</v>
+        <v>2.11</v>
       </c>
       <c r="F67" t="n">
-        <v>6.9</v>
+        <v>6.04</v>
       </c>
       <c r="G67" t="n">
-        <v>53.2</v>
+        <v>52.2</v>
       </c>
       <c r="H67" t="n">
-        <v>23.1</v>
+        <v>65.8</v>
       </c>
       <c r="I67" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J67" t="n">
-        <v>61.9</v>
+        <v>109.15</v>
       </c>
       <c r="K67" t="n">
-        <v>-32.82</v>
+        <v>-7.29</v>
       </c>
       <c r="L67" t="n">
-        <v>70.06</v>
+        <v>109.39</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>09:56:44</t>
+          <t>10:05:36</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>2.43</v>
+        <v>2.69</v>
       </c>
       <c r="F68" t="n">
-        <v>3.56</v>
+        <v>6.9</v>
       </c>
       <c r="G68" t="n">
-        <v>56.5</v>
+        <v>34</v>
       </c>
       <c r="H68" t="n">
-        <v>28.9</v>
+        <v>45.5</v>
       </c>
       <c r="I68" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J68" t="n">
-        <v>147.81</v>
+        <v>92.73</v>
       </c>
       <c r="K68" t="n">
-        <v>-12.09</v>
+        <v>-69.43000000000001</v>
       </c>
       <c r="L68" t="n">
-        <v>148.3</v>
+        <v>115.84</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>09:58:50</t>
+          <t>10:07:58</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>2.39</v>
+        <v>2.35</v>
       </c>
       <c r="F69" t="n">
-        <v>5.36</v>
+        <v>6.9</v>
       </c>
       <c r="G69" t="n">
-        <v>59.1</v>
+        <v>41.8</v>
       </c>
       <c r="H69" t="n">
-        <v>32.1</v>
+        <v>48.5</v>
       </c>
       <c r="I69" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="J69" t="n">
-        <v>106.65</v>
+        <v>83.14</v>
       </c>
       <c r="K69" t="n">
-        <v>-123.13</v>
+        <v>-6.88</v>
       </c>
       <c r="L69" t="n">
-        <v>162.89</v>
+        <v>83.42</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>10:01:27</t>
+          <t>10:09:27</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>2.29</v>
+        <v>2.16</v>
       </c>
       <c r="F70" t="n">
-        <v>6.9</v>
+        <v>6.58</v>
       </c>
       <c r="G70" t="n">
-        <v>45.5</v>
+        <v>38.5</v>
       </c>
       <c r="H70" t="n">
-        <v>46.2</v>
+        <v>53</v>
       </c>
       <c r="I70" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J70" t="n">
-        <v>-27.39</v>
+        <v>-138.91</v>
       </c>
       <c r="K70" t="n">
-        <v>-122.3</v>
+        <v>-1.02</v>
       </c>
       <c r="L70" t="n">
-        <v>125.33</v>
+        <v>138.91</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>10:05:40</t>
+          <t>10:15:18</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="F71" t="n">
-        <v>6.01</v>
+        <v>6.79</v>
       </c>
       <c r="G71" t="n">
-        <v>53.7</v>
+        <v>48.7</v>
       </c>
       <c r="H71" t="n">
-        <v>61.3</v>
+        <v>14</v>
       </c>
       <c r="I71" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>-108.01</v>
+        <v>-227.93</v>
       </c>
       <c r="K71" t="n">
-        <v>164.43</v>
+        <v>-9.289999999999999</v>
       </c>
       <c r="L71" t="n">
-        <v>196.73</v>
+        <v>228.12</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>10:07:32</t>
+          <t>10:16:42</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>2.49</v>
+        <v>2.16</v>
       </c>
       <c r="F72" t="n">
         <v>6.9</v>
       </c>
       <c r="G72" t="n">
-        <v>41.4</v>
+        <v>49.2</v>
       </c>
       <c r="H72" t="n">
-        <v>32.7</v>
+        <v>15</v>
       </c>
       <c r="I72" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J72" t="n">
-        <v>88.56999999999999</v>
+        <v>252.07</v>
       </c>
       <c r="K72" t="n">
-        <v>146.38</v>
+        <v>64.93000000000001</v>
       </c>
       <c r="L72" t="n">
-        <v>171.09</v>
+        <v>260.3</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>10:09:38</t>
+          <t>10:17:59</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.29</v>
+        <v>2.73</v>
       </c>
       <c r="F73" t="n">
-        <v>6.55</v>
+        <v>4.37</v>
       </c>
       <c r="G73" t="n">
-        <v>46.3</v>
+        <v>55.7</v>
       </c>
       <c r="H73" t="n">
-        <v>54.3</v>
+        <v>52.7</v>
       </c>
       <c r="I73" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J73" t="n">
-        <v>8.449999999999999</v>
+        <v>184.92</v>
       </c>
       <c r="K73" t="n">
-        <v>162.81</v>
+        <v>96.26000000000001</v>
       </c>
       <c r="L73" t="n">
-        <v>163.03</v>
+        <v>208.47</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>10:18:56</t>
+          <t>10:28:47</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>2.32</v>
+        <v>2.61</v>
       </c>
       <c r="F74" t="n">
         <v>6.9</v>
       </c>
       <c r="G74" t="n">
-        <v>54.4</v>
+        <v>46.2</v>
       </c>
       <c r="H74" t="n">
-        <v>24.6</v>
+        <v>66</v>
       </c>
       <c r="I74" t="n">
         <v>24</v>
       </c>
       <c r="J74" t="n">
-        <v>-28.59</v>
+        <v>31.76</v>
       </c>
       <c r="K74" t="n">
-        <v>-19.91</v>
+        <v>-35.57</v>
       </c>
       <c r="L74" t="n">
-        <v>34.84</v>
+        <v>47.68</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>10:20:12</t>
+          <t>10:30:49</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.8</v>
+        <v>2.48</v>
       </c>
       <c r="F75" t="n">
-        <v>6.57</v>
+        <v>6.9</v>
       </c>
       <c r="G75" t="n">
-        <v>43.5</v>
+        <v>45</v>
       </c>
       <c r="H75" t="n">
-        <v>69.5</v>
+        <v>30.4</v>
       </c>
       <c r="I75" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>13.33</v>
+        <v>-46.35</v>
       </c>
       <c r="K75" t="n">
-        <v>51.75</v>
+        <v>18.82</v>
       </c>
       <c r="L75" t="n">
-        <v>53.44</v>
+        <v>50.02</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>10:22:11</t>
+          <t>10:32:15</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>2.77</v>
+        <v>2.52</v>
       </c>
       <c r="F76" t="n">
         <v>6.9</v>
       </c>
       <c r="G76" t="n">
-        <v>53.9</v>
+        <v>53.2</v>
       </c>
       <c r="H76" t="n">
-        <v>24.4</v>
+        <v>20.4</v>
       </c>
       <c r="I76" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J76" t="n">
-        <v>48.91</v>
+        <v>-21.16</v>
       </c>
       <c r="K76" t="n">
-        <v>27.26</v>
+        <v>-33.32</v>
       </c>
       <c r="L76" t="n">
-        <v>56</v>
+        <v>39.47</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>10:26:36</t>
+          <t>10:35:48</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>2.51</v>
+        <v>2.81</v>
       </c>
       <c r="F77" t="n">
         <v>6.9</v>
       </c>
       <c r="G77" t="n">
-        <v>54.1</v>
+        <v>49.7</v>
       </c>
       <c r="H77" t="n">
-        <v>28.8</v>
+        <v>23.6</v>
       </c>
       <c r="I77" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="J77" t="n">
-        <v>3.43</v>
+        <v>62.43</v>
       </c>
       <c r="K77" t="n">
-        <v>-60.96</v>
+        <v>-41.9</v>
       </c>
       <c r="L77" t="n">
-        <v>61.06</v>
+        <v>75.19</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>10:27:27</t>
+          <t>10:36:54</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>2.41</v>
+        <v>2.23</v>
       </c>
       <c r="F78" t="n">
-        <v>5.13</v>
+        <v>6.9</v>
       </c>
       <c r="G78" t="n">
-        <v>49.4</v>
+        <v>46.6</v>
       </c>
       <c r="H78" t="n">
-        <v>36.6</v>
+        <v>30.9</v>
       </c>
       <c r="I78" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J78" t="n">
-        <v>-24.65</v>
+        <v>-34.4</v>
       </c>
       <c r="K78" t="n">
-        <v>70.61</v>
+        <v>-51.56</v>
       </c>
       <c r="L78" t="n">
-        <v>74.79000000000001</v>
+        <v>61.98</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>10:29:13</t>
+          <t>10:39:16</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>2.26</v>
+        <v>2.4</v>
       </c>
       <c r="F79" t="n">
-        <v>6.48</v>
+        <v>5.93</v>
       </c>
       <c r="G79" t="n">
-        <v>47.4</v>
+        <v>47.6</v>
       </c>
       <c r="H79" t="n">
-        <v>23.4</v>
+        <v>24.1</v>
       </c>
       <c r="I79" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="J79" t="n">
-        <v>-17.15</v>
+        <v>89.87</v>
       </c>
       <c r="K79" t="n">
-        <v>-59.97</v>
+        <v>-22.73</v>
       </c>
       <c r="L79" t="n">
-        <v>62.37</v>
+        <v>92.7</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>10:34:35</t>
+          <t>10:43:41</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>2.17</v>
+        <v>2.81</v>
       </c>
       <c r="F80" t="n">
-        <v>5.04</v>
+        <v>6.9</v>
       </c>
       <c r="G80" t="n">
-        <v>57.9</v>
+        <v>46.1</v>
       </c>
       <c r="H80" t="n">
-        <v>34.7</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="I80" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J80" t="n">
-        <v>-110.53</v>
+        <v>-60.43</v>
       </c>
       <c r="K80" t="n">
-        <v>40.11</v>
+        <v>41.91</v>
       </c>
       <c r="L80" t="n">
-        <v>117.59</v>
+        <v>73.54000000000001</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>10:36:55</t>
+          <t>10:45:31</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>2.33</v>
+        <v>2.52</v>
       </c>
       <c r="F81" t="n">
-        <v>4.33</v>
+        <v>6.12</v>
       </c>
       <c r="G81" t="n">
-        <v>55.1</v>
+        <v>52.2</v>
       </c>
       <c r="H81" t="n">
-        <v>69.2</v>
+        <v>21.4</v>
       </c>
       <c r="I81" t="n">
         <v>24</v>
       </c>
       <c r="J81" t="n">
-        <v>-14.32</v>
+        <v>-39.74</v>
       </c>
       <c r="K81" t="n">
-        <v>96.79000000000001</v>
+        <v>-80.65000000000001</v>
       </c>
       <c r="L81" t="n">
-        <v>97.84</v>
+        <v>89.91</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>10:38:55</t>
+          <t>10:46:28</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>2.83</v>
+        <v>2.6</v>
       </c>
       <c r="F82" t="n">
-        <v>6.9</v>
+        <v>6.82</v>
       </c>
       <c r="G82" t="n">
-        <v>49.2</v>
+        <v>44.2</v>
       </c>
       <c r="H82" t="n">
-        <v>73.90000000000001</v>
+        <v>32.9</v>
       </c>
       <c r="I82" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J82" t="n">
-        <v>88.16</v>
+        <v>129.64</v>
       </c>
       <c r="K82" t="n">
-        <v>17.71</v>
+        <v>-26.38</v>
       </c>
       <c r="L82" t="n">
-        <v>89.92</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>10:42:51</t>
+          <t>10:51:05</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="F83" t="n">
         <v>6.9</v>
       </c>
       <c r="G83" t="n">
-        <v>47.6</v>
+        <v>42</v>
       </c>
       <c r="H83" t="n">
-        <v>85</v>
+        <v>20.4</v>
       </c>
       <c r="I83" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J83" t="n">
-        <v>102.25</v>
+        <v>-99.23999999999999</v>
       </c>
       <c r="K83" t="n">
-        <v>-397.51</v>
+        <v>-22.52</v>
       </c>
       <c r="L83" t="n">
-        <v>410.45</v>
+        <v>101.76</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>10:43:58</t>
+          <t>10:52:25</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>2.63</v>
+        <v>2.45</v>
       </c>
       <c r="F84" t="n">
-        <v>6.9</v>
+        <v>5.69</v>
       </c>
       <c r="G84" t="n">
-        <v>42.7</v>
+        <v>66.2</v>
       </c>
       <c r="H84" t="n">
-        <v>3</v>
+        <v>35.9</v>
       </c>
       <c r="I84" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J84" t="n">
-        <v>-105.03</v>
+        <v>107.82</v>
       </c>
       <c r="K84" t="n">
-        <v>-109.87</v>
+        <v>-109.16</v>
       </c>
       <c r="L84" t="n">
-        <v>152</v>
+        <v>153.42</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>10:46:11</t>
+          <t>10:53:33</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>2.29</v>
+        <v>2.6</v>
       </c>
       <c r="F85" t="n">
         <v>6.9</v>
       </c>
       <c r="G85" t="n">
-        <v>51.9</v>
+        <v>52.2</v>
       </c>
       <c r="H85" t="n">
-        <v>30.1</v>
+        <v>0</v>
       </c>
       <c r="I85" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="J85" t="n">
-        <v>55.64</v>
+        <v>147.26</v>
       </c>
       <c r="K85" t="n">
-        <v>117.1</v>
+        <v>56.33</v>
       </c>
       <c r="L85" t="n">
-        <v>129.65</v>
+        <v>157.67</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>10:51:26</t>
+          <t>10:58:57</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="F86" t="n">
-        <v>5.87</v>
+        <v>6.45</v>
       </c>
       <c r="G86" t="n">
-        <v>55.9</v>
+        <v>46.9</v>
       </c>
       <c r="H86" t="n">
-        <v>35.4</v>
+        <v>38.3</v>
       </c>
       <c r="I86" t="n">
         <v>23</v>
       </c>
       <c r="J86" t="n">
-        <v>97.02</v>
+        <v>-132.08</v>
       </c>
       <c r="K86" t="n">
-        <v>-211.86</v>
+        <v>-95.54000000000001</v>
       </c>
       <c r="L86" t="n">
-        <v>233.01</v>
+        <v>163.01</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>10:53:02</t>
+          <t>11:01:01</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2.89</v>
+        <v>2.47</v>
       </c>
       <c r="F87" t="n">
         <v>6.9</v>
       </c>
       <c r="G87" t="n">
-        <v>51.7</v>
+        <v>38.3</v>
       </c>
       <c r="H87" t="n">
-        <v>41.8</v>
+        <v>51.1</v>
       </c>
       <c r="I87" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>-67.73999999999999</v>
+        <v>-91.78</v>
       </c>
       <c r="K87" t="n">
-        <v>-244.71</v>
+        <v>-143.98</v>
       </c>
       <c r="L87" t="n">
-        <v>253.92</v>
+        <v>170.74</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>10:53:33</t>
+          <t>11:02:27</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>2.25</v>
+        <v>2.83</v>
       </c>
       <c r="F88" t="n">
         <v>6.9</v>
       </c>
       <c r="G88" t="n">
-        <v>63.5</v>
+        <v>49</v>
       </c>
       <c r="H88" t="n">
-        <v>19.2</v>
+        <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>-27.34</v>
+        <v>7.06</v>
       </c>
       <c r="K88" t="n">
-        <v>146.9</v>
+        <v>186.58</v>
       </c>
       <c r="L88" t="n">
-        <v>149.43</v>
+        <v>186.72</v>
       </c>
     </row>
   </sheetData>

--- a/output/2025-10-01.xlsx
+++ b/output/2025-10-01.xlsx
@@ -640,13 +640,13 @@
         <v>21</v>
       </c>
       <c r="J14" t="n">
-        <v>39.07</v>
+        <v>37.17</v>
       </c>
       <c r="K14" t="n">
-        <v>14.48</v>
+        <v>13.77</v>
       </c>
       <c r="L14" t="n">
-        <v>41.66</v>
+        <v>39.64</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>33.08</v>
+        <v>32.98</v>
       </c>
       <c r="K15" t="n">
-        <v>-6.21</v>
+        <v>-6.19</v>
       </c>
       <c r="L15" t="n">
-        <v>33.65</v>
+        <v>33.55</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>20</v>
       </c>
       <c r="J16" t="n">
-        <v>-49.33</v>
+        <v>-44.98</v>
       </c>
       <c r="K16" t="n">
-        <v>13.69</v>
+        <v>12.48</v>
       </c>
       <c r="L16" t="n">
-        <v>51.2</v>
+        <v>46.68</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>24</v>
       </c>
       <c r="J17" t="n">
-        <v>34.45</v>
+        <v>32.96</v>
       </c>
       <c r="K17" t="n">
-        <v>48.34</v>
+        <v>46.24</v>
       </c>
       <c r="L17" t="n">
-        <v>59.36</v>
+        <v>56.79</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>23</v>
       </c>
       <c r="J18" t="n">
-        <v>-76.54000000000001</v>
+        <v>-69.45</v>
       </c>
       <c r="K18" t="n">
-        <v>-38.72</v>
+        <v>-35.13</v>
       </c>
       <c r="L18" t="n">
-        <v>85.78</v>
+        <v>77.83</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>20</v>
       </c>
       <c r="J19" t="n">
-        <v>58.82</v>
+        <v>55.51</v>
       </c>
       <c r="K19" t="n">
-        <v>51.9</v>
+        <v>48.98</v>
       </c>
       <c r="L19" t="n">
-        <v>78.45</v>
+        <v>74.03</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>19</v>
       </c>
       <c r="J20" t="n">
-        <v>-61.93</v>
+        <v>-65.7</v>
       </c>
       <c r="K20" t="n">
-        <v>-49.62</v>
+        <v>-52.64</v>
       </c>
       <c r="L20" t="n">
-        <v>79.36</v>
+        <v>84.19</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>21</v>
       </c>
       <c r="J21" t="n">
-        <v>21.05</v>
+        <v>22.81</v>
       </c>
       <c r="K21" t="n">
-        <v>-62.34</v>
+        <v>-67.56</v>
       </c>
       <c r="L21" t="n">
-        <v>65.8</v>
+        <v>71.31</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>24</v>
       </c>
       <c r="J22" t="n">
-        <v>-61.7</v>
+        <v>-65.04000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>29.66</v>
+        <v>31.27</v>
       </c>
       <c r="L22" t="n">
-        <v>68.45999999999999</v>
+        <v>72.17</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>25</v>
       </c>
       <c r="J23" t="n">
-        <v>-78.95</v>
+        <v>-86.31</v>
       </c>
       <c r="K23" t="n">
-        <v>46.45</v>
+        <v>50.78</v>
       </c>
       <c r="L23" t="n">
-        <v>91.59999999999999</v>
+        <v>100.14</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>19</v>
       </c>
       <c r="J24" t="n">
-        <v>113.54</v>
+        <v>113.06</v>
       </c>
       <c r="K24" t="n">
-        <v>-113.87</v>
+        <v>-113.38</v>
       </c>
       <c r="L24" t="n">
-        <v>160.8</v>
+        <v>160.12</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>-1.38</v>
+        <v>-1.58</v>
       </c>
       <c r="K25" t="n">
-        <v>-72.66</v>
+        <v>-83.34</v>
       </c>
       <c r="L25" t="n">
-        <v>72.67</v>
+        <v>83.36</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>23</v>
       </c>
       <c r="J26" t="n">
-        <v>-182.16</v>
+        <v>-193.31</v>
       </c>
       <c r="K26" t="n">
-        <v>-43.66</v>
+        <v>-46.33</v>
       </c>
       <c r="L26" t="n">
-        <v>187.32</v>
+        <v>198.79</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>24</v>
       </c>
       <c r="J27" t="n">
-        <v>167.05</v>
+        <v>181.03</v>
       </c>
       <c r="K27" t="n">
-        <v>39.48</v>
+        <v>42.79</v>
       </c>
       <c r="L27" t="n">
-        <v>171.65</v>
+        <v>186.02</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>19</v>
       </c>
       <c r="J28" t="n">
-        <v>-79.45</v>
+        <v>-85.90000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>194.02</v>
+        <v>209.78</v>
       </c>
       <c r="L28" t="n">
-        <v>209.66</v>
+        <v>226.68</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>21</v>
       </c>
       <c r="J29" t="n">
-        <v>19.72</v>
+        <v>19.86</v>
       </c>
       <c r="K29" t="n">
-        <v>-30.73</v>
+        <v>-30.94</v>
       </c>
       <c r="L29" t="n">
-        <v>36.51</v>
+        <v>36.77</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>10.9</v>
+        <v>10.47</v>
       </c>
       <c r="K30" t="n">
-        <v>-52.95</v>
+        <v>-50.82</v>
       </c>
       <c r="L30" t="n">
-        <v>54.06</v>
+        <v>51.89</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>46.3</v>
+        <v>42.38</v>
       </c>
       <c r="K31" t="n">
-        <v>-26.28</v>
+        <v>-24.05</v>
       </c>
       <c r="L31" t="n">
-        <v>53.24</v>
+        <v>48.73</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>25</v>
       </c>
       <c r="J32" t="n">
-        <v>39.09</v>
+        <v>42.63</v>
       </c>
       <c r="K32" t="n">
-        <v>8.67</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>40.04</v>
+        <v>43.67</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>19</v>
       </c>
       <c r="J33" t="n">
-        <v>-67.98</v>
+        <v>-64.19</v>
       </c>
       <c r="K33" t="n">
-        <v>-49.35</v>
+        <v>-46.59</v>
       </c>
       <c r="L33" t="n">
-        <v>84</v>
+        <v>79.31999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>61.73</v>
+        <v>58.21</v>
       </c>
       <c r="K34" t="n">
-        <v>34.24</v>
+        <v>32.29</v>
       </c>
       <c r="L34" t="n">
-        <v>70.59</v>
+        <v>66.56999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>25</v>
       </c>
       <c r="J35" t="n">
-        <v>78.06</v>
+        <v>79.97</v>
       </c>
       <c r="K35" t="n">
-        <v>12.15</v>
+        <v>12.45</v>
       </c>
       <c r="L35" t="n">
-        <v>79</v>
+        <v>80.93000000000001</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>25</v>
       </c>
       <c r="J36" t="n">
-        <v>79.27</v>
+        <v>80.02</v>
       </c>
       <c r="K36" t="n">
-        <v>-43.55</v>
+        <v>-43.96</v>
       </c>
       <c r="L36" t="n">
-        <v>90.44</v>
+        <v>91.3</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>22</v>
       </c>
       <c r="J37" t="n">
-        <v>-34.44</v>
+        <v>-37.09</v>
       </c>
       <c r="K37" t="n">
-        <v>-64.5</v>
+        <v>-69.47</v>
       </c>
       <c r="L37" t="n">
-        <v>73.12</v>
+        <v>78.75</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>25</v>
       </c>
       <c r="J38" t="n">
-        <v>57.96</v>
+        <v>61.69</v>
       </c>
       <c r="K38" t="n">
-        <v>-80.81999999999999</v>
+        <v>-86.03</v>
       </c>
       <c r="L38" t="n">
-        <v>99.45</v>
+        <v>105.86</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>23</v>
       </c>
       <c r="J39" t="n">
-        <v>-142.96</v>
+        <v>-141.33</v>
       </c>
       <c r="K39" t="n">
-        <v>-7.69</v>
+        <v>-7.6</v>
       </c>
       <c r="L39" t="n">
-        <v>143.17</v>
+        <v>141.54</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>19</v>
       </c>
       <c r="J40" t="n">
-        <v>126.92</v>
+        <v>136.02</v>
       </c>
       <c r="K40" t="n">
-        <v>20.96</v>
+        <v>22.47</v>
       </c>
       <c r="L40" t="n">
-        <v>128.64</v>
+        <v>137.87</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>23</v>
       </c>
       <c r="J41" t="n">
-        <v>-199.54</v>
+        <v>-207.59</v>
       </c>
       <c r="K41" t="n">
-        <v>84.90000000000001</v>
+        <v>88.33</v>
       </c>
       <c r="L41" t="n">
-        <v>216.85</v>
+        <v>225.6</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>25</v>
       </c>
       <c r="J42" t="n">
-        <v>2.53</v>
+        <v>3.16</v>
       </c>
       <c r="K42" t="n">
-        <v>103.77</v>
+        <v>129.38</v>
       </c>
       <c r="L42" t="n">
-        <v>103.8</v>
+        <v>129.42</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>132.3</v>
+        <v>155.74</v>
       </c>
       <c r="K43" t="n">
-        <v>7.16</v>
+        <v>8.43</v>
       </c>
       <c r="L43" t="n">
-        <v>132.5</v>
+        <v>155.96</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>19</v>
       </c>
       <c r="J44" t="n">
-        <v>54.02</v>
+        <v>49.42</v>
       </c>
       <c r="K44" t="n">
-        <v>24.69</v>
+        <v>22.58</v>
       </c>
       <c r="L44" t="n">
-        <v>59.39</v>
+        <v>54.33</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>19</v>
       </c>
       <c r="J45" t="n">
-        <v>-33.44</v>
+        <v>-31.58</v>
       </c>
       <c r="K45" t="n">
-        <v>-40.29</v>
+        <v>-38.05</v>
       </c>
       <c r="L45" t="n">
-        <v>52.36</v>
+        <v>49.44</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>44.91</v>
+        <v>43.3</v>
       </c>
       <c r="K46" t="n">
-        <v>-4.83</v>
+        <v>-4.66</v>
       </c>
       <c r="L46" t="n">
-        <v>45.17</v>
+        <v>43.55</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>25</v>
       </c>
       <c r="J47" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="K47" t="n">
-        <v>-18.72</v>
+        <v>-20.52</v>
       </c>
       <c r="L47" t="n">
-        <v>18.75</v>
+        <v>20.55</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>25</v>
       </c>
       <c r="J48" t="n">
+        <v>63.8</v>
+      </c>
+      <c r="K48" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="L48" t="n">
         <v>67.42</v>
-      </c>
-      <c r="K48" t="n">
-        <v>23.04</v>
-      </c>
-      <c r="L48" t="n">
-        <v>71.25</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>21</v>
       </c>
       <c r="J49" t="n">
-        <v>25.07</v>
+        <v>23.67</v>
       </c>
       <c r="K49" t="n">
-        <v>69.44</v>
+        <v>65.56999999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>73.83</v>
+        <v>69.70999999999999</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>-61.14</v>
+        <v>-63.55</v>
       </c>
       <c r="K50" t="n">
-        <v>52.84</v>
+        <v>54.92</v>
       </c>
       <c r="L50" t="n">
-        <v>80.81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>25</v>
       </c>
       <c r="J51" t="n">
-        <v>-63.98</v>
+        <v>-64.86</v>
       </c>
       <c r="K51" t="n">
-        <v>57.32</v>
+        <v>58.11</v>
       </c>
       <c r="L51" t="n">
-        <v>85.91</v>
+        <v>87.09</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>84.84999999999999</v>
+        <v>86.38</v>
       </c>
       <c r="K52" t="n">
-        <v>12.47</v>
+        <v>12.69</v>
       </c>
       <c r="L52" t="n">
-        <v>85.77</v>
+        <v>87.3</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>21</v>
       </c>
       <c r="J53" t="n">
-        <v>120.29</v>
+        <v>125.36</v>
       </c>
       <c r="K53" t="n">
-        <v>10.37</v>
+        <v>10.8</v>
       </c>
       <c r="L53" t="n">
-        <v>120.74</v>
+        <v>125.82</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>21</v>
       </c>
       <c r="J54" t="n">
-        <v>88.65000000000001</v>
+        <v>92.42</v>
       </c>
       <c r="K54" t="n">
-        <v>-85.91</v>
+        <v>-89.56999999999999</v>
       </c>
       <c r="L54" t="n">
-        <v>123.45</v>
+        <v>128.7</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>19</v>
       </c>
       <c r="J55" t="n">
-        <v>75.67</v>
+        <v>76.8</v>
       </c>
       <c r="K55" t="n">
-        <v>-141.28</v>
+        <v>-143.38</v>
       </c>
       <c r="L55" t="n">
-        <v>160.26</v>
+        <v>162.65</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>24</v>
       </c>
       <c r="J56" t="n">
-        <v>193.69</v>
+        <v>200.51</v>
       </c>
       <c r="K56" t="n">
-        <v>112.01</v>
+        <v>115.96</v>
       </c>
       <c r="L56" t="n">
-        <v>223.74</v>
+        <v>231.63</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>21</v>
       </c>
       <c r="J57" t="n">
-        <v>33.96</v>
+        <v>37.25</v>
       </c>
       <c r="K57" t="n">
-        <v>184.97</v>
+        <v>202.9</v>
       </c>
       <c r="L57" t="n">
-        <v>188.07</v>
+        <v>206.29</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>20</v>
       </c>
       <c r="J58" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="K58" t="n">
-        <v>179.53</v>
+        <v>198.89</v>
       </c>
       <c r="L58" t="n">
-        <v>179.59</v>
+        <v>198.95</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>20</v>
       </c>
       <c r="J59" t="n">
-        <v>22.59</v>
+        <v>23.02</v>
       </c>
       <c r="K59" t="n">
-        <v>-36.93</v>
+        <v>-37.63</v>
       </c>
       <c r="L59" t="n">
-        <v>43.29</v>
+        <v>44.11</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>20</v>
       </c>
       <c r="J60" t="n">
-        <v>-45.14</v>
+        <v>-40.33</v>
       </c>
       <c r="K60" t="n">
-        <v>51.87</v>
+        <v>46.34</v>
       </c>
       <c r="L60" t="n">
-        <v>68.76000000000001</v>
+        <v>61.43</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>25</v>
       </c>
       <c r="J61" t="n">
-        <v>-34.34</v>
+        <v>-34.19</v>
       </c>
       <c r="K61" t="n">
-        <v>-7.52</v>
+        <v>-7.49</v>
       </c>
       <c r="L61" t="n">
-        <v>35.15</v>
+        <v>35</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>22</v>
       </c>
       <c r="J62" t="n">
-        <v>-63.71</v>
+        <v>-60.12</v>
       </c>
       <c r="K62" t="n">
-        <v>44.35</v>
+        <v>41.85</v>
       </c>
       <c r="L62" t="n">
-        <v>77.63</v>
+        <v>73.25</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>21</v>
       </c>
       <c r="J63" t="n">
-        <v>40.74</v>
+        <v>44.67</v>
       </c>
       <c r="K63" t="n">
-        <v>-15.51</v>
+        <v>-17.01</v>
       </c>
       <c r="L63" t="n">
-        <v>43.59</v>
+        <v>47.8</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>22</v>
       </c>
       <c r="J64" t="n">
-        <v>-34.47</v>
+        <v>-32.77</v>
       </c>
       <c r="K64" t="n">
-        <v>-62.23</v>
+        <v>-59.16</v>
       </c>
       <c r="L64" t="n">
-        <v>71.14</v>
+        <v>67.63</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>20</v>
       </c>
       <c r="J65" t="n">
-        <v>18.2</v>
+        <v>19.24</v>
       </c>
       <c r="K65" t="n">
-        <v>88.39</v>
+        <v>93.43000000000001</v>
       </c>
       <c r="L65" t="n">
-        <v>90.25</v>
+        <v>95.39</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>22</v>
       </c>
       <c r="J66" t="n">
-        <v>-28.01</v>
+        <v>-28.51</v>
       </c>
       <c r="K66" t="n">
-        <v>-90.20999999999999</v>
+        <v>-91.81999999999999</v>
       </c>
       <c r="L66" t="n">
-        <v>94.45</v>
+        <v>96.14</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>20</v>
       </c>
       <c r="J67" t="n">
-        <v>106.03</v>
+        <v>104.31</v>
       </c>
       <c r="K67" t="n">
-        <v>-47.31</v>
+        <v>-46.54</v>
       </c>
       <c r="L67" t="n">
-        <v>116.1</v>
+        <v>114.23</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>20</v>
       </c>
       <c r="J68" t="n">
-        <v>-121.71</v>
+        <v>-127.68</v>
       </c>
       <c r="K68" t="n">
-        <v>-50.3</v>
+        <v>-52.77</v>
       </c>
       <c r="L68" t="n">
-        <v>131.69</v>
+        <v>138.15</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>23</v>
       </c>
       <c r="J69" t="n">
-        <v>-107.55</v>
+        <v>-115.94</v>
       </c>
       <c r="K69" t="n">
-        <v>-24.76</v>
+        <v>-26.69</v>
       </c>
       <c r="L69" t="n">
-        <v>110.37</v>
+        <v>118.97</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>25</v>
       </c>
       <c r="J70" t="n">
-        <v>-83.59999999999999</v>
+        <v>-95.22</v>
       </c>
       <c r="K70" t="n">
-        <v>-13.6</v>
+        <v>-15.49</v>
       </c>
       <c r="L70" t="n">
-        <v>84.7</v>
+        <v>96.47</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>23</v>
       </c>
       <c r="J71" t="n">
-        <v>-43.31</v>
+        <v>-53.8</v>
       </c>
       <c r="K71" t="n">
-        <v>-31.15</v>
+        <v>-38.7</v>
       </c>
       <c r="L71" t="n">
-        <v>53.35</v>
+        <v>66.27</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>-25.22</v>
+        <v>-28.09</v>
       </c>
       <c r="K72" t="n">
-        <v>180.12</v>
+        <v>200.64</v>
       </c>
       <c r="L72" t="n">
-        <v>181.88</v>
+        <v>202.59</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>23</v>
       </c>
       <c r="J73" t="n">
-        <v>-231.75</v>
+        <v>-238.11</v>
       </c>
       <c r="K73" t="n">
-        <v>86.93000000000001</v>
+        <v>89.31999999999999</v>
       </c>
       <c r="L73" t="n">
-        <v>247.52</v>
+        <v>254.32</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>25</v>
       </c>
       <c r="J74" t="n">
-        <v>-48.93</v>
+        <v>-47.47</v>
       </c>
       <c r="K74" t="n">
-        <v>-4.98</v>
+        <v>-4.83</v>
       </c>
       <c r="L74" t="n">
-        <v>49.18</v>
+        <v>47.72</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>-6.31</v>
+        <v>-6.41</v>
       </c>
       <c r="K75" t="n">
-        <v>39.74</v>
+        <v>40.37</v>
       </c>
       <c r="L75" t="n">
-        <v>40.24</v>
+        <v>40.88</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>-37.12</v>
+        <v>-34.12</v>
       </c>
       <c r="K76" t="n">
-        <v>-32.7</v>
+        <v>-30.06</v>
       </c>
       <c r="L76" t="n">
-        <v>49.46</v>
+        <v>45.47</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>-55.07</v>
+        <v>-51.9</v>
       </c>
       <c r="K77" t="n">
-        <v>58.94</v>
+        <v>55.54</v>
       </c>
       <c r="L77" t="n">
-        <v>80.66</v>
+        <v>76.01000000000001</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>19</v>
       </c>
       <c r="J78" t="n">
-        <v>-67.38</v>
+        <v>-65.75</v>
       </c>
       <c r="K78" t="n">
-        <v>-47.88</v>
+        <v>-46.72</v>
       </c>
       <c r="L78" t="n">
-        <v>82.66</v>
+        <v>80.66</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>21</v>
       </c>
       <c r="J79" t="n">
-        <v>59</v>
+        <v>60.46</v>
       </c>
       <c r="K79" t="n">
-        <v>-7.67</v>
+        <v>-7.86</v>
       </c>
       <c r="L79" t="n">
-        <v>59.49</v>
+        <v>60.97</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>23</v>
       </c>
       <c r="J80" t="n">
-        <v>55.6</v>
+        <v>58.81</v>
       </c>
       <c r="K80" t="n">
-        <v>58.89</v>
+        <v>62.3</v>
       </c>
       <c r="L80" t="n">
-        <v>80.98999999999999</v>
+        <v>85.67</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>21</v>
       </c>
       <c r="J81" t="n">
-        <v>36.94</v>
+        <v>39.54</v>
       </c>
       <c r="K81" t="n">
-        <v>-81.34999999999999</v>
+        <v>-87.06999999999999</v>
       </c>
       <c r="L81" t="n">
-        <v>89.34</v>
+        <v>95.63</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>21</v>
       </c>
       <c r="J82" t="n">
-        <v>-85.43000000000001</v>
+        <v>-83.54000000000001</v>
       </c>
       <c r="K82" t="n">
-        <v>-78.05</v>
+        <v>-76.31999999999999</v>
       </c>
       <c r="L82" t="n">
-        <v>115.72</v>
+        <v>113.16</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>20</v>
       </c>
       <c r="J83" t="n">
-        <v>-125.37</v>
+        <v>-132.68</v>
       </c>
       <c r="K83" t="n">
-        <v>26.95</v>
+        <v>28.52</v>
       </c>
       <c r="L83" t="n">
-        <v>128.24</v>
+        <v>135.71</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>21</v>
       </c>
       <c r="J84" t="n">
-        <v>-44.05</v>
+        <v>-45.78</v>
       </c>
       <c r="K84" t="n">
-        <v>118.06</v>
+        <v>122.68</v>
       </c>
       <c r="L84" t="n">
-        <v>126.02</v>
+        <v>130.94</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>-31.73</v>
+        <v>-33.12</v>
       </c>
       <c r="K85" t="n">
-        <v>-122.27</v>
+        <v>-127.63</v>
       </c>
       <c r="L85" t="n">
-        <v>126.32</v>
+        <v>131.85</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>19</v>
       </c>
       <c r="J86" t="n">
-        <v>-128.94</v>
+        <v>-150.9</v>
       </c>
       <c r="K86" t="n">
-        <v>-84.8</v>
+        <v>-99.23999999999999</v>
       </c>
       <c r="L86" t="n">
-        <v>154.32</v>
+        <v>180.61</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>24</v>
       </c>
       <c r="J87" t="n">
-        <v>124.68</v>
+        <v>136.59</v>
       </c>
       <c r="K87" t="n">
-        <v>-130.04</v>
+        <v>-142.47</v>
       </c>
       <c r="L87" t="n">
-        <v>180.15</v>
+        <v>197.37</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>19</v>
       </c>
       <c r="J88" t="n">
-        <v>-129.86</v>
+        <v>-148.26</v>
       </c>
       <c r="K88" t="n">
-        <v>-112.42</v>
+        <v>-128.35</v>
       </c>
       <c r="L88" t="n">
-        <v>171.76</v>
+        <v>196.1</v>
       </c>
     </row>
   </sheetData>
